--- a/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
+++ b/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan'!$A$1:$AC$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan'!$A$1:$AD$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AD92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,90 +516,95 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Dirección</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sale de</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Duerme en</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Tramo de llegada (min)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Tramo de salida (min)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Carretera del día (min)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Km del día</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Concepto (tablero del Valle)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Dictamen</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Estado (MEN)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Nivel de afectación (MEN)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Tipo de vía</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Por qué</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Vía de acceso</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Coordenada en revisión</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Latitud</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Longitud</t>
         </is>
@@ -657,80 +662,85 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>VEREDA LA CLORINDA</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>56.69</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>63.34</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>120</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>51.2</v>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>EL CARMEN - VIA SIMON BOLIVAR CRUCE VIA 3201</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>3.54959</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>-76.632525</v>
       </c>
     </row>
@@ -786,80 +796,85 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>BORRERO AYERBE</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>62.64</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>67.12</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>129.8</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>62.1</v>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 16 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>LA JULIA CRUCE VIA 3201</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>3.574795</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>-76.64960499999999</v>
       </c>
     </row>
@@ -915,80 +930,85 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO EL CARMEN</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>64.3</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>69.73</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>134</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>63.1</v>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>EL CARMEN - VIA SIMON BOLIVAR CRUCE VIA 3201</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>3.5527246</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>-76.6515909</v>
       </c>
     </row>
@@ -1044,75 +1064,80 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>CORREG EL PALMAR</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>62.7</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>65.98999999999999</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>128.7</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 9 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>3.6041469</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>-76.6490644</v>
       </c>
     </row>
@@ -1168,75 +1193,80 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>VEREDA JIGUALES</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>82.3</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>76.19</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>158.5</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>3.595044</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>-76.665947</v>
       </c>
     </row>
@@ -1252,11 +1282,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1292,75 +1322,80 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO EL LIMONAR</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>121.24</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>103.59</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>224.8</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>110.3</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>3.606151</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>-76.70789000000001</v>
       </c>
     </row>
@@ -1380,7 +1415,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1416,80 +1451,85 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>KR 3 2 000</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>76.88</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>85.62</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>162.5</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>71.2</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Carrera 2</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>3.6489149</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>-76.56672399999999</v>
       </c>
     </row>
@@ -1509,7 +1549,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1545,80 +1585,85 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>KR 1 3 14</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>76.91</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>85.34999999999999</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>162.3</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 49 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Diagonal 1</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>3.6478665</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>-76.56629270000001</v>
       </c>
     </row>
@@ -1638,7 +1683,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1674,80 +1719,85 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO SANTA MARIA</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>103</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>101.04</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>204</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>121.1</v>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 7 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>SANTA MARIA - EL LIMONAR CRUCE VIA 23319VL02 K5+555</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>3.63352</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>-76.715591</v>
       </c>
     </row>
@@ -1767,7 +1817,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1803,80 +1853,85 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>KR 6 6 67</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>0.73</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>0.37</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>3.1</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>0.8</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Carrera 6</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>3.85991597259148</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>-76.38388046730552</v>
       </c>
     </row>
@@ -1896,7 +1951,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1932,80 +1987,85 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>KR 5 5 79</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>0.37</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>1.99</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>3.1</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>0.8</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Calle 6</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>3.86056963997</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>-76.38430955440001</v>
       </c>
     </row>
@@ -2021,11 +2081,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2061,80 +2121,85 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>VEREDA SAN JUAN</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>59.23</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>63.8</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>123</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>46.8</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 23 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>MEDIACANOA - MIRAVALLE - CAMPO ALEGRE - CRUCE VIA 2302</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>3.962278</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>-76.40526699999999</v>
       </c>
     </row>
@@ -2150,11 +2215,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2190,80 +2255,85 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO  MEDIA CANOA</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>9.4</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>40.8</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>93.59999999999999</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>62.9</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 24 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>MEDIACANOA - PRIMAVERA</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>3.900556391368746</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>-76.37662112784321</v>
       </c>
     </row>
@@ -2279,11 +2349,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2319,80 +2389,85 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>KR 9 13 08</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>40.8</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>43.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>93.59999999999999</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>62.9</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 31 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>Carrera 9</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>3.82299113556</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>-76.52146344489999</v>
       </c>
     </row>
@@ -2412,7 +2487,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2448,75 +2523,80 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO VILLAMARIA</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>40.51</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>15.26</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>85.2</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>62.8</v>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Habitable</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>3.716456</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>-76.47793299999999</v>
       </c>
     </row>
@@ -2536,7 +2616,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2572,80 +2652,85 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>KR 4 5 34</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>15.26</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>29.46</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>85.2</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>62.8</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 3 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>Carrera 4</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>3.699871998710244</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>-76.44279828333418</v>
       </c>
     </row>
@@ -2665,7 +2750,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2701,80 +2786,85 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>VEREDA CAIMITAL</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>59.58</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>63.82</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>123.4</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>81.2</v>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Habitable</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 32 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>EL TAMBOR - LA RIVERA - OCACHE</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>3.741864</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>-76.49940700000001</v>
       </c>
     </row>
@@ -2794,7 +2884,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2830,80 +2920,85 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>CORREG LA MARIA</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>140.39</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>102.33</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>242.7</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>126.3</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>LA GUAIRA - KM113- LOMITAS</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>3.6919524</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
         <v>-76.63414659999999</v>
       </c>
     </row>
@@ -2959,70 +3054,75 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>QUEBRADASECA</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>63.71</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>4.65</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>95.7</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «trunk»). La sede queda a 37 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>Troncal de Occidente</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
         <v>3.850833</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
         <v>-76.29722</v>
       </c>
     </row>
@@ -3078,65 +3178,70 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>CORREG ZANJON-HONDO</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>4.65</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>27.37</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>95.7</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 78 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
         <v>3.845303584</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AD21" t="n">
         <v>-76.30364</v>
       </c>
     </row>
@@ -3192,70 +3297,75 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
           <t>CR 27 NO 14-23</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>21.21</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>7.2</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>29.6</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>16.9</v>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>Carrera 27</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
         <v>3.911822</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
         <v>-76.30735</v>
       </c>
     </row>
@@ -3311,70 +3421,75 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
           <t>CORREG EL PLACER</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>7.2</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>29.6</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>16.9</v>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 30 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>Calle 6</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB23" t="n">
+      <c r="AC23" t="n">
         <v>3.898611</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AD23" t="n">
         <v>-76.30056</v>
       </c>
     </row>
@@ -3430,70 +3545,75 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
           <t>KR 9 A 2 55 SUR</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>3.44</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>1.17</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>6.9</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>2</v>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 25 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>Carrera 9</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
         <v>3.892781656</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
         <v>-76.29845</v>
       </c>
     </row>
@@ -3549,65 +3669,70 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
           <t>CL 2 8 47</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1.17</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>2.28</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>6.9</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>2</v>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB25" t="n">
+      <c r="AC25" t="n">
         <v>3.894397016</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
         <v>-76.29777</v>
       </c>
     </row>
@@ -3663,65 +3788,70 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
           <t>CL 15 9 45</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>4.08</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>1.59</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>10.9</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>3.3</v>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
         <v>3.9055</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AD26" t="n">
         <v>-76.29489</v>
       </c>
     </row>
@@ -3777,70 +3907,75 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
           <t>CR 10 NO 18-81</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>1.59</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>5.21</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>10.9</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>3.3</v>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 29 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>Carrera 10</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB27" t="n">
+      <c r="AC27" t="n">
         <v>3.90894</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AD27" t="n">
         <v>-76.29465</v>
       </c>
     </row>
@@ -3896,70 +4031,75 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
           <t>VDA GUADUALEJO</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>4.38</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>0.54</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>9.1</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>2.8</v>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>Calle 4A</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB28" t="n">
+      <c r="AC28" t="n">
         <v>3.893611111</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AD28" t="n">
         <v>-76.29111</v>
       </c>
     </row>
@@ -4015,70 +4155,75 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
           <t>CL 4 A 1 E 26</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>0.54</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>4.14</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>9.1</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>2.8</v>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 30 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>Calle 4</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB29" t="n">
+      <c r="AC29" t="n">
         <v>3.89307</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AD29" t="n">
         <v>-76.29131</v>
       </c>
     </row>
@@ -4094,11 +4239,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -4134,80 +4279,85 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO EL TABOR PUENTE BLANCO</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>96.04000000000001</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>69.08</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>165.1</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>104.6</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>Habitable</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>TRUJILLO - LA SONORA CRUCE VIA 23VL13-1 K64+160</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB30" t="n">
+      <c r="AC30" t="n">
         <v>4.210564</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AD30" t="n">
         <v>-76.38158300000001</v>
       </c>
     </row>
@@ -4227,7 +4377,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4263,70 +4413,75 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
           <t>IND CALLE 27 NO. 6AW 240</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>7.41</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>42.09</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>100.2</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>57</v>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>Calle 27</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB31" t="n">
+      <c r="AC31" t="n">
         <v>4.088515899</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AD31" t="n">
         <v>-76.22009</v>
       </c>
     </row>
@@ -4346,7 +4501,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4382,80 +4537,85 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
           <t>CORREG SALONICA</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>42.09</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>50.65</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>100.2</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>57</v>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>en revisión de la mesa</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>SALONICA CRUCE CON VIA 23VL13-1 EN K44+300</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB32" t="n">
+      <c r="AC32" t="n">
         <v>4.1258314</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AD32" t="n">
         <v>-76.3722336</v>
       </c>
     </row>
@@ -4475,7 +4635,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4511,80 +4671,85 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
           <t>KR 18 15 40</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>46.98</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>0.67</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>107.2</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>61.2</v>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>Carrera 18</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB33" t="n">
+      <c r="AC33" t="n">
         <v>4.208406</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AD33" t="n">
         <v>-76.31959500000001</v>
       </c>
     </row>
@@ -4604,7 +4769,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4640,70 +4805,75 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
           <t>KR 18 15 27</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>0.67</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>59.48</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>107.2</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>61.2</v>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>Carrera 18</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB34" t="n">
+      <c r="AC34" t="n">
         <v>4.210077</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AD34" t="n">
         <v>-76.319047</v>
       </c>
     </row>
@@ -4723,7 +4893,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4759,80 +4929,85 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
           <t>CL 6 4 15</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Caicedonia</t>
         </is>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>3.3</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>69.31</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>64.59999999999999</v>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>Calle 6</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB35" t="n">
+      <c r="AC35" t="n">
         <v>4.165067</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AD35" t="n">
         <v>-76.16943499999999</v>
       </c>
     </row>
@@ -4852,7 +5027,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4888,80 +5063,85 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
           <t>CL 5 11 15</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Caicedonia</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>1.47</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>59.43</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>92.90000000000001</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>79.7</v>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>Calle 5</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB36" t="n">
+      <c r="AC36" t="n">
         <v>4.329633623</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AD36" t="n">
         <v>-75.82531724</v>
       </c>
     </row>
@@ -4981,7 +5161,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -5017,80 +5197,85 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
           <t>CL 10 KR 10 EQ</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Caicedonia</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>59.43</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>31.96</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>92.90000000000001</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>79.7</v>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>Carrera 10</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB37" t="n">
+      <c r="AC37" t="n">
         <v>4.3959229</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AD37" t="n">
         <v>-76.0708454</v>
       </c>
     </row>
@@ -5106,11 +5291,11 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -5146,80 +5331,85 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
           <t>CL 4 5 38</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>48.65</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>14.74</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>114.3</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>93.2</v>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>Carrera 5</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB38" t="n">
+      <c r="AC38" t="n">
         <v>4.412260842287796</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AD38" t="n">
         <v>-76.15737540436542</v>
       </c>
     </row>
@@ -5235,11 +5425,11 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -5275,80 +5465,85 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
           <t>KR 2 2 66</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>14.74</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>50.86</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>114.3</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>93.2</v>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 43 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>BOLIVAR CRUCE CON VIA DE INVIAS 2302 EN TRAMO 23020 INICIO A 52m DE INICIO DE VIA 10023VL02B</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB39" t="n">
+      <c r="AC39" t="n">
         <v>4.340805</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AD39" t="n">
         <v>-76.17979800000001</v>
       </c>
     </row>
@@ -5364,11 +5559,11 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5404,65 +5599,70 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
           <t>IND CALLE 27 NO 6AW 240</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>32.44</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>62</v>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 50 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB40" t="n">
+      <c r="AC40" t="n">
         <v>4.090555556</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AD40" t="n">
         <v>-76.22221999999999</v>
       </c>
     </row>
@@ -5478,11 +5678,11 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5518,80 +5718,85 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
           <t>CORREG PORTUGAL DE PIEDRAS</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>32.44</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>47.02</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>62</v>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>PORTUGAL DE PIEDRAS - CRUCE VIA 23VL13</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB41" t="n">
+      <c r="AC41" t="n">
         <v>4.0553</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AD41" t="n">
         <v>-76.35465000000001</v>
       </c>
     </row>
@@ -5611,7 +5816,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5647,65 +5852,70 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
           <t>CL 23 KR 9 A</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>7.33</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>21.88</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>117.9</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>85</v>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 32 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB42" t="n">
+      <c r="AC42" t="n">
         <v>3.914166667</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AD42" t="n">
         <v>-76.2925</v>
       </c>
     </row>
@@ -5725,7 +5935,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5761,65 +5971,70 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
           <t>CHAMBIMBAL</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>21.88</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>88.65000000000001</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>117.9</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>85</v>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 187 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB43" t="n">
+      <c r="AC43" t="n">
         <v>3.956111</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AD43" t="n">
         <v>-76.30028</v>
       </c>
     </row>
@@ -5875,65 +6090,70 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
           <t>VDA EL GUAYABO</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Pereira</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>100.86</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>65.68000000000001</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>166.5</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>78.8</v>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 29 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB44" t="n">
+      <c r="AC44" t="n">
         <v>4.635095</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AD44" t="n">
         <v>-75.871531</v>
       </c>
     </row>
@@ -5989,65 +6209,70 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
           <t>VDA GUANABANO</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>20.37</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>9</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>42</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>15.4</v>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 7 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB45" t="n">
+      <c r="AC45" t="n">
         <v>4.764122</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AD45" t="n">
         <v>-75.966184</v>
       </c>
     </row>
@@ -6103,70 +6328,75 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
           <t>CORREG CAUCA</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>9</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>12.67</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="R46" t="n">
         <v>42</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>15.4</v>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 3 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>Carrera 2</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB46" t="n">
+      <c r="AC46" t="n">
         <v>4.764444444</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AD46" t="n">
         <v>-75.95083</v>
       </c>
     </row>
@@ -6222,65 +6452,70 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
           <t>VDA CHARA</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>44.94</v>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>9.27</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="R47" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
         <v>39.8</v>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB47" t="n">
+      <c r="AC47" t="n">
         <v>4.647653</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AD47" t="n">
         <v>-75.894413</v>
       </c>
     </row>
@@ -6336,65 +6571,70 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
           <t>VDA ORIENTE</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>9.27</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>43.73</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="R48" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="R48" t="n">
+      <c r="S48" t="n">
         <v>39.8</v>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 179 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB48" t="n">
+      <c r="AC48" t="n">
         <v>4.660883219</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AD48" t="n">
         <v>-75.88415999999999</v>
       </c>
     </row>
@@ -6450,65 +6690,70 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
           <t>CORREG PIEDRAS DE MOLER</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>25.12</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>32.36</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>110.6</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>41.7</v>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «primary»). La sede queda a 30 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB49" t="n">
+      <c r="AC49" t="n">
         <v>4.711094</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AD49" t="n">
         <v>-75.858474</v>
       </c>
     </row>
@@ -6564,65 +6809,70 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
           <t>VDA DE COLORADAS</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>32.36</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>53.08</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
         <v>110.6</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>41.7</v>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 45 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB50" t="n">
+      <c r="AC50" t="n">
         <v>4.648227</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AD50" t="n">
         <v>-75.85445900000001</v>
       </c>
     </row>
@@ -6678,80 +6928,85 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
           <t>CORREG EL VERGEL</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>65.8</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>65.38</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>131.2</v>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
         <v>54.1</v>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 13 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>EL VERGEL CRUCE CON VIA 04123VL13-5C EN K6+384</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB51" t="n">
+      <c r="AC51" t="n">
         <v>4.86111676163</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AD51" t="n">
         <v>-75.99733304110001</v>
       </c>
     </row>
@@ -6767,11 +7022,11 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -6807,80 +7062,85 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
           <t>CORREG EL VILLAR</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>97.39</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>97.67</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="R52" t="n">
         <v>195.1</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>Colapso total</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 34 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>LA PLAYA CRUCE CON VIA 04123VL13-5G3 EN K3</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB52" t="n">
+      <c r="AC52" t="n">
         <v>4.819842722212309</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AD52" t="n">
         <v>-76.08934449628445</v>
       </c>
     </row>
@@ -6900,7 +7160,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6936,80 +7196,85 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
           <t>VEREDA EL PLACER</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>104.08</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>102.25</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
         <v>206.3</v>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
         <v>85.8</v>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 3 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>EL REAL PLACER CRUCE CON VIA 0414802VL-G EN K22+316</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB53" t="n">
+      <c r="AC53" t="n">
         <v>4.7883859</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AD53" t="n">
         <v>-76.0724936</v>
       </c>
     </row>
@@ -7029,7 +7294,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -7065,80 +7330,85 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
           <t>VEREDA LA ESTRELLA</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>75.41</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="R54" t="n">
         <v>150.8</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>76.5</v>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>LAS BRISAS - EL BRILLANTE</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB54" t="n">
+      <c r="AC54" t="n">
         <v>4.72634</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AD54" t="n">
         <v>-76.11562499999999</v>
       </c>
     </row>
@@ -7158,7 +7428,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -7194,80 +7464,85 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
           <t>CORRG SAN FRANCISCO</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>40.95</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>15.49</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="R55" t="n">
         <v>103.2</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>SAN FRANCISCO CRUCE 82323VL02-N K0+000</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB55" t="n">
+      <c r="AC55" t="n">
         <v>4.68415925</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AD55" t="n">
         <v>-76.0351458</v>
       </c>
     </row>
@@ -7287,7 +7562,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -7323,80 +7598,85 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
           <t>CLL 18 NO 1-100</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>15.49</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>46.69</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="R56" t="n">
         <v>103.2</v>
       </c>
-      <c r="R56" t="n">
+      <c r="S56" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 41 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>Calle 18</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB56" t="n">
+      <c r="AC56" t="n">
         <v>4.60769678</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AD56" t="n">
         <v>-76.07215911999999</v>
       </c>
     </row>
@@ -7416,7 +7696,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -7452,65 +7732,70 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
           <t>CORREGIMENTO LA FLORIDA</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>33.24</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>34.3</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
         <v>67.5</v>
       </c>
-      <c r="R57" t="n">
+      <c r="S57" t="n">
         <v>36.4</v>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 14 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB57" t="n">
+      <c r="AC57" t="n">
         <v>4.64998614</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AD57" t="n">
         <v>-76.13698533</v>
       </c>
     </row>
@@ -7526,11 +7811,11 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -7566,80 +7851,85 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
           <t>CRA 14 NO 13-25</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>36.24</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>0.17</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="n">
         <v>44.3</v>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 11 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>Calle 13</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB58" t="n">
+      <c r="AC58" t="n">
         <v>4.5307229</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AD58" t="n">
         <v>-76.1031742</v>
       </c>
     </row>
@@ -7655,11 +7945,11 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -7695,80 +7985,85 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
           <t>CL 13 14 51</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>0.17</v>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>39.7</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="R59" t="n">
+      <c r="S59" t="n">
         <v>44.3</v>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 14 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>Calle 13</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB59" t="n">
+      <c r="AC59" t="n">
         <v>4.5306222</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AD59" t="n">
         <v>-76.10365280000001</v>
       </c>
     </row>
@@ -7784,11 +8079,11 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -7824,80 +8119,85 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
           <t>CL 16 16 00</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>35.88</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>13.08</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="R60" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="R60" t="n">
+      <c r="S60" t="n">
         <v>64.59999999999999</v>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>Colapso total</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 11 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>Calle 16</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB60" t="n">
+      <c r="AC60" t="n">
         <v>4.53325</v>
       </c>
-      <c r="AC60" t="n">
+      <c r="AD60" t="n">
         <v>-76.1032</v>
       </c>
     </row>
@@ -7913,11 +8213,11 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -7953,80 +8253,85 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
           <t>CL 8 7 61</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O61" t="n">
+      <c r="P61" t="n">
         <v>13.08</v>
       </c>
-      <c r="P61" t="n">
+      <c r="Q61" t="n">
         <v>39.94</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="R61" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="R61" t="n">
+      <c r="S61" t="n">
         <v>64.59999999999999</v>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>Carrera 8</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB61" t="n">
+      <c r="AC61" t="n">
         <v>4.522653896403604</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AD61" t="n">
         <v>-76.0369985666723</v>
       </c>
     </row>
@@ -8046,7 +8351,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -8082,65 +8387,70 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
           <t>VDA BUENA VISTA</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>Pereira</t>
         </is>
       </c>
-      <c r="O62" t="n">
+      <c r="P62" t="n">
         <v>23.24</v>
       </c>
-      <c r="P62" t="n">
+      <c r="Q62" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="R62" t="n">
         <v>100.3</v>
       </c>
-      <c r="R62" t="n">
+      <c r="S62" t="n">
         <v>53.5</v>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB62" t="n">
+      <c r="AC62" t="n">
         <v>4.708390336</v>
       </c>
-      <c r="AC62" t="n">
+      <c r="AD62" t="n">
         <v>-75.87908</v>
       </c>
     </row>
@@ -8160,7 +8470,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -8196,65 +8506,70 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
           <t>CORREG MODIN</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>Pereira</t>
         </is>
       </c>
-      <c r="O63" t="n">
+      <c r="P63" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="P63" t="n">
+      <c r="Q63" t="n">
         <v>68.20999999999999</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="R63" t="n">
         <v>100.3</v>
       </c>
-      <c r="R63" t="n">
+      <c r="S63" t="n">
         <v>53.5</v>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB63" t="n">
+      <c r="AC63" t="n">
         <v>4.681657</v>
       </c>
-      <c r="AC63" t="n">
+      <c r="AD63" t="n">
         <v>-75.889206</v>
       </c>
     </row>
@@ -8310,70 +8625,75 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
           <t>PANORAMA PARTE ALTA</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O64" t="n">
+      <c r="P64" t="n">
         <v>28.88</v>
       </c>
-      <c r="P64" t="n">
+      <c r="Q64" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="R64" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="R64" t="n">
+      <c r="S64" t="n">
         <v>45.9</v>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 0 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>Calle 8</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB64" t="n">
+      <c r="AC64" t="n">
         <v>3.563871751</v>
       </c>
-      <c r="AC64" t="n">
+      <c r="AD64" t="n">
         <v>-76.49699</v>
       </c>
     </row>
@@ -8429,70 +8749,75 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
           <t>KR 18 G 17 A 60</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O65" t="n">
+      <c r="P65" t="n">
         <v>2.7</v>
       </c>
-      <c r="P65" t="n">
+      <c r="Q65" t="n">
         <v>40</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="R65" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="R65" t="n">
+      <c r="S65" t="n">
         <v>45.9</v>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 17 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>Calle 7</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB65" t="n">
+      <c r="AC65" t="n">
         <v>3.569142</v>
       </c>
-      <c r="AC65" t="n">
+      <c r="AD65" t="n">
         <v>-76.49818</v>
       </c>
     </row>
@@ -8548,70 +8873,75 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
           <t>CR 28 NO 33 12</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O66" t="n">
+      <c r="P66" t="n">
         <v>1.17</v>
       </c>
-      <c r="P66" t="n">
+      <c r="Q66" t="n">
         <v>1.41</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="R66" t="n">
         <v>2.6</v>
       </c>
-      <c r="R66" t="n">
+      <c r="S66" t="n">
         <v>0.8</v>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="V66" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 21 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>Calle 34</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB66" t="n">
+      <c r="AC66" t="n">
         <v>3.530963312</v>
       </c>
-      <c r="AC66" t="n">
+      <c r="AD66" t="n">
         <v>-76.29813</v>
       </c>
     </row>
@@ -8667,70 +8997,75 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
           <t>CL 40 KR 12 ESQ</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O67" t="n">
+      <c r="P67" t="n">
         <v>5.49</v>
       </c>
-      <c r="P67" t="n">
+      <c r="Q67" t="n">
         <v>4.7</v>
       </c>
-      <c r="Q67" t="n">
+      <c r="R67" t="n">
         <v>12</v>
       </c>
-      <c r="R67" t="n">
+      <c r="S67" t="n">
         <v>4</v>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>Calle 40</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB67" t="n">
+      <c r="AC67" t="n">
         <v>3.535564379</v>
       </c>
-      <c r="AC67" t="n">
+      <c r="AD67" t="n">
         <v>-76.28555</v>
       </c>
     </row>
@@ -8786,70 +9121,75 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
           <t>CR 22 CLL  33 ESQ</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O68" t="n">
+      <c r="P68" t="n">
         <v>4.7</v>
       </c>
-      <c r="P68" t="n">
+      <c r="Q68" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q68" t="n">
+      <c r="R68" t="n">
         <v>12</v>
       </c>
-      <c r="R68" t="n">
+      <c r="S68" t="n">
         <v>4</v>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>Calle 33</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB68" t="n">
+      <c r="AC68" t="n">
         <v>3.529666412</v>
       </c>
-      <c r="AC68" t="n">
+      <c r="AD68" t="n">
         <v>-76.29319</v>
       </c>
     </row>
@@ -8905,70 +9245,75 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
           <t>KR 25 21 52</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O69" t="n">
+      <c r="P69" t="n">
         <v>4.81</v>
       </c>
-      <c r="P69" t="n">
+      <c r="Q69" t="n">
         <v>0.26</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="R69" t="n">
         <v>10.2</v>
       </c>
-      <c r="R69" t="n">
+      <c r="S69" t="n">
         <v>3.2</v>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>Calle 21</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB69" t="n">
+      <c r="AC69" t="n">
         <v>3.519487</v>
       </c>
-      <c r="AC69" t="n">
+      <c r="AD69" t="n">
         <v>-76.29709</v>
       </c>
     </row>
@@ -9024,65 +9369,70 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
           <t>KR 24 A 20 97</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O70" t="n">
+      <c r="P70" t="n">
         <v>0.26</v>
       </c>
-      <c r="P70" t="n">
+      <c r="Q70" t="n">
         <v>5.15</v>
       </c>
-      <c r="Q70" t="n">
+      <c r="R70" t="n">
         <v>10.2</v>
       </c>
-      <c r="R70" t="n">
+      <c r="S70" t="n">
         <v>3.2</v>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="V70" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 27 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB70" t="n">
+      <c r="AC70" t="n">
         <v>3.518847963</v>
       </c>
-      <c r="AC70" t="n">
+      <c r="AD70" t="n">
         <v>-76.29706</v>
       </c>
     </row>
@@ -9138,65 +9488,70 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
           <t>KR 16 32 02</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O71" t="n">
+      <c r="P71" t="n">
         <v>7.29</v>
       </c>
-      <c r="P71" t="n">
+      <c r="Q71" t="n">
         <v>0.73</v>
       </c>
-      <c r="Q71" t="n">
+      <c r="R71" t="n">
         <v>14.3</v>
       </c>
-      <c r="R71" t="n">
+      <c r="S71" t="n">
         <v>4</v>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="V71" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 17 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB71" t="n">
+      <c r="AC71" t="n">
         <v>3.528177503</v>
       </c>
-      <c r="AC71" t="n">
+      <c r="AD71" t="n">
         <v>-76.28814</v>
       </c>
     </row>
@@ -9252,65 +9607,70 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
           <t>CLL 31NO 15 44</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O72" t="n">
+      <c r="P72" t="n">
         <v>0.73</v>
       </c>
-      <c r="P72" t="n">
+      <c r="Q72" t="n">
         <v>6.24</v>
       </c>
-      <c r="Q72" t="n">
+      <c r="R72" t="n">
         <v>14.3</v>
       </c>
-      <c r="R72" t="n">
+      <c r="S72" t="n">
         <v>4</v>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="V72" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="W72" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 41 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB72" t="n">
+      <c r="AC72" t="n">
         <v>3.52714115</v>
       </c>
-      <c r="AC72" t="n">
+      <c r="AD72" t="n">
         <v>-76.28801</v>
       </c>
     </row>
@@ -9326,11 +9686,11 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -9366,70 +9726,75 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
           <t>CLL 2ENO 31 20</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O73" t="n">
+      <c r="P73" t="n">
         <v>3.67</v>
       </c>
-      <c r="P73" t="n">
+      <c r="Q73" t="n">
         <v>3.91</v>
       </c>
-      <c r="Q73" t="n">
+      <c r="R73" t="n">
         <v>14.4</v>
       </c>
-      <c r="R73" t="n">
+      <c r="S73" t="n">
         <v>4.8</v>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="V73" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="W73" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 17 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>Calle 32A</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB73" t="n">
+      <c r="AC73" t="n">
         <v>3.528611111</v>
       </c>
-      <c r="AC73" t="n">
+      <c r="AD73" t="n">
         <v>-76.28861000000001</v>
       </c>
     </row>
@@ -9445,11 +9810,11 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -9485,70 +9850,75 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
           <t>CLL 30 NO 7  40</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O74" t="n">
+      <c r="P74" t="n">
         <v>3.91</v>
       </c>
-      <c r="P74" t="n">
+      <c r="Q74" t="n">
         <v>6.85</v>
       </c>
-      <c r="Q74" t="n">
+      <c r="R74" t="n">
         <v>14.4</v>
       </c>
-      <c r="R74" t="n">
+      <c r="S74" t="n">
         <v>4.8</v>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="V74" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="W74" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>Calle 30</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB74" t="n">
+      <c r="AC74" t="n">
         <v>3.523726631</v>
       </c>
-      <c r="AC74" t="n">
+      <c r="AD74" t="n">
         <v>-76.28198</v>
       </c>
     </row>
@@ -9568,7 +9938,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -9604,70 +9974,75 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
           <t>KR 31 15 A 40</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O75" t="n">
+      <c r="P75" t="n">
         <v>6.96</v>
       </c>
-      <c r="P75" t="n">
+      <c r="Q75" t="n">
         <v>4.04</v>
       </c>
-      <c r="Q75" t="n">
+      <c r="R75" t="n">
         <v>14</v>
       </c>
-      <c r="R75" t="n">
+      <c r="S75" t="n">
         <v>4.5</v>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="V75" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 14 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>Carrera 30</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB75" t="n">
+      <c r="AC75" t="n">
         <v>3.514837633</v>
       </c>
-      <c r="AC75" t="n">
+      <c r="AD75" t="n">
         <v>-76.30277</v>
       </c>
     </row>
@@ -9687,7 +10062,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -9723,70 +10098,75 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
           <t>CR 27 NO  25 50</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O76" t="n">
+      <c r="P76" t="n">
         <v>4.04</v>
       </c>
-      <c r="P76" t="n">
+      <c r="Q76" t="n">
         <v>3.03</v>
       </c>
-      <c r="Q76" t="n">
+      <c r="R76" t="n">
         <v>14</v>
       </c>
-      <c r="R76" t="n">
+      <c r="S76" t="n">
         <v>4.5</v>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="V76" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="W76" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>Carrera 27</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB76" t="n">
+      <c r="AC76" t="n">
         <v>3.522721634</v>
       </c>
-      <c r="AC76" t="n">
+      <c r="AD76" t="n">
         <v>-76.29872</v>
       </c>
     </row>
@@ -9806,7 +10186,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -9842,70 +10222,75 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
           <t>CR 35 NO 25B 10</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O77" t="n">
+      <c r="P77" t="n">
         <v>6.08</v>
       </c>
-      <c r="P77" t="n">
+      <c r="Q77" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q77" t="n">
+      <c r="R77" t="n">
         <v>14.5</v>
       </c>
-      <c r="R77" t="n">
+      <c r="S77" t="n">
         <v>4.7</v>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="V77" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
+      <c r="W77" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 31 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>Carrera 35</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB77" t="n">
+      <c r="AC77" t="n">
         <v>3.523493621</v>
       </c>
-      <c r="AC77" t="n">
+      <c r="AD77" t="n">
         <v>-76.306</v>
       </c>
     </row>
@@ -9925,7 +10310,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -9961,70 +10346,75 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
           <t>CL 23 33 A 37</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O78" t="n">
+      <c r="P78" t="n">
         <v>2.62</v>
       </c>
-      <c r="P78" t="n">
+      <c r="Q78" t="n">
         <v>5.81</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="R78" t="n">
         <v>14.5</v>
       </c>
-      <c r="R78" t="n">
+      <c r="S78" t="n">
         <v>4.7</v>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="V78" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr">
+      <c r="W78" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 16 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>Calle 23</t>
         </is>
       </c>
-      <c r="AA78" t="inlineStr">
+      <c r="AB78" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB78" t="n">
+      <c r="AC78" t="n">
         <v>3.521595</v>
       </c>
-      <c r="AC78" t="n">
+      <c r="AD78" t="n">
         <v>-76.30551</v>
       </c>
     </row>
@@ -10044,7 +10434,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -10080,65 +10470,70 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
           <t>CORREG AMAIME</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O79" t="n">
+      <c r="P79" t="n">
         <v>18.8</v>
       </c>
-      <c r="P79" t="n">
+      <c r="Q79" t="n">
         <v>14.44</v>
       </c>
-      <c r="Q79" t="n">
+      <c r="R79" t="n">
         <v>43.1</v>
       </c>
-      <c r="R79" t="n">
+      <c r="S79" t="n">
         <v>22.4</v>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="V79" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="W79" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 58 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB79" t="n">
+      <c r="AC79" t="n">
         <v>3.608742554</v>
       </c>
-      <c r="AC79" t="n">
+      <c r="AD79" t="n">
         <v>-76.26954000000001</v>
       </c>
     </row>
@@ -10158,7 +10553,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -10194,70 +10589,75 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
           <t>IND KR 35 CL 60 EQ</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O80" t="n">
+      <c r="P80" t="n">
         <v>14.44</v>
       </c>
-      <c r="P80" t="n">
+      <c r="Q80" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="Q80" t="n">
+      <c r="R80" t="n">
         <v>43.1</v>
       </c>
-      <c r="R80" t="n">
+      <c r="S80" t="n">
         <v>22.4</v>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="V80" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
+      <c r="W80" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="Y80" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>Carrera 35</t>
         </is>
       </c>
-      <c r="AA80" t="inlineStr">
+      <c r="AB80" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB80" t="n">
+      <c r="AC80" t="n">
         <v>3.5498</v>
       </c>
-      <c r="AC80" t="n">
+      <c r="AD80" t="n">
         <v>-76.306017</v>
       </c>
     </row>
@@ -10277,7 +10677,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -10313,65 +10713,70 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
           <t>VDA LA PAMPA</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O81" t="n">
+      <c r="P81" t="n">
         <v>20.23</v>
       </c>
-      <c r="P81" t="n">
+      <c r="Q81" t="n">
         <v>5.77</v>
       </c>
-      <c r="Q81" t="n">
+      <c r="R81" t="n">
         <v>44.6</v>
       </c>
-      <c r="R81" t="n">
+      <c r="S81" t="n">
         <v>23.1</v>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="V81" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr">
+      <c r="W81" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 60 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB81" t="n">
+      <c r="AC81" t="n">
         <v>3.593751949</v>
       </c>
-      <c r="AC81" t="n">
+      <c r="AD81" t="n">
         <v>-76.25812000000001</v>
       </c>
     </row>
@@ -10391,7 +10796,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -10427,65 +10832,70 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
           <t>CORREG AMAIME</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O82" t="n">
+      <c r="P82" t="n">
         <v>5.77</v>
       </c>
-      <c r="P82" t="n">
+      <c r="Q82" t="n">
         <v>18.61</v>
       </c>
-      <c r="Q82" t="n">
+      <c r="R82" t="n">
         <v>44.6</v>
       </c>
-      <c r="R82" t="n">
+      <c r="S82" t="n">
         <v>23.1</v>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="V82" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
+      <c r="W82" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 134 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr">
+      <c r="AB82" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB82" t="n">
+      <c r="AC82" t="n">
         <v>3.606101352</v>
       </c>
-      <c r="AC82" t="n">
+      <c r="AD82" t="n">
         <v>-76.26662</v>
       </c>
     </row>
@@ -10501,11 +10911,11 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -10541,70 +10951,75 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
           <t>KR 26 CL 12 ESQ</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O83" t="n">
+      <c r="P83" t="n">
         <v>6.98</v>
       </c>
-      <c r="P83" t="n">
+      <c r="Q83" t="n">
         <v>4.37</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="R83" t="n">
         <v>34.9</v>
       </c>
-      <c r="R83" t="n">
+      <c r="S83" t="n">
         <v>17.8</v>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="V83" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr">
+      <c r="W83" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>Calle 12</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr">
+      <c r="AB83" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB83" t="n">
+      <c r="AC83" t="n">
         <v>3.51096553</v>
       </c>
-      <c r="AC83" t="n">
+      <c r="AD83" t="n">
         <v>-76.29906</v>
       </c>
     </row>
@@ -10620,11 +11035,11 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -10660,70 +11075,75 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
           <t xml:space="preserve">IND CL 5 29 107 </t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O84" t="n">
+      <c r="P84" t="n">
         <v>4.37</v>
       </c>
-      <c r="P84" t="n">
+      <c r="Q84" t="n">
         <v>23.51</v>
       </c>
-      <c r="Q84" t="n">
+      <c r="R84" t="n">
         <v>34.9</v>
       </c>
-      <c r="R84" t="n">
+      <c r="S84" t="n">
         <v>17.8</v>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="V84" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V84" t="inlineStr">
+      <c r="W84" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>Calle 5</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB84" t="n">
+      <c r="AC84" t="n">
         <v>3.502527</v>
       </c>
-      <c r="AC84" t="n">
+      <c r="AD84" t="n">
         <v>-76.30364</v>
       </c>
     </row>
@@ -10739,11 +11159,11 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -10779,80 +11199,85 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
           <t>CL 7 9 11</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O85" t="n">
+      <c r="P85" t="n">
         <v>0.23</v>
       </c>
-      <c r="P85" t="n">
+      <c r="Q85" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q85" t="n">
+      <c r="R85" t="n">
         <v>2.2</v>
       </c>
-      <c r="R85" t="n">
+      <c r="S85" t="n">
         <v>0.6</v>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="V85" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr">
+      <c r="W85" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="Y85" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
+      <c r="AA85" t="inlineStr">
         <is>
           <t>Calle 7</t>
         </is>
       </c>
-      <c r="AA85" t="inlineStr">
+      <c r="AB85" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB85" t="n">
+      <c r="AC85" t="n">
         <v>3.407489</v>
       </c>
-      <c r="AC85" t="n">
+      <c r="AD85" t="n">
         <v>-76.34917799999999</v>
       </c>
     </row>
@@ -10868,11 +11293,11 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -10908,80 +11333,85 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
           <t>CL 7 8 42</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O86" t="n">
+      <c r="P86" t="n">
         <v>0.25</v>
       </c>
-      <c r="P86" t="n">
+      <c r="Q86" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q86" t="n">
+      <c r="R86" t="n">
         <v>2.2</v>
       </c>
-      <c r="R86" t="n">
+      <c r="S86" t="n">
         <v>0.6</v>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="U86" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="V86" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
+      <c r="W86" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>Calle 7</t>
         </is>
       </c>
-      <c r="AA86" t="inlineStr">
+      <c r="AB86" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB86" t="n">
+      <c r="AC86" t="n">
         <v>3.40761667</v>
       </c>
-      <c r="AC86" t="n">
+      <c r="AD86" t="n">
         <v>-76.34858894</v>
       </c>
     </row>
@@ -11001,7 +11431,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -11037,70 +11467,75 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
           <t>CR 21 NO 9-89</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O87" t="n">
+      <c r="P87" t="n">
         <v>27.65</v>
       </c>
-      <c r="P87" t="n">
+      <c r="Q87" t="n">
         <v>28.95</v>
       </c>
-      <c r="Q87" t="n">
+      <c r="R87" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="R87" t="n">
+      <c r="S87" t="n">
         <v>44</v>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="V87" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr">
+      <c r="W87" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 23 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="AA87" t="inlineStr">
         <is>
           <t>Calle 10</t>
         </is>
       </c>
-      <c r="AA87" t="inlineStr">
+      <c r="AB87" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB87" t="n">
+      <c r="AC87" t="n">
         <v>3.32644406118</v>
       </c>
-      <c r="AC87" t="n">
+      <c r="AD87" t="n">
         <v>-76.23742270629999</v>
       </c>
     </row>
@@ -11120,7 +11555,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -11156,80 +11591,85 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
           <t>CR 12 NO 10-81</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O88" t="n">
+      <c r="P88" t="n">
         <v>28.95</v>
       </c>
-      <c r="P88" t="n">
+      <c r="Q88" t="n">
         <v>8.539999999999999</v>
       </c>
-      <c r="Q88" t="n">
+      <c r="R88" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="R88" t="n">
+      <c r="S88" t="n">
         <v>44</v>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="V88" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr">
+      <c r="W88" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="Y88" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>CALLEJON FLORO MERCADO CRUCE VIA 13025VL04-2E</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr">
+      <c r="AB88" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB88" t="n">
+      <c r="AC88" t="n">
         <v>3.39537597879</v>
       </c>
-      <c r="AC88" t="n">
+      <c r="AD88" t="n">
         <v>-76.3859481842</v>
       </c>
     </row>
@@ -11249,7 +11689,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -11285,70 +11725,75 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
           <t>CLL 37 NO 42A 110</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O89" t="n">
+      <c r="P89" t="n">
         <v>23.96</v>
       </c>
-      <c r="P89" t="n">
+      <c r="Q89" t="n">
         <v>5.5</v>
       </c>
-      <c r="Q89" t="n">
+      <c r="R89" t="n">
         <v>32</v>
       </c>
-      <c r="R89" t="n">
+      <c r="S89" t="n">
         <v>20.4</v>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="V89" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr">
+      <c r="W89" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="AA89" t="inlineStr">
         <is>
           <t>Calle 38</t>
         </is>
       </c>
-      <c r="AA89" t="inlineStr">
+      <c r="AB89" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB89" t="n">
+      <c r="AC89" t="n">
         <v>3.534745489</v>
       </c>
-      <c r="AC89" t="n">
+      <c r="AD89" t="n">
         <v>-76.31374</v>
       </c>
     </row>
@@ -11368,7 +11813,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -11404,70 +11849,75 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
           <t>CLL 34 NO 31 71</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O90" t="n">
+      <c r="P90" t="n">
         <v>5.5</v>
       </c>
-      <c r="P90" t="n">
+      <c r="Q90" t="n">
         <v>2.57</v>
       </c>
-      <c r="Q90" t="n">
+      <c r="R90" t="n">
         <v>32</v>
       </c>
-      <c r="R90" t="n">
+      <c r="S90" t="n">
         <v>20.4</v>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="V90" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr">
+      <c r="W90" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>Calle 34</t>
         </is>
       </c>
-      <c r="AA90" t="inlineStr">
+      <c r="AB90" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB90" t="n">
+      <c r="AC90" t="n">
         <v>3.531528575</v>
       </c>
-      <c r="AC90" t="n">
+      <c r="AD90" t="n">
         <v>-76.30112</v>
       </c>
     </row>
@@ -11487,7 +11937,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -11523,65 +11973,70 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
           <t>CLL 20 NO 13A-16</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O91" t="n">
+      <c r="P91" t="n">
         <v>39.32</v>
       </c>
-      <c r="P91" t="n">
+      <c r="Q91" t="n">
         <v>17.94</v>
       </c>
-      <c r="Q91" t="n">
+      <c r="R91" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="R91" t="n">
+      <c r="S91" t="n">
         <v>50.8</v>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="V91" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V91" t="inlineStr">
+      <c r="W91" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA91" t="inlineStr">
+      <c r="AB91" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB91" t="n">
+      <c r="AC91" t="n">
         <v>3.573823</v>
       </c>
-      <c r="AC91" t="n">
+      <c r="AD91" t="n">
         <v>-76.48081000000001</v>
       </c>
     </row>
@@ -11601,7 +12056,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -11637,75 +12092,80 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
           <t>CLL 10 NO 31A-150</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O92" t="n">
+      <c r="P92" t="n">
         <v>17.94</v>
       </c>
-      <c r="P92" t="n">
+      <c r="Q92" t="n">
         <v>23.81</v>
       </c>
-      <c r="Q92" t="n">
+      <c r="R92" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="R92" t="n">
+      <c r="S92" t="n">
         <v>50.8</v>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="V92" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V92" t="inlineStr">
+      <c r="W92" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
+      <c r="Y92" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>Calle 10</t>
         </is>
       </c>
-      <c r="AA92" t="inlineStr">
+      <c r="AB92" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB92" t="n">
+      <c r="AC92" t="n">
         <v>3.51115</v>
       </c>
-      <c r="AC92" t="n">
+      <c r="AD92" t="n">
         <v>-76.51866</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC92"/>
+  <autoFilter ref="A1:AD92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11716,7 +12176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11731,7 +12191,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Las cinco secretarías. Las 91 sedes de las cinco secretarías. No cabe en el TdR: necesita una cuarta cuadrilla, con base en Cali, y 60 días de campo en vez de 45. Sin volver a la base los fines de semana.</t>
+          <t>Todo Valle* 4 cuadrillas. Las 91 sedes del Valle sin Buenaventura: las 43 del BID más Palmira, Yumbo, Tuluá, Buga y Cartago. El asterisco es eso. No cabe en el TdR: necesita una cuarta cuadrilla, con base en Cali, y 56 días de campo en vez de 45. Sin volver a la base los domingos.</t>
         </is>
       </c>
     </row>
@@ -11743,176 +12203,205 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Jornada</t>
+          <t>Semana de campo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hasta 8 horas contando carretera e inspecciones; cada inspección dura 3 horas.</t>
+          <t>De lunes a sábado, seis días. La semana 1 son los días 1 a 6, la 2 del 7 al 12, y así.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Tiempos</t>
+          <t>Jornada</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mapbox, saliendo a las 7:00, entre sedes a las 11:00 y regresando a las 16:00 de un martes.</t>
+          <t>Hasta 8 horas contando carretera e inspecciones; cada inspección dura 3 horas.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Noches fuera</t>
+          <t>Tiempos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Una por cada día que la cuadrilla termina fuera de su base. Los fines de semana no se suman.</t>
+          <t>Mapbox, saliendo a las 7:00, entre sedes a las 11:00 y regresando a las 16:00 de un martes.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
+          <t>Noches fuera</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Una por cada día que la cuadrilla termina fuera de su base. El domingo de descanso no se suma acá; para el alojamiento que se paga están las noches de hotel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
           <t>Coordenadas</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Las marcadas en revisión son provisionales.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Cuadrilla</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Días</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Sedes</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Horas de carretera</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Km</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Noches fuera</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>15</v>
-      </c>
-      <c r="C9" t="n">
-        <v>18</v>
-      </c>
-      <c r="D9" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1070</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6</v>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Cuadrilla</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Días</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Sedes</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Horas de carretera</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Km</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Noches fuera</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Noches de hotel</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>16.9</v>
+        <v>34.9</v>
       </c>
       <c r="E10" t="n">
-        <v>716</v>
+        <v>1070</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>25.6</v>
+        <v>16.9</v>
       </c>
       <c r="E11" t="n">
-        <v>740</v>
+        <v>716</v>
       </c>
       <c r="F11" t="n">
         <v>12</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>740</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B13" t="n">
         <v>15</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C13" t="n">
         <v>29</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D13" t="n">
         <v>7.6</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E13" t="n">
         <v>251</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F13" t="n">
         <v>14</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
+++ b/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
@@ -9520,7 +9520,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>

--- a/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
+++ b/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
@@ -3247,17 +3247,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SAN JUAN BOSCO</t>
+          <t>POLICARPA SALAVARRIETA</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAN JUAN BOSCO</t>
+          <t>INSTITUCION EDUCATIVA ALFONSO ZAWADZKY</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>276890000237</t>
+          <t>176890000020</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>VEREDA SAN JUAN</t>
+          <t>KR 6 6 67</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3286,20 +3286,20 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>59.23</v>
+        <v>0.73</v>
       </c>
       <c r="Q22" t="n">
-        <v>63.8</v>
+        <v>0.37</v>
       </c>
       <c r="R22" t="n">
-        <v>123</v>
+        <v>3.1</v>
       </c>
       <c r="S22" t="n">
-        <v>46.8</v>
+        <v>0.8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>No habitable</t>
+          <t>Peligro de colapso</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 23 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>MEDIACANOA - MIRAVALLE - CAMPO ALEGRE - CRUCE VIA 2302</t>
+          <t>Carrera 6</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="AC22" t="n">
-        <v>3.962278</v>
+        <v>3.85991597259148</v>
       </c>
       <c r="AD22" t="n">
-        <v>-76.40526699999999</v>
+        <v>-76.38388046730552</v>
       </c>
     </row>
     <row r="23">
@@ -3365,14 +3365,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>POLICARPA SALAVARRIETA</t>
+          <t>ALFONSO ZAWADZKY</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>176890000020</t>
+          <t>176890000305</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>KR 6 6 67</t>
+          <t>KR 5 5 79</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3416,24 +3416,24 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Yotoco</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.73</v>
+        <v>0.37</v>
       </c>
       <c r="Q23" t="n">
-        <v>22.81</v>
+        <v>1.99</v>
       </c>
       <c r="R23" t="n">
-        <v>25.8</v>
+        <v>3.1</v>
       </c>
       <c r="S23" t="n">
-        <v>14.1</v>
+        <v>0.8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Peligro de colapso</t>
+          <t>No habitable</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3443,32 +3443,32 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Carrera 6</t>
+          <t>Calle 6</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="AC23" t="n">
-        <v>3.85991597259148</v>
+        <v>3.86056963997</v>
       </c>
       <c r="AD23" t="n">
-        <v>-76.38388046730552</v>
+        <v>-76.38430955440001</v>
       </c>
     </row>
     <row r="24">
@@ -3506,88 +3506,103 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>BID (43)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SAN JUAN BOSCO</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA SAN JUAN BOSCO</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>276890000237</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>YOTOCO</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>VEREDA SAN JUAN</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Yotoco</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>NARCISO CABAL SALCEDO - SEDE PRINCIPAL</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA NARCISO CABAL SALCEDO</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>176111000469</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Buga</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>CL 2 8 47</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Yotoco</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Buga</t>
-        </is>
-      </c>
       <c r="P24" t="n">
-        <v>22.81</v>
+        <v>59.23</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.28</v>
+        <v>75.05</v>
       </c>
       <c r="R24" t="n">
-        <v>25.8</v>
+        <v>134.3</v>
       </c>
       <c r="S24" t="n">
-        <v>14.1</v>
+        <v>51.6</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>No habitable</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 15 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 23 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>MEDIACANOA - MIRAVALLE - CAMPO ALEGRE - CRUCE VIA 2302</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3596,10 +3611,10 @@
         </is>
       </c>
       <c r="AC24" t="n">
-        <v>3.894397016</v>
+        <v>3.962278</v>
       </c>
       <c r="AD24" t="n">
-        <v>-76.29777</v>
+        <v>-76.40526699999999</v>
       </c>
     </row>
     <row r="25">
@@ -3634,17 +3649,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CRISTOBAL COLÓN</t>
+          <t>ESC JOAQUIN CAMILO TORRES</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MANUEL ANTONIO SANCLEMENTE</t>
+          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>276111001087</t>
+          <t>176111001171</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3659,7 +3674,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>VDA GUADUALEJO</t>
+          <t>CL 15 9 45</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3673,20 +3688,20 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.38</v>
+        <v>4.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.54</v>
+        <v>4.46</v>
       </c>
       <c r="R25" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3706,12 +3721,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Calle 4A</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3720,10 +3730,10 @@
         </is>
       </c>
       <c r="AC25" t="n">
-        <v>3.893611111</v>
+        <v>3.9055</v>
       </c>
       <c r="AD25" t="n">
-        <v>-76.29111</v>
+        <v>-76.29489</v>
       </c>
     </row>
     <row r="26">
@@ -3758,17 +3768,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>MANUEL ANTONIO SANCLEMENTE - SEDE PRINCIPAL</t>
+          <t>EL PLACER - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MANUEL ANTONIO SANCLEMENTE</t>
+          <t>INSTITUCION EDUCATIVA EL PLACER</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>176111000515</t>
+          <t>276111000102</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3778,12 +3788,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>CL 4 A 1 E 26</t>
+          <t>CORREG EL PLACER</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3797,16 +3807,16 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.54</v>
+        <v>4.46</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.14</v>
+        <v>1.2</v>
       </c>
       <c r="R26" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -3820,7 +3830,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3830,12 +3840,12 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 30 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 30 m de esa vía.</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Calle 4</t>
+          <t>Calle 6</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3844,10 +3854,10 @@
         </is>
       </c>
       <c r="AC26" t="n">
-        <v>3.89307</v>
+        <v>3.898611</v>
       </c>
       <c r="AD26" t="n">
-        <v>-76.29131</v>
+        <v>-76.30056</v>
       </c>
     </row>
     <row r="27">
@@ -3882,17 +3892,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ESC JOAQUIN CAMILO TORRES</t>
+          <t>ACADEMICO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON</t>
+          <t>INSTITUCION EDUCATIVA ACADEMICO</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>176111001171</t>
+          <t>176111001104</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3907,7 +3917,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>CL 15 9 45</t>
+          <t>KR 9 A 2 55 SUR</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3917,29 +3927,29 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Caicedonia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4.08</v>
+        <v>3.44</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.59</v>
+        <v>1.17</v>
       </c>
       <c r="R27" t="n">
-        <v>106</v>
+        <v>6.9</v>
       </c>
       <c r="S27" t="n">
-        <v>98.7</v>
+        <v>2</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3954,7 +3964,12 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 12 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 25 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Carrera 9</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -3963,10 +3978,10 @@
         </is>
       </c>
       <c r="AC27" t="n">
-        <v>3.9055</v>
+        <v>3.892781656</v>
       </c>
       <c r="AD27" t="n">
-        <v>-76.29489</v>
+        <v>-76.29845</v>
       </c>
     </row>
     <row r="28">
@@ -4001,17 +4016,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ESC JORGE ELIECER GAITAN</t>
+          <t>NARCISO CABAL SALCEDO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON</t>
+          <t>INSTITUCION EDUCATIVA NARCISO CABAL SALCEDO</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>176111001139</t>
+          <t>176111000469</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4026,7 +4041,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>CR 10 NO 18-81</t>
+          <t>CL 2 8 47</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4036,29 +4051,29 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Caicedonia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.59</v>
+        <v>1.17</v>
       </c>
       <c r="Q28" t="n">
-        <v>100.29</v>
+        <v>2.28</v>
       </c>
       <c r="R28" t="n">
-        <v>106</v>
+        <v>6.9</v>
       </c>
       <c r="S28" t="n">
-        <v>98.7</v>
+        <v>2</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -4073,12 +4088,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 29 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Carrera 10</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4087,10 +4097,10 @@
         </is>
       </c>
       <c r="AC28" t="n">
-        <v>3.90894</v>
+        <v>3.894397016</v>
       </c>
       <c r="AD28" t="n">
-        <v>-76.29465</v>
+        <v>-76.29777</v>
       </c>
     </row>
     <row r="29">
@@ -4120,27 +4130,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>BOLIVARIANO</t>
+          <t>ESC JORGE ELIECER GAITAN</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA BOLIVARIANO</t>
+          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>176122000380</t>
+          <t>176111001139</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>CAICEDONIA</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -4150,44 +4160,34 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>CL 5 11 15</t>
+          <t>CR 10 NO 18-81</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Caicedonia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Andalucia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.47</v>
+        <v>3.97</v>
       </c>
       <c r="Q29" t="n">
-        <v>59.43</v>
+        <v>3.43</v>
       </c>
       <c r="R29" t="n">
-        <v>92.90000000000001</v>
+        <v>16.9</v>
       </c>
       <c r="S29" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Peligro de colapso</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>4.5</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 29 m de esa vía.</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Calle 5</t>
+          <t>Carrera 10</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4221,10 +4221,10 @@
         </is>
       </c>
       <c r="AC29" t="n">
-        <v>4.329633623</v>
+        <v>3.90894</v>
       </c>
       <c r="AD29" t="n">
-        <v>-75.82531724</v>
+        <v>-76.29465</v>
       </c>
     </row>
     <row r="30">
@@ -4254,27 +4254,27 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SANTA CECILIA</t>
+          <t>INSTITUTO TECNICO AGRICOLA-SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EFRAIN VARELA VACA</t>
+          <t>INSTITUCION EDUCATIVA AGRICOLA DE GUADALAJARA DE BUGA</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>176895000231</t>
+          <t>176111000507</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>ZARZAL</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -4284,54 +4284,44 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>CL 10 KR 10 EQ</t>
+          <t>CL 23 KR 9 A</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Caicedonia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Andalucia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>59.43</v>
+        <v>3.43</v>
       </c>
       <c r="Q30" t="n">
-        <v>31.96</v>
+        <v>9.52</v>
       </c>
       <c r="R30" t="n">
-        <v>92.90000000000001</v>
+        <v>16.9</v>
       </c>
       <c r="S30" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Peligro de colapso</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>4.5</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4341,12 +4331,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 18 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Carrera 10</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 32 m de esa vía.</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4355,10 +4340,10 @@
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>4.3959229</v>
+        <v>3.914166667</v>
       </c>
       <c r="AD30" t="n">
-        <v>-76.0708454</v>
+        <v>-76.2925</v>
       </c>
     </row>
     <row r="31">
@@ -4393,17 +4378,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>TULIO ENRIQUE TASCON CHAMBIMBAL - SEDE PRINCIPAL</t>
+          <t>CRISTOBAL COLÓN</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON CHAMBIMBAL</t>
+          <t>INSTITUCION EDUCATIVA MANUEL ANTONIO SANCLEMENTE</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>276111000781</t>
+          <t>276111001087</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4413,17 +4398,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>CHAMBIMBAL</t>
+          <t>VDA GUADUALEJO</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Andalucia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -4432,40 +4417,45 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>41.77</v>
+        <v>4.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>16.89</v>
+        <v>0.54</v>
       </c>
       <c r="R31" t="n">
-        <v>66.8</v>
+        <v>9.1</v>
       </c>
       <c r="S31" t="n">
-        <v>46.6</v>
+        <v>2.8</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 187 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Calle 4A</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4474,10 +4464,10 @@
         </is>
       </c>
       <c r="AC31" t="n">
-        <v>3.956111</v>
+        <v>3.893611111</v>
       </c>
       <c r="AD31" t="n">
-        <v>-76.30028</v>
+        <v>-76.29111</v>
       </c>
     </row>
     <row r="32">
@@ -4512,17 +4502,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>GUADALAJARA</t>
+          <t>MANUEL ANTONIO SANCLEMENTE - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA GRAN COLOMBIA</t>
+          <t>INSTITUCION EDUCATIVA MANUEL ANTONIO SANCLEMENTE</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>176111000604</t>
+          <t>176111000515</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4537,12 +4527,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>CR 27 NO 14-23</t>
+          <t>CL 4 A 1 E 26</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Andalucia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -4551,30 +4541,30 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>16.89</v>
+        <v>0.54</v>
       </c>
       <c r="Q32" t="n">
-        <v>8.17</v>
+        <v>4.14</v>
       </c>
       <c r="R32" t="n">
-        <v>66.8</v>
+        <v>9.1</v>
       </c>
       <c r="S32" t="n">
-        <v>46.6</v>
+        <v>2.8</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4584,12 +4574,12 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 22 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 30 m de esa vía.</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Carrera 27</t>
+          <t>Calle 4</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4598,10 +4588,10 @@
         </is>
       </c>
       <c r="AC32" t="n">
-        <v>3.911822</v>
+        <v>3.89307</v>
       </c>
       <c r="AD32" t="n">
-        <v>-76.30735</v>
+        <v>-76.29131</v>
       </c>
     </row>
     <row r="33">
@@ -4636,17 +4626,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>INSTITUTO TECNICO AGRICOLA-SEDE PRINCIPAL</t>
+          <t>GUADALAJARA</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA AGRICOLA DE GUADALAJARA DE BUGA</t>
+          <t>INSTITUCION EDUCATIVA GRAN COLOMBIA</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>176111000507</t>
+          <t>176111000604</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4661,7 +4651,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>CL 23 KR 9 A</t>
+          <t>CR 27 NO 14-23</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4671,29 +4661,29 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Andalucia</t>
+          <t>Caicedonia</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>7.33</v>
+        <v>7.65</v>
       </c>
       <c r="Q33" t="n">
-        <v>35.55</v>
+        <v>34.79</v>
       </c>
       <c r="R33" t="n">
-        <v>45.9</v>
+        <v>111.8</v>
       </c>
       <c r="S33" t="n">
-        <v>38.3</v>
+        <v>102.8</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -4708,7 +4698,12 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 32 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 22 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Carrera 27</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4717,10 +4712,10 @@
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>3.914166667</v>
+        <v>3.911822</v>
       </c>
       <c r="AD33" t="n">
-        <v>-76.2925</v>
+        <v>-76.30735</v>
       </c>
     </row>
     <row r="34">
@@ -4790,20 +4785,20 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Andalucia</t>
+          <t>Caicedonia</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>35.55</v>
+        <v>34.79</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.99</v>
+        <v>69.31</v>
       </c>
       <c r="R34" t="n">
-        <v>45.9</v>
+        <v>111.8</v>
       </c>
       <c r="S34" t="n">
-        <v>38.3</v>
+        <v>102.8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4889,22 +4884,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE CHIQUINQUIRA</t>
+          <t>BOLIVARIANO</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DE CHIQUINQUIRA</t>
+          <t>INSTITUCION EDUCATIVA BOLIVARIANO</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>176622000076</t>
+          <t>176122000380</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>ROLDANILLO</t>
+          <t>CAICEDONIA</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4914,34 +4909,34 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>CL 4 5 38</t>
+          <t>CL 5 11 15</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
+          <t>Caicedonia</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Tulua</t>
-        </is>
-      </c>
       <c r="P35" t="n">
-        <v>48.65</v>
+        <v>1.47</v>
       </c>
       <c r="Q35" t="n">
-        <v>14.74</v>
+        <v>59.43</v>
       </c>
       <c r="R35" t="n">
-        <v>114.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S35" t="n">
-        <v>93.2</v>
+        <v>79.7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Uso restringido</t>
+          <t>Peligro de colapso</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4951,12 +4946,12 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -4971,12 +4966,12 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Carrera 5</t>
+          <t>Calle 5</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -4985,10 +4980,10 @@
         </is>
       </c>
       <c r="AC35" t="n">
-        <v>4.412260842287796</v>
+        <v>4.329633623</v>
       </c>
       <c r="AD35" t="n">
-        <v>-76.15737540436542</v>
+        <v>-75.82531724</v>
       </c>
     </row>
     <row r="36">
@@ -5023,22 +5018,22 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MANUEL DOLORES MONDRAGON</t>
+          <t>SANTA CECILIA</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MANUEL DOLORES MONDRAGON</t>
+          <t>INSTITUCION EDUCATIVA EFRAIN VARELA VACA</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>176100000254</t>
+          <t>176895000231</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>BOLIVAR</t>
+          <t>ZARZAL</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -5048,34 +5043,34 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>KR 2 2 66</t>
+          <t>CL 10 KR 10 EQ</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
+          <t>Caicedonia</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Tulua</t>
-        </is>
-      </c>
       <c r="P36" t="n">
-        <v>14.74</v>
+        <v>59.43</v>
       </c>
       <c r="Q36" t="n">
-        <v>50.86</v>
+        <v>31.96</v>
       </c>
       <c r="R36" t="n">
-        <v>114.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S36" t="n">
-        <v>93.2</v>
+        <v>79.7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>Uso restringido</t>
+          <t>Peligro de colapso</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5085,17 +5080,17 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -5105,12 +5100,12 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 43 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>BOLIVAR CRUCE CON VIA DE INVIAS 2302 EN TRAMO 23020 INICIO A 52m DE INICIO DE VIA 10023VL02B</t>
+          <t>Carrera 10</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5119,10 +5114,10 @@
         </is>
       </c>
       <c r="AC36" t="n">
-        <v>4.340805</v>
+        <v>4.3959229</v>
       </c>
       <c r="AD36" t="n">
-        <v>-76.17979800000001</v>
+        <v>-76.0708454</v>
       </c>
     </row>
     <row r="37">
@@ -5152,27 +5147,27 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SEDE PRINCIPAL LICEO MODERNO</t>
+          <t>NUESTRA SEÑORA DE CHIQUINQUIRA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
+          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DE CHIQUINQUIRA</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>176834000106</t>
+          <t>176622000076</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>ROLDANILLO</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -5182,44 +5177,54 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>IND CALLE 27 NO. 6AW 240</t>
+          <t>CL 4 5 38</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
+          <t>Andalucia</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Tulua</t>
-        </is>
-      </c>
       <c r="P37" t="n">
-        <v>7.41</v>
+        <v>48.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>42.09</v>
+        <v>14.74</v>
       </c>
       <c r="R37" t="n">
-        <v>100.2</v>
+        <v>114.3</v>
       </c>
       <c r="S37" t="n">
-        <v>57</v>
+        <v>93.2</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uso restringido</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -5229,12 +5234,12 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 12 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Calle 27</t>
+          <t>Carrera 5</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5243,10 +5248,10 @@
         </is>
       </c>
       <c r="AC37" t="n">
-        <v>4.088515899</v>
+        <v>4.412260842287796</v>
       </c>
       <c r="AD37" t="n">
-        <v>-76.22009</v>
+        <v>-76.15737540436542</v>
       </c>
     </row>
     <row r="38">
@@ -5281,74 +5286,74 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>JOSE MARIA CORDOBA</t>
+          <t>MANUEL DOLORES MONDRAGON</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA HERNANDO LLORENTE ARROYO</t>
+          <t>INSTITUCION EDUCATIVA MANUEL DOLORES MONDRAGON</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>276616000212</t>
+          <t>176100000254</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>RIOFRIO</t>
+          <t>BOLIVAR</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>CORREG SALONICA</t>
+          <t>KR 2 2 66</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
+          <t>Andalucia</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Tulua</t>
-        </is>
-      </c>
       <c r="P38" t="n">
-        <v>42.09</v>
+        <v>14.74</v>
       </c>
       <c r="Q38" t="n">
-        <v>50.65</v>
+        <v>50.86</v>
       </c>
       <c r="R38" t="n">
-        <v>100.2</v>
+        <v>114.3</v>
       </c>
       <c r="S38" t="n">
-        <v>57</v>
+        <v>93.2</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Peligro de colapso</t>
+          <t>Uso restringido</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>en revisión de la mesa</t>
+          <t>aprobado por la mesa</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -5363,12 +5368,12 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 43 m de esa vía.</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>SALONICA CRUCE CON VIA 23VL13-1 EN K44+300</t>
+          <t>BOLIVAR CRUCE CON VIA DE INVIAS 2302 EN TRAMO 23020 INICIO A 52m DE INICIO DE VIA 10023VL02B</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5377,10 +5382,10 @@
         </is>
       </c>
       <c r="AC38" t="n">
-        <v>4.1258314</v>
+        <v>4.340805</v>
       </c>
       <c r="AD38" t="n">
-        <v>-76.3722336</v>
+        <v>-76.17979800000001</v>
       </c>
     </row>
     <row r="39">
@@ -5410,27 +5415,27 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>INTEGRADA DE TRUJILLO</t>
+          <t>SEDE PRINCIPAL LICEO MODERNO</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA INTEGRADA DE TRUJILLO</t>
+          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>176828000021</t>
+          <t>176834000106</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -5440,7 +5445,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>KR 18 15 40</t>
+          <t>IND CALLE 27 NO. 6AW 240</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5454,40 +5459,30 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>46.98</v>
+        <v>7.41</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.67</v>
+        <v>42.09</v>
       </c>
       <c r="R39" t="n">
-        <v>91.90000000000001</v>
+        <v>100.2</v>
       </c>
       <c r="S39" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>57</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5497,12 +5492,12 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 33 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Carrera 18</t>
+          <t>Calle 27</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5511,10 +5506,10 @@
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>4.208406</v>
+        <v>4.088515899</v>
       </c>
       <c r="AD39" t="n">
-        <v>-76.31959500000001</v>
+        <v>-76.22009</v>
       </c>
     </row>
     <row r="40">
@@ -5549,32 +5544,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>JOSE MARIA CORDOBA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA INTEGRADA DE TRUJILLO</t>
+          <t>INSTITUCION EDUCATIVA HERNANDO LLORENTE ARROYO</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>176828000064</t>
+          <t>276616000212</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>RIOFRIO</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>KR 18 15 27</t>
+          <t>CORREG SALONICA</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5588,20 +5583,30 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.67</v>
+        <v>42.09</v>
       </c>
       <c r="Q40" t="n">
-        <v>44.3</v>
+        <v>50.65</v>
       </c>
       <c r="R40" t="n">
-        <v>91.90000000000001</v>
+        <v>100.2</v>
       </c>
       <c r="S40" t="n">
-        <v>48.5</v>
+        <v>57</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Peligro de colapso</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>en revisión de la mesa</t>
+        </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5626,7 +5631,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Carrera 18</t>
+          <t>SALONICA CRUCE CON VIA 23VL13-1 EN K44+300</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5635,10 +5640,10 @@
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>4.210077</v>
+        <v>4.1258314</v>
       </c>
       <c r="AD40" t="n">
-        <v>-76.319047</v>
+        <v>-76.3722336</v>
       </c>
     </row>
     <row r="41">
@@ -5673,17 +5678,17 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SAN ISIDRO</t>
+          <t>INTEGRADA DE TRUJILLO</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAN ISIDRO</t>
+          <t>INSTITUCION EDUCATIVA INTEGRADA DE TRUJILLO</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>276828000174</t>
+          <t>176828000021</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5693,12 +5698,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>CORREGIMIENTO EL TABOR PUENTE BLANCO</t>
+          <t>KR 18 15 40</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5712,20 +5717,20 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>77.20999999999999</v>
+        <v>46.98</v>
       </c>
       <c r="Q41" t="n">
-        <v>69.08</v>
+        <v>0.67</v>
       </c>
       <c r="R41" t="n">
-        <v>146.3</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="S41" t="n">
-        <v>74.2</v>
+        <v>48.5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Habitable</t>
+          <t>No habitable</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5745,7 +5750,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -5755,12 +5760,12 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>TRUJILLO - LA SONORA CRUCE VIA 23VL13-1 K64+160</t>
+          <t>Carrera 18</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5769,10 +5774,10 @@
         </is>
       </c>
       <c r="AC41" t="n">
-        <v>4.210564</v>
+        <v>4.208406</v>
       </c>
       <c r="AD41" t="n">
-        <v>-76.38158300000001</v>
+        <v>-76.31959500000001</v>
       </c>
     </row>
     <row r="42">
@@ -5787,42 +5792,42 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SEDE INSTITUTO CAMPESTRE SANTA CECILIA</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
+          <t>INSTITUCION EDUCATIVA INTEGRADA DE TRUJILLO</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>176834000599</t>
+          <t>176828000064</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -5832,7 +5837,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>IND CALLE 27 NO 6AW 240</t>
+          <t>KR 18 15 27</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5842,44 +5847,49 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Yotoco</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>9.890000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="Q42" t="n">
-        <v>32.44</v>
+        <v>44.3</v>
       </c>
       <c r="R42" t="n">
-        <v>82.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="S42" t="n">
-        <v>59.6</v>
+        <v>48.5</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 50 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Carrera 18</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -5888,10 +5898,10 @@
         </is>
       </c>
       <c r="AC42" t="n">
-        <v>4.090555556</v>
+        <v>4.210077</v>
       </c>
       <c r="AD42" t="n">
-        <v>-76.22221999999999</v>
+        <v>-76.319047</v>
       </c>
     </row>
     <row r="43">
@@ -5917,7 +5927,7 @@
         <v>13</v>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5926,22 +5936,22 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ALFREDO GARRIDO TOVAR</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ALFREDO GARRIDO TOVAR</t>
+          <t>INSTITUCION EDUCATIVA SAN ISIDRO</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>276616000654</t>
+          <t>276828000174</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>RIOFRIO</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -5951,7 +5961,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>CORREG PORTUGAL DE PIEDRAS</t>
+          <t>CORREGIMIENTO EL TABOR PUENTE BLANCO</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5961,24 +5971,24 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Yotoco</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>32.44</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="Q43" t="n">
-        <v>40.13</v>
+        <v>69.08</v>
       </c>
       <c r="R43" t="n">
-        <v>82.5</v>
+        <v>146.3</v>
       </c>
       <c r="S43" t="n">
-        <v>59.6</v>
+        <v>74.2</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>No habitable</t>
+          <t>Habitable</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5988,32 +5998,32 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>PORTUGAL DE PIEDRAS - CRUCE VIA 23VL13</t>
+          <t>TRUJILLO - LA SONORA CRUCE VIA 23VL13-1 K64+160</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -6022,10 +6032,10 @@
         </is>
       </c>
       <c r="AC43" t="n">
-        <v>4.0553</v>
+        <v>4.210564</v>
       </c>
       <c r="AD43" t="n">
-        <v>-76.35465000000001</v>
+        <v>-76.38158300000001</v>
       </c>
     </row>
     <row r="44">
@@ -6055,27 +6065,27 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>ALFONSO ZAWADZKY</t>
+          <t>SEDE INSTITUTO CAMPESTRE SANTA CECILIA</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ALFONSO ZAWADZKY</t>
+          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>176890000305</t>
+          <t>176834000599</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>YOTOCO</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -6085,12 +6095,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>KR 5 5 79</t>
+          <t>IND CALLE 27 NO 6AW 240</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Yotoco</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -6099,40 +6109,30 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.76</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="Q44" t="n">
-        <v>23.14</v>
+        <v>32.44</v>
       </c>
       <c r="R44" t="n">
-        <v>25.1</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="S44" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>62</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -6142,12 +6142,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 15 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>Calle 6</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 50 m de esa vía.</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -6156,10 +6151,10 @@
         </is>
       </c>
       <c r="AC44" t="n">
-        <v>3.86056963997</v>
+        <v>4.090555556</v>
       </c>
       <c r="AD44" t="n">
-        <v>-76.38430955440001</v>
+        <v>-76.22221999999999</v>
       </c>
     </row>
     <row r="45">
@@ -6189,89 +6184,99 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>BID (43)</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ALFREDO GARRIDO TOVAR</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA ALFREDO GARRIDO TOVAR</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>276616000654</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>RIOFRIO</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>CORREG PORTUGAL DE PIEDRAS</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tulua</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>EL PLACER - SEDE PRINCIPAL</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA EL PLACER</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>276111000102</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Buga</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>CORREG EL PLACER</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Yotoco</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Buga</t>
-        </is>
-      </c>
       <c r="P45" t="n">
-        <v>23.14</v>
+        <v>32.44</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.2</v>
+        <v>47.02</v>
       </c>
       <c r="R45" t="n">
-        <v>25.1</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="S45" t="n">
-        <v>13.6</v>
+        <v>62</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>No habitable</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 30 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Calle 6</t>
+          <t>PORTUGAL DE PIEDRAS - CRUCE VIA 23VL13</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6280,10 +6285,10 @@
         </is>
       </c>
       <c r="AC45" t="n">
-        <v>3.898611</v>
+        <v>4.0553</v>
       </c>
       <c r="AD45" t="n">
-        <v>-76.30056</v>
+        <v>-76.35465000000001</v>
       </c>
     </row>
     <row r="46">
@@ -6318,17 +6323,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>ACADEMICO - SEDE PRINCIPAL</t>
+          <t>TULIO ENRIQUE TASCON CHAMBIMBAL - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ACADEMICO</t>
+          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON CHAMBIMBAL</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>176111001104</t>
+          <t>276111000781</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6338,12 +6343,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>KR 9 A 2 55 SUR</t>
+          <t>CHAMBIMBAL</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6357,16 +6362,16 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.44</v>
+        <v>24.58</v>
       </c>
       <c r="Q46" t="n">
-        <v>13.01</v>
+        <v>24.3</v>
       </c>
       <c r="R46" t="n">
-        <v>84.3</v>
+        <v>116.8</v>
       </c>
       <c r="S46" t="n">
-        <v>69.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -6380,22 +6385,17 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 25 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>Carrera 9</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 187 m de esa vía.</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6404,10 +6404,10 @@
         </is>
       </c>
       <c r="AC46" t="n">
-        <v>3.892781656</v>
+        <v>3.956111</v>
       </c>
       <c r="AD46" t="n">
-        <v>-76.29845</v>
+        <v>-76.30028</v>
       </c>
     </row>
     <row r="47">
@@ -6481,16 +6481,16 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>13.01</v>
+        <v>24.3</v>
       </c>
       <c r="Q47" t="n">
         <v>67.88</v>
       </c>
       <c r="R47" t="n">
-        <v>84.3</v>
+        <v>116.8</v>
       </c>
       <c r="S47" t="n">
-        <v>69.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -12183,10 +12183,10 @@
         <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>20.1</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>822</v>
+        <v>747</v>
       </c>
       <c r="F11" t="n">
         <v>14</v>

--- a/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
+++ b/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
@@ -2324,22 +2324,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA CONSOLACION</t>
+          <t>POLICARPA SALAVARRIETA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA JORGE ELICER GAITAN</t>
+          <t>INSTITUCION EDUCATIVA ALFONSO ZAWADZKY</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>176606000139</t>
+          <t>176890000020</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>RESTREPO</t>
+          <t>YOTOCO</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>KR 9 13 08</t>
+          <t>KR 6 6 67</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2363,20 +2363,20 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>43.11</v>
+        <v>0.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>43.4</v>
+        <v>0.37</v>
       </c>
       <c r="R15" t="n">
-        <v>86.59999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="S15" t="n">
-        <v>62.3</v>
+        <v>0.8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Uso restringido</t>
+          <t>Peligro de colapso</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2386,17 +2386,17 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 31 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Carrera 9</t>
+          <t>Carrera 6</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="AC15" t="n">
-        <v>3.82299113556</v>
+        <v>3.85991597259148</v>
       </c>
       <c r="AD15" t="n">
-        <v>-76.52146344489999</v>
+        <v>-76.38388046730552</v>
       </c>
     </row>
     <row r="16">
@@ -2438,18 +2438,18 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>VEINTE DE JULIO</t>
+          <t>ALFONSO ZAWADZKY</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA JORGE ROBLEDO</t>
+          <t>INSTITUCION EDUCATIVA ALFONSO ZAWADZKY</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>276869000171</t>
+          <t>176890000305</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>VIJES</t>
+          <t>YOTOCO</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>CORREGIMIENTO VILLAMARIA</t>
+          <t>KR 5 5 79</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2497,20 +2497,20 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>40.51</v>
+        <v>0.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>15.26</v>
+        <v>1.99</v>
       </c>
       <c r="R16" t="n">
-        <v>85.2</v>
+        <v>3.1</v>
       </c>
       <c r="S16" t="n">
-        <v>62.8</v>
+        <v>0.8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Habitable</t>
+          <t>No habitable</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2520,27 +2520,32 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Bajo</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 26 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 15 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Calle 6</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2549,10 +2554,10 @@
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>3.716456</v>
+        <v>3.86056963997</v>
       </c>
       <c r="AD16" t="n">
-        <v>-76.47793299999999</v>
+        <v>-76.38430955440001</v>
       </c>
     </row>
     <row r="17">
@@ -2578,7 +2583,7 @@
         <v>13</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2587,32 +2592,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>POLICARPA SALAVARRIETA</t>
+          <t>SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA JORGE ROBLEDO</t>
+          <t>INSTITUCION EDUCATIVA SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>176869000061</t>
+          <t>276890000237</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>VIJES</t>
+          <t>YOTOCO</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>KR 4 5 34</t>
+          <t>VEREDA SAN JUAN</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2626,20 +2631,20 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.26</v>
+        <v>59.23</v>
       </c>
       <c r="Q17" t="n">
-        <v>29.46</v>
+        <v>63.8</v>
       </c>
       <c r="R17" t="n">
-        <v>85.2</v>
+        <v>123</v>
       </c>
       <c r="S17" t="n">
-        <v>62.8</v>
+        <v>46.8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Uso restringido</t>
+          <t>No habitable</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2649,32 +2654,32 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 3 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 23 m de esa vía.</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Carrera 4</t>
+          <t>MEDIACANOA - MIRAVALLE - CAMPO ALEGRE - CRUCE VIA 2302</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2683,10 +2688,10 @@
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>3.699871998710244</v>
+        <v>3.962278</v>
       </c>
       <c r="AD17" t="n">
-        <v>-76.44279828333418</v>
+        <v>-76.40526699999999</v>
       </c>
     </row>
     <row r="18">
@@ -2721,22 +2726,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MANUELA BELTRAN</t>
+          <t>ANTONIA SANTOS</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA JORGE ROBLEDO</t>
+          <t>INSTITUCION EDUCATIVA ALFONSO ZAWADZKY</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>276869000154</t>
+          <t>276890000253</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>VIJES</t>
+          <t>YOTOCO</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2746,7 +2751,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>VEREDA CAIMITAL</t>
+          <t>CORREGIMIENTO  MEDIA CANOA</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2760,20 +2765,20 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>59.58</v>
+        <v>9.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>63.82</v>
+        <v>40.8</v>
       </c>
       <c r="R18" t="n">
-        <v>123.4</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>81.2</v>
+        <v>62.9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Habitable</t>
+          <t>Peligro de colapso</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2793,22 +2798,22 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 32 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 24 m de esa vía.</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>EL TAMBOR - LA RIVERA - OCACHE</t>
+          <t>MEDIACANOA - PRIMAVERA</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2817,10 +2822,10 @@
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>3.741864</v>
+        <v>3.900556391368746</v>
       </c>
       <c r="AD18" t="n">
-        <v>-76.49940700000001</v>
+        <v>-76.37662112784321</v>
       </c>
     </row>
     <row r="19">
@@ -2839,14 +2844,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2855,32 +2860,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>RAFAEL NUÑEZ</t>
+          <t>NUESTRA SEÑORA DE LA CONSOLACION</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MARÍA AUXILIADORA</t>
+          <t>INSTITUCION EDUCATIVA JORGE ELICER GAITAN</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>276377000035</t>
+          <t>176606000139</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LA_CUMBRE</t>
+          <t>RESTREPO</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>CORREG LA MARIA</t>
+          <t>KR 9 13 08</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2890,24 +2895,24 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Yotoco</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>140.39</v>
+        <v>40.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>102.33</v>
+        <v>43.4</v>
       </c>
       <c r="R19" t="n">
-        <v>242.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>126.3</v>
+        <v>62.9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Peligro de colapso</t>
+          <t>Uso restringido</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2927,22 +2932,22 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 2 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 31 m de esa vía.</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>LA GUAIRA - KM113- LOMITAS</t>
+          <t>Carrera 9</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2951,16 +2956,16 @@
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>3.6919524</v>
+        <v>3.82299113556</v>
       </c>
       <c r="AD19" t="n">
-        <v>-76.63414659999999</v>
+        <v>-76.52146344489999</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2969,42 +2974,42 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ANTONIO GUENDICA</t>
+          <t>RAFAEL NUÑEZ</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ANGEL CUADROS</t>
+          <t>INSTITUCION EDUCATIVA MARÍA AUXILIADORA</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>276111000811</t>
+          <t>276377000035</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>LA_CUMBRE</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -3014,59 +3019,69 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>QUEBRADASECA</t>
+          <t>CORREG LA MARIA</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
+          <t>Yotoco</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Yotoco</t>
-        </is>
-      </c>
       <c r="P20" t="n">
-        <v>63.71</v>
+        <v>140.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>18.31</v>
+        <v>102.33</v>
       </c>
       <c r="R20" t="n">
-        <v>93.5</v>
+        <v>242.7</v>
       </c>
       <c r="S20" t="n">
-        <v>80</v>
+        <v>126.3</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Peligro de colapso</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «trunk»). La sede queda a 37 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Troncal de Occidente</t>
+          <t>LA GUAIRA - KM113- LOMITAS</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3075,10 +3090,10 @@
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>3.850833</v>
+        <v>3.6919524</v>
       </c>
       <c r="AD20" t="n">
-        <v>-76.29722</v>
+        <v>-76.63414659999999</v>
       </c>
     </row>
     <row r="21">
@@ -3104,7 +3119,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3113,22 +3128,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ANTONIA SANTOS</t>
+          <t>MANUELA BELTRAN</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ALFONSO ZAWADZKY</t>
+          <t>INSTITUCION EDUCATIVA JORGE ROBLEDO</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>276890000253</t>
+          <t>276869000154</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>YOTOCO</t>
+          <t>VIJES</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3138,7 +3153,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>CORREGIMIENTO  MEDIA CANOA</t>
+          <t>VEREDA CAIMITAL</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3152,20 +3167,20 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>18.31</v>
+        <v>91.59</v>
       </c>
       <c r="Q21" t="n">
-        <v>11.47</v>
+        <v>63.82</v>
       </c>
       <c r="R21" t="n">
-        <v>93.5</v>
+        <v>155.4</v>
       </c>
       <c r="S21" t="n">
-        <v>80</v>
+        <v>91.8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Peligro de colapso</t>
+          <t>Habitable</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3185,22 +3200,22 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 24 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 32 m de esa vía.</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>MEDIACANOA - PRIMAVERA</t>
+          <t>EL TAMBOR - LA RIVERA - OCACHE</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3209,10 +3224,10 @@
         </is>
       </c>
       <c r="AC21" t="n">
-        <v>3.900556391368746</v>
+        <v>3.741864</v>
       </c>
       <c r="AD21" t="n">
-        <v>-76.37662112784321</v>
+        <v>-76.49940700000001</v>
       </c>
     </row>
     <row r="22">
@@ -3247,32 +3262,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>POLICARPA SALAVARRIETA</t>
+          <t>ALFREDO GARRIDO TOVAR</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ALFONSO ZAWADZKY</t>
+          <t>INSTITUCION EDUCATIVA ALFREDO GARRIDO TOVAR</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>176890000020</t>
+          <t>276616000654</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>YOTOCO</t>
+          <t>RIOFRIO</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>KR 6 6 67</t>
+          <t>CORREG PORTUGAL DE PIEDRAS</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3282,24 +3297,24 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Yotoco</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.73</v>
+        <v>38.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.37</v>
+        <v>31.2</v>
       </c>
       <c r="R22" t="n">
-        <v>3.1</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8</v>
+        <v>58.5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Peligro de colapso</t>
+          <t>No habitable</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3309,32 +3324,32 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Carrera 6</t>
+          <t>PORTUGAL DE PIEDRAS - CRUCE VIA 23VL13</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3343,10 +3358,10 @@
         </is>
       </c>
       <c r="AC22" t="n">
-        <v>3.85991597259148</v>
+        <v>4.0553</v>
       </c>
       <c r="AD22" t="n">
-        <v>-76.38388046730552</v>
+        <v>-76.35465000000001</v>
       </c>
     </row>
     <row r="23">
@@ -3376,27 +3391,27 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>ALFONSO ZAWADZKY</t>
+          <t>SEDE PRINCIPAL LICEO MODERNO</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ALFONSO ZAWADZKY</t>
+          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>176890000305</t>
+          <t>176834000106</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>YOTOCO</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3406,7 +3421,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>KR 5 5 79</t>
+          <t>IND CALLE 27 NO. 6AW 240</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3416,34 +3431,24 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Yotoco</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.37</v>
+        <v>31.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.99</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R23" t="n">
-        <v>3.1</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>58.5</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3453,22 +3458,22 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 15 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Calle 6</t>
+          <t>Calle 27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3477,10 +3482,10 @@
         </is>
       </c>
       <c r="AC23" t="n">
-        <v>3.86056963997</v>
+        <v>4.088515899</v>
       </c>
       <c r="AD23" t="n">
-        <v>-76.38430955440001</v>
+        <v>-76.22009</v>
       </c>
     </row>
     <row r="24">
@@ -3510,79 +3515,69 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SAN JUAN BOSCO</t>
+          <t>SEDE INSTITUTO CAMPESTRE SANTA CECILIA</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAN JUAN BOSCO</t>
+          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>276890000237</t>
+          <t>176834000599</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>YOTOCO</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>VEREDA SAN JUAN</t>
+          <t>IND CALLE 27 NO 6AW 240</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Yotoco</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>59.23</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>75.05</v>
+        <v>43.42</v>
       </c>
       <c r="R24" t="n">
-        <v>134.3</v>
+        <v>104</v>
       </c>
       <c r="S24" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>57.8</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -3597,12 +3592,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 23 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>MEDIACANOA - MIRAVALLE - CAMPO ALEGRE - CRUCE VIA 2302</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 50 m de esa vía.</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3611,10 +3601,10 @@
         </is>
       </c>
       <c r="AC24" t="n">
-        <v>3.962278</v>
+        <v>4.090555556</v>
       </c>
       <c r="AD24" t="n">
-        <v>-76.40526699999999</v>
+        <v>-76.22221999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3633,71 +3623,81 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ESC JOAQUIN CAMILO TORRES</t>
+          <t>JOSE MARIA CORDOBA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON</t>
+          <t>INSTITUCION EDUCATIVA HERNANDO LLORENTE ARROYO</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>176111001171</t>
+          <t>276616000212</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>RIOFRIO</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>CL 15 9 45</t>
+          <t>CORREG SALONICA</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.08</v>
+        <v>43.42</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.46</v>
+        <v>50.65</v>
       </c>
       <c r="R25" t="n">
-        <v>9.699999999999999</v>
+        <v>104</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9</v>
+        <v>57.8</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Peligro de colapso</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>en revisión de la mesa</t>
+        </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -3721,7 +3721,12 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 12 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>SALONICA CRUCE CON VIA 23VL13-1 EN K44+300</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3730,10 +3735,10 @@
         </is>
       </c>
       <c r="AC25" t="n">
-        <v>3.9055</v>
+        <v>4.1258314</v>
       </c>
       <c r="AD25" t="n">
-        <v>-76.29489</v>
+        <v>-76.3722336</v>
       </c>
     </row>
     <row r="26">
@@ -3759,64 +3764,74 @@
         <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>EL PLACER - SEDE PRINCIPAL</t>
+          <t>INTEGRADA DE TRUJILLO</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EL PLACER</t>
+          <t>INSTITUCION EDUCATIVA INTEGRADA DE TRUJILLO</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>276111000102</t>
+          <t>176828000021</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>CORREG EL PLACER</t>
+          <t>KR 18 15 40</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4.46</v>
+        <v>46.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.2</v>
+        <v>0.67</v>
       </c>
       <c r="R26" t="n">
-        <v>9.699999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>2.9</v>
+        <v>48.5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>No habitable</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -3840,12 +3855,12 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 30 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Calle 6</t>
+          <t>Carrera 18</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3854,10 +3869,10 @@
         </is>
       </c>
       <c r="AC26" t="n">
-        <v>3.898611</v>
+        <v>4.208406</v>
       </c>
       <c r="AD26" t="n">
-        <v>-76.30056</v>
+        <v>-76.31959500000001</v>
       </c>
     </row>
     <row r="27">
@@ -3876,38 +3891,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ACADEMICO - SEDE PRINCIPAL</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ACADEMICO</t>
+          <t>INSTITUCION EDUCATIVA INTEGRADA DE TRUJILLO</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>176111001104</t>
+          <t>176828000064</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3917,39 +3932,39 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>KR 9 A 2 55 SUR</t>
+          <t>KR 18 15 27</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.44</v>
+        <v>0.67</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.17</v>
+        <v>44.3</v>
       </c>
       <c r="R27" t="n">
-        <v>6.9</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>48.5</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3964,12 +3979,12 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 25 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Carrera 9</t>
+          <t>Carrera 18</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -3978,10 +3993,10 @@
         </is>
       </c>
       <c r="AC27" t="n">
-        <v>3.892781656</v>
+        <v>4.210077</v>
       </c>
       <c r="AD27" t="n">
-        <v>-76.29845</v>
+        <v>-76.319047</v>
       </c>
     </row>
     <row r="28">
@@ -4007,64 +4022,74 @@
         <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>NARCISO CABAL SALCEDO - SEDE PRINCIPAL</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA NARCISO CABAL SALCEDO</t>
+          <t>INSTITUCION EDUCATIVA SAN ISIDRO</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>176111000469</t>
+          <t>276828000174</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>CL 2 8 47</t>
+          <t>CORREGIMIENTO EL TABOR PUENTE BLANCO</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.17</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.28</v>
+        <v>69.08</v>
       </c>
       <c r="R28" t="n">
-        <v>6.9</v>
+        <v>146.3</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>74.2</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Habitable</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -4078,7 +4103,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4088,7 +4113,12 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 15 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>TRUJILLO - LA SONORA CRUCE VIA 23VL13-1 K64+160</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4097,10 +4127,10 @@
         </is>
       </c>
       <c r="AC28" t="n">
-        <v>3.894397016</v>
+        <v>4.210564</v>
       </c>
       <c r="AD28" t="n">
-        <v>-76.29777</v>
+        <v>-76.38158300000001</v>
       </c>
     </row>
     <row r="29">
@@ -4130,27 +4160,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ESC JORGE ELIECER GAITAN</t>
+          <t>MANUEL DOLORES MONDRAGON</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON</t>
+          <t>INSTITUCION EDUCATIVA MANUEL DOLORES MONDRAGON</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>176111001139</t>
+          <t>176100000254</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BOLIVAR</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -4160,39 +4190,49 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>CR 10 NO 18-81</t>
+          <t>KR 2 2 66</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Andalucia</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.97</v>
+        <v>57.35</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.43</v>
+        <v>14.61</v>
       </c>
       <c r="R29" t="n">
-        <v>16.9</v>
+        <v>115.4</v>
       </c>
       <c r="S29" t="n">
-        <v>4.5</v>
+        <v>93.2</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uso restringido</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -4207,12 +4247,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 29 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 43 m de esa vía.</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Carrera 10</t>
+          <t>BOLIVAR CRUCE CON VIA DE INVIAS 2302 EN TRAMO 23020 INICIO A 52m DE INICIO DE VIA 10023VL02B</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4221,10 +4261,10 @@
         </is>
       </c>
       <c r="AC29" t="n">
-        <v>3.90894</v>
+        <v>4.340805</v>
       </c>
       <c r="AD29" t="n">
-        <v>-76.29465</v>
+        <v>-76.17979800000001</v>
       </c>
     </row>
     <row r="30">
@@ -4254,27 +4294,27 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>INSTITUTO TECNICO AGRICOLA-SEDE PRINCIPAL</t>
+          <t>NUESTRA SEÑORA DE CHIQUINQUIRA</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA AGRICOLA DE GUADALAJARA DE BUGA</t>
+          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DE CHIQUINQUIRA</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>176111000507</t>
+          <t>176622000076</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>ROLDANILLO</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -4284,30 +4324,40 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>CL 23 KR 9 A</t>
+          <t>CL 4 5 38</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Andalucia</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.43</v>
+        <v>14.61</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.52</v>
+        <v>43.44</v>
       </c>
       <c r="R30" t="n">
-        <v>16.9</v>
+        <v>115.4</v>
       </c>
       <c r="S30" t="n">
-        <v>4.5</v>
+        <v>93.2</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uso restringido</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -4331,7 +4381,12 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 32 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Carrera 5</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4340,10 +4395,10 @@
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>3.914166667</v>
+        <v>4.412260842287796</v>
       </c>
       <c r="AD30" t="n">
-        <v>-76.2925</v>
+        <v>-76.15737540436542</v>
       </c>
     </row>
     <row r="31">
@@ -4373,27 +4428,27 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CRISTOBAL COLÓN</t>
+          <t>ELEAZAR LIBREROS SALAMANCA</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MANUEL ANTONIO SANCLEMENTE</t>
+          <t>INSTITUCION EDUCATIVA ELEAZAR LIBREROS SALAMANCA</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>276111001087</t>
+          <t>176036000024</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>ANDALUCIA</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4403,30 +4458,40 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>VDA GUADUALEJO</t>
+          <t>CL 6 4 15</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Andalucia</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Caicedonia</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.38</v>
+        <v>3.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.54</v>
+        <v>69.31</v>
       </c>
       <c r="R31" t="n">
-        <v>9.1</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="S31" t="n">
-        <v>2.8</v>
+        <v>64.59999999999999</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uso restringido</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -4450,12 +4515,12 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Calle 4A</t>
+          <t>Calle 6</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4464,10 +4529,10 @@
         </is>
       </c>
       <c r="AC31" t="n">
-        <v>3.893611111</v>
+        <v>4.165067</v>
       </c>
       <c r="AD31" t="n">
-        <v>-76.29111</v>
+        <v>-76.16943499999999</v>
       </c>
     </row>
     <row r="32">
@@ -4486,38 +4551,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MANUEL ANTONIO SANCLEMENTE - SEDE PRINCIPAL</t>
+          <t>BOLIVARIANO</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MANUEL ANTONIO SANCLEMENTE</t>
+          <t>INSTITUCION EDUCATIVA BOLIVARIANO</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>176111000515</t>
+          <t>176122000380</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>CAICEDONIA</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -4527,44 +4592,54 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>CL 4 A 1 E 26</t>
+          <t>CL 5 11 15</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Caicedonia</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Andalucia</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.54</v>
+        <v>1.47</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.14</v>
+        <v>59.43</v>
       </c>
       <c r="R32" t="n">
-        <v>9.1</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S32" t="n">
-        <v>2.8</v>
+        <v>79.7</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Peligro de colapso</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4574,12 +4649,12 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 30 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Calle 4</t>
+          <t>Calle 5</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4588,10 +4663,10 @@
         </is>
       </c>
       <c r="AC32" t="n">
-        <v>3.89307</v>
+        <v>4.329633623</v>
       </c>
       <c r="AD32" t="n">
-        <v>-76.29131</v>
+        <v>-75.82531724</v>
       </c>
     </row>
     <row r="33">
@@ -4617,31 +4692,31 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>GUADALAJARA</t>
+          <t>SANTA CECILIA</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA GRAN COLOMBIA</t>
+          <t>INSTITUCION EDUCATIVA EFRAIN VARELA VACA</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>176111000604</t>
+          <t>176895000231</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>ZARZAL</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -4651,30 +4726,40 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>CR 27 NO 14-23</t>
+          <t>CL 10 KR 10 EQ</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Caicedonia</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Caicedonia</t>
+          <t>Andalucia</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>7.65</v>
+        <v>59.43</v>
       </c>
       <c r="Q33" t="n">
-        <v>34.79</v>
+        <v>31.96</v>
       </c>
       <c r="R33" t="n">
-        <v>111.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S33" t="n">
-        <v>102.8</v>
+        <v>79.7</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Peligro de colapso</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -4688,7 +4773,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4698,12 +4783,12 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 22 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Carrera 27</t>
+          <t>Carrera 10</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4712,10 +4797,10 @@
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>3.911822</v>
+        <v>4.3959229</v>
       </c>
       <c r="AD33" t="n">
-        <v>-76.30735</v>
+        <v>-76.0708454</v>
       </c>
     </row>
     <row r="34">
@@ -4734,110 +4819,95 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ELEAZAR LIBREROS SALAMANCA</t>
+          <t>TULIO ENRIQUE TASCON CHAMBIMBAL - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ELEAZAR LIBREROS SALAMANCA</t>
+          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON CHAMBIMBAL</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>176036000024</t>
+          <t>276111000781</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>ANDALUCIA</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>CL 6 4 15</t>
+          <t>CHAMBIMBAL</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
+          <t>Andalucia</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Caicedonia</t>
-        </is>
-      </c>
       <c r="P34" t="n">
-        <v>34.79</v>
+        <v>41.77</v>
       </c>
       <c r="Q34" t="n">
-        <v>69.31</v>
+        <v>16.89</v>
       </c>
       <c r="R34" t="n">
-        <v>111.8</v>
+        <v>66.8</v>
       </c>
       <c r="S34" t="n">
-        <v>102.8</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Uso restringido</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>46.6</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Calle 6</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 187 m de esa vía.</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -4846,10 +4916,10 @@
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>4.165067</v>
+        <v>3.956111</v>
       </c>
       <c r="AD34" t="n">
-        <v>-76.16943499999999</v>
+        <v>-76.30028</v>
       </c>
     </row>
     <row r="35">
@@ -4875,31 +4945,31 @@
         <v>9</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>BOLIVARIANO</t>
+          <t>GUADALAJARA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA BOLIVARIANO</t>
+          <t>INSTITUCION EDUCATIVA GRAN COLOMBIA</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>176122000380</t>
+          <t>176111000604</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>CAICEDONIA</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4909,44 +4979,34 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>CL 5 11 15</t>
+          <t>CR 27 NO 14-23</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Caicedonia</t>
+          <t>Andalucia</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Andalucia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.47</v>
+        <v>16.89</v>
       </c>
       <c r="Q35" t="n">
-        <v>59.43</v>
+        <v>8.17</v>
       </c>
       <c r="R35" t="n">
-        <v>92.90000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="S35" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Peligro de colapso</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>46.6</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -4966,12 +5026,12 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Calle 5</t>
+          <t>Carrera 27</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -4980,10 +5040,10 @@
         </is>
       </c>
       <c r="AC35" t="n">
-        <v>4.329633623</v>
+        <v>3.911822</v>
       </c>
       <c r="AD35" t="n">
-        <v>-75.82531724</v>
+        <v>-76.30735</v>
       </c>
     </row>
     <row r="36">
@@ -5002,38 +5062,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SANTA CECILIA</t>
+          <t>ESC JOAQUIN CAMILO TORRES</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EFRAIN VARELA VACA</t>
+          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>176895000231</t>
+          <t>176111001171</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>ZARZAL</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -5043,40 +5103,30 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>CL 10 KR 10 EQ</t>
+          <t>CL 15 9 45</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Caicedonia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Andalucia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>59.43</v>
+        <v>4.08</v>
       </c>
       <c r="Q36" t="n">
-        <v>31.96</v>
+        <v>4.46</v>
       </c>
       <c r="R36" t="n">
-        <v>92.90000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S36" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Peligro de colapso</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>2.9</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -5090,7 +5140,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -5100,12 +5150,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 18 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Carrera 10</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5114,10 +5159,10 @@
         </is>
       </c>
       <c r="AC36" t="n">
-        <v>4.3959229</v>
+        <v>3.9055</v>
       </c>
       <c r="AD36" t="n">
-        <v>-76.0708454</v>
+        <v>-76.29489</v>
       </c>
     </row>
     <row r="37">
@@ -5143,74 +5188,64 @@
         <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE CHIQUINQUIRA</t>
+          <t>EL PLACER - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DE CHIQUINQUIRA</t>
+          <t>INSTITUCION EDUCATIVA EL PLACER</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>176622000076</t>
+          <t>276111000102</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>ROLDANILLO</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>CL 4 5 38</t>
+          <t>CORREG EL PLACER</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Andalucia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>48.65</v>
+        <v>4.46</v>
       </c>
       <c r="Q37" t="n">
-        <v>14.74</v>
+        <v>1.2</v>
       </c>
       <c r="R37" t="n">
-        <v>114.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S37" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Uso restringido</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>2.9</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -5234,12 +5269,12 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 30 m de esa vía.</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Carrera 5</t>
+          <t>Calle 6</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5248,10 +5283,10 @@
         </is>
       </c>
       <c r="AC37" t="n">
-        <v>4.412260842287796</v>
+        <v>3.898611</v>
       </c>
       <c r="AD37" t="n">
-        <v>-76.15737540436542</v>
+        <v>-76.30056</v>
       </c>
     </row>
     <row r="38">
@@ -5270,82 +5305,72 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Buga</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ACADEMICO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA ACADEMICO</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>176111001104</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Buga</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>KR 9 A 2 55 SUR</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Buga</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Buga</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="S38" t="n">
         <v>2</v>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>BID (43)</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>MANUEL DOLORES MONDRAGON</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA MANUEL DOLORES MONDRAGON</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>176100000254</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>BOLIVAR</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>KR 2 2 66</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Andalucia</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Tulua</t>
-        </is>
-      </c>
-      <c r="P38" t="n">
-        <v>14.74</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>50.86</v>
-      </c>
-      <c r="R38" t="n">
-        <v>114.3</v>
-      </c>
-      <c r="S38" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Uso restringido</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
-      </c>
       <c r="V38" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
@@ -5368,12 +5393,12 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 43 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 25 m de esa vía.</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>BOLIVAR CRUCE CON VIA DE INVIAS 2302 EN TRAMO 23020 INICIO A 52m DE INICIO DE VIA 10023VL02B</t>
+          <t>Carrera 9</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5382,10 +5407,10 @@
         </is>
       </c>
       <c r="AC38" t="n">
-        <v>4.340805</v>
+        <v>3.892781656</v>
       </c>
       <c r="AD38" t="n">
-        <v>-76.17979800000001</v>
+        <v>-76.29845</v>
       </c>
     </row>
     <row r="39">
@@ -5411,31 +5436,31 @@
         <v>11</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SEDE PRINCIPAL LICEO MODERNO</t>
+          <t>NARCISO CABAL SALCEDO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
+          <t>INSTITUCION EDUCATIVA NARCISO CABAL SALCEDO</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>176834000106</t>
+          <t>176111000469</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -5445,44 +5470,44 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>IND CALLE 27 NO. 6AW 240</t>
+          <t>CL 2 8 47</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>7.41</v>
+        <v>1.17</v>
       </c>
       <c r="Q39" t="n">
-        <v>42.09</v>
+        <v>2.28</v>
       </c>
       <c r="R39" t="n">
-        <v>100.2</v>
+        <v>6.9</v>
       </c>
       <c r="S39" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5492,12 +5517,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 12 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>Calle 27</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5506,10 +5526,10 @@
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>4.088515899</v>
+        <v>3.894397016</v>
       </c>
       <c r="AD39" t="n">
-        <v>-76.22009</v>
+        <v>-76.29777</v>
       </c>
     </row>
     <row r="40">
@@ -5528,81 +5548,71 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>JOSE MARIA CORDOBA</t>
+          <t>ESC JORGE ELIECER GAITAN</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA HERNANDO LLORENTE ARROYO</t>
+          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>276616000212</t>
+          <t>176111001139</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>RIOFRIO</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>CORREG SALONICA</t>
+          <t>CR 10 NO 18-81</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>42.09</v>
+        <v>3.97</v>
       </c>
       <c r="Q40" t="n">
-        <v>50.65</v>
+        <v>3.43</v>
       </c>
       <c r="R40" t="n">
-        <v>100.2</v>
+        <v>16.9</v>
       </c>
       <c r="S40" t="n">
-        <v>57</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Peligro de colapso</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>en revisión de la mesa</t>
-        </is>
+        <v>4.5</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -5626,12 +5636,12 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 29 m de esa vía.</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>SALONICA CRUCE CON VIA 23VL13-1 EN K44+300</t>
+          <t>Carrera 10</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5640,10 +5650,10 @@
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>4.1258314</v>
+        <v>3.90894</v>
       </c>
       <c r="AD40" t="n">
-        <v>-76.3722336</v>
+        <v>-76.29465</v>
       </c>
     </row>
     <row r="41">
@@ -5669,31 +5679,31 @@
         <v>12</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>INTEGRADA DE TRUJILLO</t>
+          <t>INSTITUTO TECNICO AGRICOLA-SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA INTEGRADA DE TRUJILLO</t>
+          <t>INSTITUCION EDUCATIVA AGRICOLA DE GUADALAJARA DE BUGA</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>176828000021</t>
+          <t>176111000507</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -5703,40 +5713,30 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>KR 18 15 40</t>
+          <t>CL 23 KR 9 A</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>46.98</v>
+        <v>3.43</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.67</v>
+        <v>9.52</v>
       </c>
       <c r="R41" t="n">
-        <v>91.90000000000001</v>
+        <v>16.9</v>
       </c>
       <c r="S41" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>4.5</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -5760,12 +5760,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 33 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Carrera 18</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 32 m de esa vía.</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5774,10 +5769,10 @@
         </is>
       </c>
       <c r="AC41" t="n">
-        <v>4.208406</v>
+        <v>3.914166667</v>
       </c>
       <c r="AD41" t="n">
-        <v>-76.31959500000001</v>
+        <v>-76.2925</v>
       </c>
     </row>
     <row r="42">
@@ -5792,42 +5787,42 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>CRISTOBAL COLÓN</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA INTEGRADA DE TRUJILLO</t>
+          <t>INSTITUCION EDUCATIVA MANUEL ANTONIO SANCLEMENTE</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>176828000064</t>
+          <t>276111001087</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -5837,30 +5832,30 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>KR 18 15 27</t>
+          <t>VDA GUADUALEJO</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.67</v>
+        <v>4.38</v>
       </c>
       <c r="Q42" t="n">
-        <v>44.3</v>
+        <v>0.54</v>
       </c>
       <c r="R42" t="n">
-        <v>91.90000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="S42" t="n">
-        <v>48.5</v>
+        <v>2.8</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -5884,12 +5879,12 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Carrera 18</t>
+          <t>Calle 4A</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -5898,10 +5893,10 @@
         </is>
       </c>
       <c r="AC42" t="n">
-        <v>4.210077</v>
+        <v>3.893611111</v>
       </c>
       <c r="AD42" t="n">
-        <v>-76.319047</v>
+        <v>-76.29111</v>
       </c>
     </row>
     <row r="43">
@@ -5927,74 +5922,64 @@
         <v>13</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SAN ISIDRO</t>
+          <t>MANUEL ANTONIO SANCLEMENTE - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAN ISIDRO</t>
+          <t>INSTITUCION EDUCATIVA MANUEL ANTONIO SANCLEMENTE</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>276828000174</t>
+          <t>176111000515</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>CORREGIMIENTO EL TABOR PUENTE BLANCO</t>
+          <t>CL 4 A 1 E 26</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>77.20999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="Q43" t="n">
-        <v>69.08</v>
+        <v>4.14</v>
       </c>
       <c r="R43" t="n">
-        <v>146.3</v>
+        <v>9.1</v>
       </c>
       <c r="S43" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Habitable</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>2.8</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -6018,12 +6003,12 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 30 m de esa vía.</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>TRUJILLO - LA SONORA CRUCE VIA 23VL13-1 K64+160</t>
+          <t>Calle 4</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -6032,10 +6017,10 @@
         </is>
       </c>
       <c r="AC43" t="n">
-        <v>4.210564</v>
+        <v>3.89307</v>
       </c>
       <c r="AD43" t="n">
-        <v>-76.38158300000001</v>
+        <v>-76.29131</v>
       </c>
     </row>
     <row r="44">
@@ -6065,69 +6050,69 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SEDE INSTITUTO CAMPESTRE SANTA CECILIA</t>
+          <t>ANGEL CUADROS - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
+          <t>INSTITUCION EDUCATIVA ANGEL CUADROS</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>176834000599</t>
+          <t>276111000153</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>IND CALLE 27 NO 6AW 240</t>
+          <t>CORREG ZANJON-HONDO</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Yotoco</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>9.890000000000001</v>
+        <v>14.84</v>
       </c>
       <c r="Q44" t="n">
-        <v>32.44</v>
+        <v>4.16</v>
       </c>
       <c r="R44" t="n">
-        <v>89.40000000000001</v>
+        <v>42.4</v>
       </c>
       <c r="S44" t="n">
-        <v>62</v>
+        <v>28.8</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -6142,7 +6127,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 50 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 78 m de esa vía.</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -6151,10 +6136,10 @@
         </is>
       </c>
       <c r="AC44" t="n">
-        <v>4.090555556</v>
+        <v>3.845303584</v>
       </c>
       <c r="AD44" t="n">
-        <v>-76.22221999999999</v>
+        <v>-76.30364</v>
       </c>
     </row>
     <row r="45">
@@ -6184,27 +6169,27 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ALFREDO GARRIDO TOVAR</t>
+          <t>ANTONIO GUENDICA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ALFREDO GARRIDO TOVAR</t>
+          <t>INSTITUCION EDUCATIVA ANGEL CUADROS</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>276616000654</t>
+          <t>276111000811</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>RIOFRIO</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -6214,69 +6199,59 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>CORREG PORTUGAL DE PIEDRAS</t>
+          <t>QUEBRADASECA</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Yotoco</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>32.44</v>
+        <v>4.16</v>
       </c>
       <c r="Q45" t="n">
-        <v>47.02</v>
+        <v>23.43</v>
       </c>
       <c r="R45" t="n">
-        <v>89.40000000000001</v>
+        <v>42.4</v>
       </c>
       <c r="S45" t="n">
-        <v>62</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>28.8</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «trunk»). La sede queda a 37 m de esa vía.</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>PORTUGAL DE PIEDRAS - CRUCE VIA 23VL13</t>
+          <t>Troncal de Occidente</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6285,10 +6260,10 @@
         </is>
       </c>
       <c r="AC45" t="n">
-        <v>4.0553</v>
+        <v>3.850833</v>
       </c>
       <c r="AD45" t="n">
-        <v>-76.35465000000001</v>
+        <v>-76.29722</v>
       </c>
     </row>
     <row r="46">
@@ -6318,27 +6293,27 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>TULIO ENRIQUE TASCON CHAMBIMBAL - SEDE PRINCIPAL</t>
+          <t>VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON CHAMBIMBAL</t>
+          <t>INSTITUCION EDUCATIVA JORGE ROBLEDO</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>276111000781</t>
+          <t>276869000171</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>VIJES</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -6348,12 +6323,12 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>CHAMBIMBAL</t>
+          <t>CORREGIMIENTO VILLAMARIA</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Yotoco</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -6362,40 +6337,50 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>24.58</v>
+        <v>40.51</v>
       </c>
       <c r="Q46" t="n">
-        <v>24.3</v>
+        <v>15.26</v>
       </c>
       <c r="R46" t="n">
-        <v>116.8</v>
+        <v>112.8</v>
       </c>
       <c r="S46" t="n">
-        <v>84.90000000000001</v>
+        <v>83.3</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Habitable</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 187 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6404,10 +6389,10 @@
         </is>
       </c>
       <c r="AC46" t="n">
-        <v>3.956111</v>
+        <v>3.716456</v>
       </c>
       <c r="AD46" t="n">
-        <v>-76.30028</v>
+        <v>-76.47793299999999</v>
       </c>
     </row>
     <row r="47">
@@ -6437,42 +6422,42 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ANGEL CUADROS - SEDE PRINCIPAL</t>
+          <t>POLICARPA SALAVARRIETA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ANGEL CUADROS</t>
+          <t>INSTITUCION EDUCATIVA JORGE ROBLEDO</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>276111000153</t>
+          <t>176869000061</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>VIJES</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>CORREG ZANJON-HONDO</t>
+          <t>KR 4 5 34</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Yotoco</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -6481,40 +6466,55 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>24.3</v>
+        <v>15.26</v>
       </c>
       <c r="Q47" t="n">
-        <v>67.88</v>
+        <v>57.07</v>
       </c>
       <c r="R47" t="n">
-        <v>116.8</v>
+        <v>112.8</v>
       </c>
       <c r="S47" t="n">
-        <v>84.90000000000001</v>
+        <v>83.3</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uso restringido</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 78 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 3 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Carrera 4</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="AC47" t="n">
-        <v>3.845303584</v>
+        <v>3.699871998710244</v>
       </c>
       <c r="AD47" t="n">
-        <v>-76.30364</v>
+        <v>-76.44279828333418</v>
       </c>
     </row>
     <row r="48">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -9141,10 +9141,10 @@
         <v>7.07</v>
       </c>
       <c r="R68" t="n">
-        <v>75.8</v>
+        <v>83.3</v>
       </c>
       <c r="S68" t="n">
-        <v>49.8</v>
+        <v>61.9</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -9255,20 +9255,20 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="P69" t="n">
         <v>7.07</v>
       </c>
       <c r="Q69" t="n">
-        <v>30.35</v>
+        <v>37.84</v>
       </c>
       <c r="R69" t="n">
-        <v>75.8</v>
+        <v>83.3</v>
       </c>
       <c r="S69" t="n">
-        <v>49.8</v>
+        <v>61.9</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -9339,27 +9339,27 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>NIÑA MARIA</t>
+          <t>ALFONSO LOPEZ PUMAREJO</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DEL PALMAR</t>
+          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DE LA CANDELARIA</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>176520002261</t>
+          <t>176130000330</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>CANDELARIA</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -9369,30 +9369,40 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>KR 26 37 01</t>
+          <t>CL 7 9 11</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.99</v>
+        <v>0.23</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="R70" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="S70" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>No habitable</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -9406,7 +9416,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -9416,24 +9426,24 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 21 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Carrera 26</t>
+          <t>Calle 7</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC70" t="n">
-        <v>3.53399314013</v>
+        <v>3.407489</v>
       </c>
       <c r="AD70" t="n">
-        <v>-76.2962377697</v>
+        <v>-76.34917799999999</v>
       </c>
     </row>
     <row r="71">
@@ -9463,27 +9473,27 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>LICEO FEMENINO</t>
+          <t>SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DEL PALMAR</t>
+          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DE LA CANDELARIA</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>176520000489</t>
+          <t>176130000356</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>CANDELARIA</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -9493,30 +9503,40 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>CR 28 NO 37 81</t>
+          <t>CL 7 8 42</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.66</v>
+        <v>1.68</v>
       </c>
       <c r="R71" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="S71" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>No habitable</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -9530,7 +9550,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -9540,24 +9560,24 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 43 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Carrera 28</t>
+          <t>Calle 7</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC71" t="n">
-        <v>3.53438389943</v>
+        <v>3.40761667</v>
       </c>
       <c r="AD71" t="n">
-        <v>-76.2982293309</v>
+        <v>-76.34858894</v>
       </c>
     </row>
     <row r="72">
@@ -9587,60 +9607,70 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ENELIA RIVERA</t>
+          <t>JOSE EUSEBIO CARO</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SANTA BARBARA</t>
+          <t>INSTITUCION EDUCATIVA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>176520001957</t>
+          <t>276130000288</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>CANDELARIA</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>CLL 30 CR 40</t>
+          <t>CR 12 NO 10-81</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>6</v>
+        <v>11.66</v>
       </c>
       <c r="Q72" t="n">
-        <v>5.87</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="R72" t="n">
-        <v>11.9</v>
+        <v>20.2</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>13.6</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>No habitable</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -9664,24 +9694,24 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 48 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Carrera 41</t>
+          <t>CALLEJON FLORO MERCADO CRUCE VIA 13025VL04-2E</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC72" t="n">
-        <v>3.528369858</v>
+        <v>3.39537597879</v>
       </c>
       <c r="AD72" t="n">
-        <v>-76.30969955</v>
+        <v>-76.3859481842</v>
       </c>
     </row>
     <row r="73">
@@ -9711,69 +9741,69 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
+          <t>BID (43)</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA ABSALON TORRES CAMACHO</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>176275000125</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>FLORIDA</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>CR 21 NO 9-89</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Candelaria</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>CENTRO ALFONSO LOPEZ</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA DOMINGO IRURITA</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>176520003623</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>KR 25 21 52</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>Palmira</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>Palmira</t>
-        </is>
-      </c>
       <c r="P73" t="n">
-        <v>4.81</v>
+        <v>27.65</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.85</v>
+        <v>50.58</v>
       </c>
       <c r="R73" t="n">
-        <v>14.4</v>
+        <v>119.1</v>
       </c>
       <c r="S73" t="n">
-        <v>4.5</v>
+        <v>65.8</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -9788,12 +9818,12 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 36 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 23 m de esa vía.</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Calle 21</t>
+          <t>Calle 10</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
@@ -9802,10 +9832,10 @@
         </is>
       </c>
       <c r="AC73" t="n">
-        <v>3.519487</v>
+        <v>3.32644406118</v>
       </c>
       <c r="AD73" t="n">
-        <v>-76.29709</v>
+        <v>-76.23742270629999</v>
       </c>
     </row>
     <row r="74">
@@ -9840,17 +9870,17 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>DOMINGO IRURITA</t>
+          <t>SANTO TOMAS DE AQUINO</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA DOMINGO IRURITA</t>
+          <t>INSTITUCION EDUCATIVA FRANCISCO MIRANDA</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>176520002163</t>
+          <t>276520000548</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -9860,49 +9890,49 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>CL 23 33 A 37</t>
+          <t>VDA MESON</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
+          <t>Candelaria</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>Palmira</t>
-        </is>
-      </c>
       <c r="P74" t="n">
-        <v>3.85</v>
+        <v>50.58</v>
       </c>
       <c r="Q74" t="n">
-        <v>5.78</v>
+        <v>40.86</v>
       </c>
       <c r="R74" t="n">
-        <v>14.4</v>
+        <v>119.1</v>
       </c>
       <c r="S74" t="n">
-        <v>4.5</v>
+        <v>65.8</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
@@ -9912,12 +9942,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 35 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>Carrera 33A</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 129 m de esa vía.</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
@@ -9926,10 +9951,10 @@
         </is>
       </c>
       <c r="AC74" t="n">
-        <v>3.521358245</v>
+        <v>3.499130225</v>
       </c>
       <c r="AD74" t="n">
-        <v>-76.30535072000001</v>
+        <v>-76.18842022</v>
       </c>
     </row>
     <row r="75">
@@ -9964,17 +9989,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>JOSE MANUEL GROOT</t>
+          <t>NIÑA MARIA</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA HAROLD EDER</t>
+          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DEL PALMAR</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>276520002192</t>
+          <t>176520002261</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -9989,7 +10014,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>CL 65 31 C 95</t>
+          <t>KR 26 37 01</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -10003,25 +10028,25 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>10.39</v>
+        <v>1.99</v>
       </c>
       <c r="Q75" t="n">
-        <v>47.5</v>
+        <v>1.75</v>
       </c>
       <c r="R75" t="n">
-        <v>100.6</v>
+        <v>6.4</v>
       </c>
       <c r="S75" t="n">
-        <v>55.7</v>
+        <v>1.9</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
@@ -10036,24 +10061,24 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 21 m de esa vía.</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Carrera 32</t>
+          <t>Carrera 26</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC75" t="n">
-        <v>3.556083</v>
+        <v>3.53399314013</v>
       </c>
       <c r="AD75" t="n">
-        <v>-76.30073299999999</v>
+        <v>-76.2962377697</v>
       </c>
     </row>
     <row r="76">
@@ -10088,17 +10113,17 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>MARCO FIDEL SUAREZ</t>
+          <t>LICEO FEMENINO</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TABLONES</t>
+          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DEL PALMAR</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>276520001684</t>
+          <t>176520000489</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -10108,12 +10133,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>VDA LA ESPERANZA</t>
+          <t>CR 28 NO 37 81</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -10127,20 +10152,30 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>47.5</v>
+        <v>1.75</v>
       </c>
       <c r="Q76" t="n">
-        <v>42.74</v>
+        <v>2.66</v>
       </c>
       <c r="R76" t="n">
-        <v>100.6</v>
+        <v>6.4</v>
       </c>
       <c r="S76" t="n">
-        <v>55.7</v>
+        <v>1.9</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -10150,19 +10185,24 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 9 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 43 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Carrera 28</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC76" t="n">
-        <v>3.610511</v>
+        <v>3.53438389943</v>
       </c>
       <c r="AD76" t="n">
-        <v>-76.155193</v>
+        <v>-76.2982293309</v>
       </c>
     </row>
     <row r="77">
@@ -10197,17 +10237,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>CRISTOBAL COLON</t>
+          <t>CENTRO ALFONSO LOPEZ</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TABLONES</t>
+          <t>INSTITUCION EDUCATIVA DOMINGO IRURITA</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>276520001552</t>
+          <t>176520003623</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -10217,12 +10257,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>VDA LA CASCADA</t>
+          <t>KR 25 21 52</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -10236,30 +10276,30 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>33.72</v>
+        <v>4.81</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.14</v>
+        <v>7.64</v>
       </c>
       <c r="R77" t="n">
-        <v>53.3</v>
+        <v>19.5</v>
       </c>
       <c r="S77" t="n">
-        <v>28.7</v>
+        <v>5.8</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -10269,24 +10309,24 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 37 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Vía a Tienda Nueva</t>
+          <t>Calle 21</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC77" t="n">
-        <v>3.564564</v>
+        <v>3.519487</v>
       </c>
       <c r="AD77" t="n">
-        <v>-76.231579</v>
+        <v>-76.29709</v>
       </c>
     </row>
     <row r="78">
@@ -10321,17 +10361,17 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ROSARIO DE FATIMA</t>
+          <t>ALFONSO LOPEZ PUMAREJO</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TABLONES</t>
+          <t>INSTITUCION EDUCATIVA ALFONSO LOPEZ PUMAREJO</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>276520000742</t>
+          <t>176520002091</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -10341,12 +10381,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>CORREG LA BOLSA</t>
+          <t>KR 16 32 02</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -10360,57 +10400,52 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.14</v>
+        <v>7.64</v>
       </c>
       <c r="Q78" t="n">
-        <v>17.42</v>
+        <v>7.03</v>
       </c>
       <c r="R78" t="n">
-        <v>53.3</v>
+        <v>19.5</v>
       </c>
       <c r="S78" t="n">
-        <v>28.7</v>
+        <v>5.8</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 18 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>La Bolsa</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 17 m de esa vía.</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC78" t="n">
-        <v>3.555961</v>
+        <v>3.528177503</v>
       </c>
       <c r="AD78" t="n">
-        <v>-76.23436599999999</v>
+        <v>-76.28814192999999</v>
       </c>
     </row>
     <row r="79">
@@ -10445,17 +10480,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>MARIA DOMINGUEZ</t>
+          <t>ENELIA RIVERA</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAGRADA FAMILIA POTRERILLO</t>
+          <t>INSTITUCION EDUCATIVA SANTA BARBARA</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>276520001625</t>
+          <t>176520001957</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -10465,12 +10500,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>VDA LA MARIA</t>
+          <t>CLL 30 CR 40</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -10484,35 +10519,45 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>58.29</v>
+        <v>6</v>
       </c>
       <c r="Q79" t="n">
-        <v>68.20999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="R79" t="n">
-        <v>126.5</v>
+        <v>16.6</v>
       </c>
       <c r="S79" t="n">
-        <v>49.7</v>
+        <v>5.5</v>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Afectación menor</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 16 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 48 m de esa vía.</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Via Tenjo - Mariala Alta</t>
+          <t>Carrera 41</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
@@ -10521,10 +10566,10 @@
         </is>
       </c>
       <c r="AC79" t="n">
-        <v>3.510825276</v>
+        <v>3.528369858</v>
       </c>
       <c r="AD79" t="n">
-        <v>-76.14317477</v>
+        <v>-76.30969955</v>
       </c>
     </row>
     <row r="80">
@@ -10543,14 +10588,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -10559,17 +10604,17 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>TABLONES</t>
+          <t>DOMINGO IRURITA</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TABLONES</t>
+          <t>INSTITUCION EDUCATIVA DOMINGO IRURITA</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>276520000564</t>
+          <t>176520002163</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -10579,12 +10624,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>CORREG TABLONES</t>
+          <t>CL 23 33 A 37</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -10598,16 +10643,16 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>38.78</v>
+        <v>4.8</v>
       </c>
       <c r="Q80" t="n">
-        <v>25.67</v>
+        <v>5.78</v>
       </c>
       <c r="R80" t="n">
-        <v>117.8</v>
+        <v>16.6</v>
       </c>
       <c r="S80" t="n">
-        <v>61</v>
+        <v>5.5</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -10621,29 +10666,34 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 21 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 35 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Carrera 33A</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC80" t="n">
-        <v>3.602559</v>
+        <v>3.521358245</v>
       </c>
       <c r="AD80" t="n">
-        <v>-76.20097800000001</v>
+        <v>-76.30535072000001</v>
       </c>
     </row>
     <row r="81">
@@ -10669,7 +10719,7 @@
         <v>8</v>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -10678,17 +10728,17 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>ROSARIO MENESSES</t>
+          <t>JOSE MANUEL GROOT</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAGRADA FAMILIA POTRERILLO</t>
+          <t>INSTITUCION EDUCATIVA HAROLD EDER</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>276520001676</t>
+          <t>276520002192</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -10698,12 +10748,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>VDA LOS CUCHOS</t>
+          <t>CL 65 31 C 95</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -10717,52 +10767,57 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>25.67</v>
+        <v>10.39</v>
       </c>
       <c r="Q81" t="n">
-        <v>53.34</v>
+        <v>47.5</v>
       </c>
       <c r="R81" t="n">
-        <v>117.8</v>
+        <v>100.6</v>
       </c>
       <c r="S81" t="n">
-        <v>61</v>
+        <v>55.7</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 1330 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Carrera 32</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC81" t="n">
-        <v>3.582859967</v>
+        <v>3.556083</v>
       </c>
       <c r="AD81" t="n">
-        <v>-76.15750609</v>
+        <v>-76.30073299999999</v>
       </c>
     </row>
     <row r="82">
@@ -10781,14 +10836,14 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -10797,17 +10852,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>LA NEVERA</t>
+          <t>MARCO FIDEL SUAREZ</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAGRADA FAMILIA POTRERILLO</t>
+          <t>INSTITUCION EDUCATIVA TABLONES</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>276520003032</t>
+          <t>276520001684</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -10822,7 +10877,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>VDA LA NEVERA</t>
+          <t>VDA LA ESPERANZA</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -10836,40 +10891,30 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>99.38</v>
+        <v>47.5</v>
       </c>
       <c r="Q82" t="n">
-        <v>104.79</v>
+        <v>42.74</v>
       </c>
       <c r="R82" t="n">
-        <v>204.2</v>
+        <v>100.6</v>
       </c>
       <c r="S82" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Afectación parcial</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Moderado</t>
-        </is>
+        <v>55.7</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 272 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 9 m de esa vía.</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
@@ -10878,10 +10923,10 @@
         </is>
       </c>
       <c r="AC82" t="n">
-        <v>3.545813</v>
+        <v>3.610511</v>
       </c>
       <c r="AD82" t="n">
-        <v>-76.113687</v>
+        <v>-76.155193</v>
       </c>
     </row>
     <row r="83">
@@ -10900,11 +10945,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -10916,7 +10961,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>RITA SABOGAL</t>
+          <t>CRISTOBAL COLON</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -10926,7 +10971,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>276520001633</t>
+          <t>276520001552</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -10941,7 +10986,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>VDA TIATINO</t>
+          <t>VDA LA CASCADA</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -10955,40 +11000,45 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>98.42</v>
+        <v>33.72</v>
       </c>
       <c r="Q83" t="n">
-        <v>79.44</v>
+        <v>2.14</v>
       </c>
       <c r="R83" t="n">
-        <v>177.9</v>
+        <v>53.3</v>
       </c>
       <c r="S83" t="n">
-        <v>83.90000000000001</v>
+        <v>28.7</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 352 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 37 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>Vía a Tienda Nueva</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
@@ -10997,10 +11047,10 @@
         </is>
       </c>
       <c r="AC83" t="n">
-        <v>3.641394707</v>
+        <v>3.564564</v>
       </c>
       <c r="AD83" t="n">
-        <v>-76.05537963</v>
+        <v>-76.231579</v>
       </c>
     </row>
     <row r="84">
@@ -11019,14 +11069,14 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -11035,17 +11085,17 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>ALFONSO LOPEZ PUMAREJO</t>
+          <t>ROSARIO DE FATIMA</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ALFONSO LOPEZ PUMAREJO</t>
+          <t>INSTITUCION EDUCATIVA TABLONES</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>176520002091</t>
+          <t>276520000742</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -11055,12 +11105,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>KR 16 32 02</t>
+          <t>CORREG LA BOLSA</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -11070,56 +11120,61 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>7.29</v>
+        <v>2.14</v>
       </c>
       <c r="Q84" t="n">
-        <v>33.28</v>
+        <v>17.42</v>
       </c>
       <c r="R84" t="n">
-        <v>92.5</v>
+        <v>53.3</v>
       </c>
       <c r="S84" t="n">
-        <v>48.5</v>
+        <v>28.7</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 17 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 18 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>La Bolsa</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC84" t="n">
-        <v>3.528177503</v>
+        <v>3.555961</v>
       </c>
       <c r="AD84" t="n">
-        <v>-76.28814192999999</v>
+        <v>-76.23436599999999</v>
       </c>
     </row>
     <row r="85">
@@ -11138,14 +11193,14 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -11154,17 +11209,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>SANTO TOMAS DE AQUINO</t>
+          <t>MARIA DOMINGUEZ</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA FRANCISCO MIRANDA</t>
+          <t>INSTITUCION EDUCATIVA SAGRADA FAMILIA POTRERILLO</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>276520000548</t>
+          <t>276520001625</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -11179,7 +11234,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>VDA MESON</t>
+          <t>VDA LA MARIA</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -11189,44 +11244,39 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>33.28</v>
+        <v>58.29</v>
       </c>
       <c r="Q85" t="n">
-        <v>51.93</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="R85" t="n">
-        <v>92.5</v>
+        <v>126.5</v>
       </c>
       <c r="S85" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
+        <v>49.7</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 129 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 16 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Via Tenjo - Mariala Alta</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
@@ -11235,10 +11285,10 @@
         </is>
       </c>
       <c r="AC85" t="n">
-        <v>3.499130225</v>
+        <v>3.510825276</v>
       </c>
       <c r="AD85" t="n">
-        <v>-76.18842022</v>
+        <v>-76.14317477</v>
       </c>
     </row>
     <row r="86">
@@ -11257,81 +11307,71 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ALFONSO LOPEZ PUMAREJO</t>
+          <t>TABLONES</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DE LA CANDELARIA</t>
+          <t>INSTITUCION EDUCATIVA TABLONES</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>176130000330</t>
+          <t>276520000564</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>CANDELARIA</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>CL 7 9 11</t>
+          <t>CORREG TABLONES</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0.23</v>
+        <v>38.78</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.25</v>
+        <v>25.67</v>
       </c>
       <c r="R86" t="n">
-        <v>2.2</v>
+        <v>117.8</v>
       </c>
       <c r="S86" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>61</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -11345,22 +11385,17 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 2 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>Calle 7</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 21 m de esa vía.</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
@@ -11369,10 +11404,10 @@
         </is>
       </c>
       <c r="AC86" t="n">
-        <v>3.407489</v>
+        <v>3.602559</v>
       </c>
       <c r="AD86" t="n">
-        <v>-76.34917799999999</v>
+        <v>-76.20097800000001</v>
       </c>
     </row>
     <row r="87">
@@ -11391,122 +11426,107 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F87" t="n">
         <v>2</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>SAGRADA FAMILIA</t>
+          <t>ROSARIO MENESSES</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DE LA CANDELARIA</t>
+          <t>INSTITUCION EDUCATIVA SAGRADA FAMILIA POTRERILLO</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>176130000356</t>
+          <t>276520001676</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>CANDELARIA</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>CL 7 8 42</t>
+          <t>VDA LOS CUCHOS</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0.25</v>
+        <v>25.67</v>
       </c>
       <c r="Q87" t="n">
-        <v>1.68</v>
+        <v>53.34</v>
       </c>
       <c r="R87" t="n">
-        <v>2.2</v>
+        <v>117.8</v>
       </c>
       <c r="S87" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>61</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>Calle 7</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 1330 m de esa vía.</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC87" t="n">
-        <v>3.40761667</v>
+        <v>3.582859967</v>
       </c>
       <c r="AD87" t="n">
-        <v>-76.34858894</v>
+        <v>-76.15750609</v>
       </c>
     </row>
     <row r="88">
@@ -11521,104 +11541,99 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>LA NEVERA</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ABSALON TORRES CAMACHO</t>
+          <t>INSTITUCION EDUCATIVA SAGRADA FAMILIA POTRERILLO</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>176275000125</t>
+          <t>276520003032</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>FLORIDA</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>CR 21 NO 9-89</t>
+          <t>VDA LA NEVERA</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>27.65</v>
+        <v>99.38</v>
       </c>
       <c r="Q88" t="n">
-        <v>28.95</v>
+        <v>104.79</v>
       </c>
       <c r="R88" t="n">
-        <v>65.09999999999999</v>
+        <v>204.2</v>
       </c>
       <c r="S88" t="n">
-        <v>44</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>Bajo</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 23 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>Calle 10</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 272 m de esa vía.</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
@@ -11627,10 +11642,10 @@
         </is>
       </c>
       <c r="AC88" t="n">
-        <v>3.32644406118</v>
+        <v>3.545813</v>
       </c>
       <c r="AD88" t="n">
-        <v>-76.23742270629999</v>
+        <v>-76.113687</v>
       </c>
     </row>
     <row r="89">
@@ -11656,31 +11671,31 @@
         <v>13</v>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>JOSE EUSEBIO CARO</t>
+          <t>RITA SABOGAL</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA INMACULADA CONCEPCION</t>
+          <t>INSTITUCION EDUCATIVA TABLONES</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>276130000288</t>
+          <t>276520001633</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>CANDELARIA</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -11690,81 +11705,66 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>CR 12 NO 10-81</t>
+          <t>VDA TIATINO</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>28.95</v>
+        <v>98.42</v>
       </c>
       <c r="Q89" t="n">
-        <v>8.539999999999999</v>
+        <v>79.44</v>
       </c>
       <c r="R89" t="n">
-        <v>65.09999999999999</v>
+        <v>177.9</v>
       </c>
       <c r="S89" t="n">
-        <v>44</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>83.90000000000001</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>Bajo</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>CALLEJON FLORO MERCADO CRUCE VIA 13025VL04-2E</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 352 m de esa vía.</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC89" t="n">
-        <v>3.39537597879</v>
+        <v>3.641394707</v>
       </c>
       <c r="AD89" t="n">
-        <v>-76.3859481842</v>
+        <v>-76.05537963</v>
       </c>
     </row>
     <row r="90">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -11838,16 +11838,16 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>36.99</v>
+        <v>29.19</v>
       </c>
       <c r="Q90" t="n">
         <v>11.21</v>
       </c>
       <c r="R90" t="n">
-        <v>85.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="S90" t="n">
-        <v>60.7</v>
+        <v>52.2</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -11963,10 +11963,10 @@
         <v>37.19</v>
       </c>
       <c r="R91" t="n">
-        <v>85.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="S91" t="n">
-        <v>60.7</v>
+        <v>52.2</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Todo Valle* 4 cuadrillas. Las 91 sedes del Valle sin Buenaventura: las 43 del BID más Palmira, Yumbo, Tuluá, Buga y Cartago. El asterisco es eso. No cabe en el TdR: necesita una cuarta cuadrilla, con base en Cali, y 56 días de campo en vez de 45. Sin volver a la base los domingos.</t>
+          <t>Todo Valle* 4 cuadrillas. Las 90 sedes del Valle sin Buenaventura: las 43 del BID más Palmira, Yumbo, Tuluá, Buga y Cartago. El asterisco es eso. No cabe en el TdR: necesita una cuarta cuadrilla, con base en Cali, y al menos 56 días de campo contra 45. Sin volver a la base los domingos.</t>
         </is>
       </c>
     </row>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12155,13 +12155,13 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>35.1</v>
+        <v>33.8</v>
       </c>
       <c r="E10" t="n">
-        <v>1088</v>
+        <v>992</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -12180,13 +12180,13 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="E11" t="n">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="F11" t="n">
         <v>14</v>
@@ -12233,10 +12233,10 @@
         <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="E13" t="n">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>

--- a/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
+++ b/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PANORAMA</t>
+          <t>IRENE FERREROSA - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>276892001125</t>
+          <t>176892100102</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PANORAMA PARTE ALTA</t>
+          <t>KR 18 G 17 A 60</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -924,20 +924,20 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>28.88</v>
+        <v>29.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="R4" t="n">
-        <v>68.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -947,22 +947,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 0 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Calle 8</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 3 m de esa vía.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -971,10 +966,10 @@
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>3.563871751</v>
+        <v>3.5643709</v>
       </c>
       <c r="AD4" t="n">
-        <v>-76.49699</v>
+        <v>-76.4995401</v>
       </c>
     </row>
     <row r="5">
@@ -1009,7 +1004,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>IRENE FERREROSA - SEDE PRINCIPAL</t>
+          <t>PANORAMA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1019,7 +1014,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>176892100102</t>
+          <t>276892001125</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>KR 18 G 17 A 60</t>
+          <t>PANORAMA PARTE ALTA</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1048,20 +1043,20 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>37.21</v>
+        <v>36.96</v>
       </c>
       <c r="R5" t="n">
-        <v>68.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1071,7 +1066,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1081,12 +1076,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 17 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 4 m de esa vía.</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Calle 7</t>
+          <t>Calle 7B</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1095,10 +1090,10 @@
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>3.569142</v>
+        <v>3.5690111</v>
       </c>
       <c r="AD5" t="n">
-        <v>-76.49818</v>
+        <v>-76.4979953</v>
       </c>
     </row>
     <row r="6">
@@ -3257,27 +3252,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ALFREDO GARRIDO TOVAR</t>
+          <t>ANGEL CUADROS - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ALFREDO GARRIDO TOVAR</t>
+          <t>INSTITUCION EDUCATIVA ANGEL CUADROS</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>276616000654</t>
+          <t>276111000153</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>RIOFRIO</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3287,7 +3282,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>CORREG PORTUGAL DE PIEDRAS</t>
+          <t>CORREG ZANJON-HONDO</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3297,30 +3292,20 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>38.38</v>
+        <v>22.19</v>
       </c>
       <c r="Q22" t="n">
-        <v>31.2</v>
+        <v>4.73</v>
       </c>
       <c r="R22" t="n">
-        <v>77.90000000000001</v>
+        <v>36.9</v>
       </c>
       <c r="S22" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>23.2</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -3334,22 +3319,17 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>PORTUGAL DE PIEDRAS - CRUCE VIA 23VL13</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3358,10 +3338,10 @@
         </is>
       </c>
       <c r="AC22" t="n">
-        <v>4.0553</v>
+        <v>3.8504316</v>
       </c>
       <c r="AD22" t="n">
-        <v>-76.35465000000001</v>
+        <v>-76.29718</v>
       </c>
     </row>
     <row r="23">
@@ -3391,37 +3371,37 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SEDE PRINCIPAL LICEO MODERNO</t>
+          <t>ANTONIO GUENDICA</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
+          <t>INSTITUCION EDUCATIVA ANGEL CUADROS</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>176834000106</t>
+          <t>276111000811</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>IND CALLE 27 NO. 6AW 240</t>
+          <t>QUEBRADASECA</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3431,29 +3411,29 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>31.2</v>
+        <v>4.73</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="R23" t="n">
-        <v>77.90000000000001</v>
+        <v>36.9</v>
       </c>
       <c r="S23" t="n">
-        <v>58.5</v>
+        <v>23.2</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -3468,12 +3448,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 12 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Calle 27</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3482,10 +3457,10 @@
         </is>
       </c>
       <c r="AC23" t="n">
-        <v>4.088515899</v>
+        <v>3.870531</v>
       </c>
       <c r="AD23" t="n">
-        <v>-76.22009</v>
+        <v>-76.29683900000001</v>
       </c>
     </row>
     <row r="24">
@@ -3515,27 +3490,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SEDE INSTITUTO CAMPESTRE SANTA CECILIA</t>
+          <t>ACADEMICO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
+          <t>INSTITUCION EDUCATIVA ACADEMICO</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>176834000599</t>
+          <t>176111001104</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3545,30 +3520,30 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>IND CALLE 27 NO 6AW 240</t>
+          <t>KR 9 A 2 55 SUR</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>9.890000000000001</v>
+        <v>3.44</v>
       </c>
       <c r="Q24" t="n">
-        <v>43.42</v>
+        <v>1.17</v>
       </c>
       <c r="R24" t="n">
-        <v>104</v>
+        <v>6.9</v>
       </c>
       <c r="S24" t="n">
-        <v>57.8</v>
+        <v>2</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -3582,17 +3557,22 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 50 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 25 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Carrera 9</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3601,10 +3581,10 @@
         </is>
       </c>
       <c r="AC24" t="n">
-        <v>4.090555556</v>
+        <v>3.892781656</v>
       </c>
       <c r="AD24" t="n">
-        <v>-76.22221999999999</v>
+        <v>-76.29845</v>
       </c>
     </row>
     <row r="25">
@@ -3634,79 +3614,69 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>JOSE MARIA CORDOBA</t>
+          <t>NARCISO CABAL SALCEDO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA HERNANDO LLORENTE ARROYO</t>
+          <t>INSTITUCION EDUCATIVA NARCISO CABAL SALCEDO</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>276616000212</t>
+          <t>176111000469</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>RIOFRIO</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>CORREG SALONICA</t>
+          <t>CL 2 8 47</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>43.42</v>
+        <v>1.17</v>
       </c>
       <c r="Q25" t="n">
-        <v>50.65</v>
+        <v>2.28</v>
       </c>
       <c r="R25" t="n">
-        <v>104</v>
+        <v>6.9</v>
       </c>
       <c r="S25" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Peligro de colapso</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>en revisión de la mesa</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3721,12 +3691,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>SALONICA CRUCE CON VIA 23VL13-1 EN K44+300</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3735,10 +3700,10 @@
         </is>
       </c>
       <c r="AC25" t="n">
-        <v>4.1258314</v>
+        <v>3.894397016</v>
       </c>
       <c r="AD25" t="n">
-        <v>-76.3722336</v>
+        <v>-76.29777</v>
       </c>
     </row>
     <row r="26">
@@ -3768,27 +3733,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>INTEGRADA DE TRUJILLO</t>
+          <t>ESC JOAQUIN CAMILO TORRES</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA INTEGRADA DE TRUJILLO</t>
+          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>176828000021</t>
+          <t>176111001171</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3798,49 +3763,39 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>KR 18 15 40</t>
+          <t>CL 15 9 45</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>46.98</v>
+        <v>4.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.67</v>
+        <v>1.59</v>
       </c>
       <c r="R26" t="n">
-        <v>91.90000000000001</v>
+        <v>10.9</v>
       </c>
       <c r="S26" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>3.3</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3855,12 +3810,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 33 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Carrera 18</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3869,10 +3819,10 @@
         </is>
       </c>
       <c r="AC26" t="n">
-        <v>4.208406</v>
+        <v>3.9055</v>
       </c>
       <c r="AD26" t="n">
-        <v>-76.31959500000001</v>
+        <v>-76.29489</v>
       </c>
     </row>
     <row r="27">
@@ -3902,27 +3852,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>ESC JORGE ELIECER GAITAN</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA INTEGRADA DE TRUJILLO</t>
+          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>176828000064</t>
+          <t>176111001139</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3932,34 +3882,34 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>KR 18 15 27</t>
+          <t>CR 10 NO 18-81</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.67</v>
+        <v>1.59</v>
       </c>
       <c r="Q27" t="n">
-        <v>44.3</v>
+        <v>5.21</v>
       </c>
       <c r="R27" t="n">
-        <v>91.90000000000001</v>
+        <v>10.9</v>
       </c>
       <c r="S27" t="n">
-        <v>48.5</v>
+        <v>3.3</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3979,12 +3929,12 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 29 m de esa vía.</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Carrera 18</t>
+          <t>Carrera 10</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -3993,10 +3943,10 @@
         </is>
       </c>
       <c r="AC27" t="n">
-        <v>4.210077</v>
+        <v>3.90894</v>
       </c>
       <c r="AD27" t="n">
-        <v>-76.319047</v>
+        <v>-76.29465</v>
       </c>
     </row>
     <row r="28">
@@ -4026,84 +3976,74 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SAN ISIDRO</t>
+          <t>CRISTOBAL COLÓN</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAN ISIDRO</t>
+          <t>INSTITUCION EDUCATIVA MANUEL ANTONIO SANCLEMENTE</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>276828000174</t>
+          <t>276111001087</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>CORREGIMIENTO EL TABOR PUENTE BLANCO</t>
+          <t>VDA GUADUALEJO</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>77.20999999999999</v>
+        <v>4.38</v>
       </c>
       <c r="Q28" t="n">
-        <v>69.08</v>
+        <v>0.54</v>
       </c>
       <c r="R28" t="n">
-        <v>146.3</v>
+        <v>9.1</v>
       </c>
       <c r="S28" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Habitable</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>2.8</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4113,12 +4053,12 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>TRUJILLO - LA SONORA CRUCE VIA 23VL13-1 K64+160</t>
+          <t>Calle 4A</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4127,10 +4067,10 @@
         </is>
       </c>
       <c r="AC28" t="n">
-        <v>4.210564</v>
+        <v>3.893611111</v>
       </c>
       <c r="AD28" t="n">
-        <v>-76.38158300000001</v>
+        <v>-76.29111</v>
       </c>
     </row>
     <row r="29">
@@ -4149,38 +4089,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>MANUEL DOLORES MONDRAGON</t>
+          <t>MANUEL ANTONIO SANCLEMENTE - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MANUEL DOLORES MONDRAGON</t>
+          <t>INSTITUCION EDUCATIVA MANUEL ANTONIO SANCLEMENTE</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>176100000254</t>
+          <t>176111000515</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>BOLIVAR</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -4190,40 +4130,30 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>KR 2 2 66</t>
+          <t>CL 4 A 1 E 26</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Andalucia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>57.35</v>
+        <v>0.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>14.61</v>
+        <v>4.14</v>
       </c>
       <c r="R29" t="n">
-        <v>115.4</v>
+        <v>9.1</v>
       </c>
       <c r="S29" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Uso restringido</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>2.8</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -4237,7 +4167,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4247,12 +4177,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 43 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 30 m de esa vía.</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>BOLIVAR CRUCE CON VIA DE INVIAS 2302 EN TRAMO 23020 INICIO A 52m DE INICIO DE VIA 10023VL02B</t>
+          <t>Calle 4</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4261,10 +4191,10 @@
         </is>
       </c>
       <c r="AC29" t="n">
-        <v>4.340805</v>
+        <v>3.89307</v>
       </c>
       <c r="AD29" t="n">
-        <v>-76.17979800000001</v>
+        <v>-76.29131</v>
       </c>
     </row>
     <row r="30">
@@ -4290,74 +4220,64 @@
         <v>6</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE CHIQUINQUIRA</t>
+          <t>TULIO ENRIQUE TASCON CHAMBIMBAL - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DE CHIQUINQUIRA</t>
+          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON CHAMBIMBAL</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>176622000076</t>
+          <t>276111000781</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>ROLDANILLO</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>CL 4 5 38</t>
+          <t>CHAMBIMBAL</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Andalucia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>14.61</v>
+        <v>17.61</v>
       </c>
       <c r="Q30" t="n">
-        <v>43.44</v>
+        <v>7.25</v>
       </c>
       <c r="R30" t="n">
-        <v>115.4</v>
+        <v>33</v>
       </c>
       <c r="S30" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Uso restringido</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>20.4</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -4371,7 +4291,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4381,12 +4301,12 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «trunk»). La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Carrera 5</t>
+          <t>Troncal de Occidente</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4395,10 +4315,10 @@
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>4.412260842287796</v>
+        <v>3.9553497</v>
       </c>
       <c r="AD30" t="n">
-        <v>-76.15737540436542</v>
+        <v>-76.2707521</v>
       </c>
     </row>
     <row r="31">
@@ -4413,42 +4333,42 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="n">
         <v>2</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>lunes</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>7</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ELEAZAR LIBREROS SALAMANCA</t>
+          <t>GUADALAJARA</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ELEAZAR LIBREROS SALAMANCA</t>
+          <t>INSTITUCION EDUCATIVA GRAN COLOMBIA</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>176036000024</t>
+          <t>176111000604</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>ANDALUCIA</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4458,44 +4378,34 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>CL 6 4 15</t>
+          <t>CR 27 NO 14-23</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Andalucia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Caicedonia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.3</v>
+        <v>7.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>69.31</v>
+        <v>8.17</v>
       </c>
       <c r="R31" t="n">
-        <v>72.59999999999999</v>
+        <v>33</v>
       </c>
       <c r="S31" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Uso restringido</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>20.4</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4515,12 +4425,12 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Calle 6</t>
+          <t>Carrera 27</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4529,10 +4439,10 @@
         </is>
       </c>
       <c r="AC31" t="n">
-        <v>4.165067</v>
+        <v>3.911822</v>
       </c>
       <c r="AD31" t="n">
-        <v>-76.16943499999999</v>
+        <v>-76.30735</v>
       </c>
     </row>
     <row r="32">
@@ -4551,90 +4461,80 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>BOLIVARIANO</t>
+          <t>EL PLACER - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA BOLIVARIANO</t>
+          <t>INSTITUCION EDUCATIVA EL PLACER</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>176122000380</t>
+          <t>276111000102</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>CAICEDONIA</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>CL 5 11 15</t>
+          <t>CORREG EL PLACER</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Caicedonia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Andalucia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.47</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>59.43</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="R32" t="n">
-        <v>92.90000000000001</v>
+        <v>178.8</v>
       </c>
       <c r="S32" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Peligro de colapso</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>77.5</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -4649,12 +4549,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>Calle 5</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 90 m de esa vía.</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4663,10 +4558,10 @@
         </is>
       </c>
       <c r="AC32" t="n">
-        <v>4.329633623</v>
+        <v>3.88102932</v>
       </c>
       <c r="AD32" t="n">
-        <v>-75.82531724</v>
+        <v>-76.09909786</v>
       </c>
     </row>
     <row r="33">
@@ -4692,31 +4587,31 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SANTA CECILIA</t>
+          <t>INSTITUTO TECNICO AGRICOLA-SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EFRAIN VARELA VACA</t>
+          <t>INSTITUCION EDUCATIVA AGRICOLA DE GUADALAJARA DE BUGA</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>176895000231</t>
+          <t>176111000507</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>ZARZAL</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -4726,54 +4621,44 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>CL 10 KR 10 EQ</t>
+          <t>CL 23 KR 9 A</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
+          <t>Buga</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
           <t>Caicedonia</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Andalucia</t>
-        </is>
-      </c>
       <c r="P33" t="n">
-        <v>59.43</v>
+        <v>6.26</v>
       </c>
       <c r="Q33" t="n">
-        <v>31.96</v>
+        <v>34.04</v>
       </c>
       <c r="R33" t="n">
-        <v>92.90000000000001</v>
+        <v>109.6</v>
       </c>
       <c r="S33" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Peligro de colapso</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>99.90000000000001</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4783,12 +4668,12 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 18 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Carrera 10</t>
+          <t>Calle 25</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4797,10 +4682,10 @@
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>4.3959229</v>
+        <v>3.911563</v>
       </c>
       <c r="AD33" t="n">
-        <v>-76.0708454</v>
+        <v>-76.291687</v>
       </c>
     </row>
     <row r="34">
@@ -4819,95 +4704,110 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>BID (43)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ELEAZAR LIBREROS SALAMANCA</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA ELEAZAR LIBREROS SALAMANCA</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>176036000024</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ANDALUCIA</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>CL 6 4 15</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>Buga</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>TULIO ENRIQUE TASCON CHAMBIMBAL - SEDE PRINCIPAL</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON CHAMBIMBAL</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>276111000781</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Buga</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>CHAMBIMBAL</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Andalucia</t>
-        </is>
-      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Caicedonia</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>41.77</v>
+        <v>34.04</v>
       </c>
       <c r="Q34" t="n">
-        <v>16.89</v>
+        <v>69.31</v>
       </c>
       <c r="R34" t="n">
-        <v>66.8</v>
+        <v>109.6</v>
       </c>
       <c r="S34" t="n">
-        <v>46.6</v>
+        <v>99.90000000000001</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uso restringido</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 187 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Calle 6</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -4916,10 +4816,10 @@
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>3.956111</v>
+        <v>4.165067</v>
       </c>
       <c r="AD34" t="n">
-        <v>-76.30028</v>
+        <v>-76.16943499999999</v>
       </c>
     </row>
     <row r="35">
@@ -4945,31 +4845,31 @@
         <v>9</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>GUADALAJARA</t>
+          <t>BOLIVARIANO</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA GRAN COLOMBIA</t>
+          <t>INSTITUCION EDUCATIVA BOLIVARIANO</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>176111000604</t>
+          <t>176122000380</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>CAICEDONIA</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4979,34 +4879,44 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>CR 27 NO 14-23</t>
+          <t>CL 5 11 15</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
+          <t>Caicedonia</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Buga</t>
-        </is>
-      </c>
       <c r="P35" t="n">
-        <v>16.89</v>
+        <v>1.47</v>
       </c>
       <c r="Q35" t="n">
-        <v>8.17</v>
+        <v>59.43</v>
       </c>
       <c r="R35" t="n">
-        <v>66.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S35" t="n">
-        <v>46.6</v>
+        <v>79.7</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Peligro de colapso</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5026,12 +4936,12 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 22 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Carrera 27</t>
+          <t>Calle 5</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5040,10 +4950,10 @@
         </is>
       </c>
       <c r="AC35" t="n">
-        <v>3.911822</v>
+        <v>4.329633623</v>
       </c>
       <c r="AD35" t="n">
-        <v>-76.30735</v>
+        <v>-75.82531724</v>
       </c>
     </row>
     <row r="36">
@@ -5062,38 +4972,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ESC JOAQUIN CAMILO TORRES</t>
+          <t>SANTA CECILIA</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON</t>
+          <t>INSTITUCION EDUCATIVA EFRAIN VARELA VACA</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>176111001171</t>
+          <t>176895000231</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>ZARZAL</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -5103,30 +5013,40 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>CL 15 9 45</t>
+          <t>CL 10 KR 10 EQ</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Caicedonia</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Andalucia</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4.08</v>
+        <v>59.43</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.46</v>
+        <v>31.96</v>
       </c>
       <c r="R36" t="n">
-        <v>9.699999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S36" t="n">
-        <v>2.9</v>
+        <v>79.7</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Peligro de colapso</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -5140,7 +5060,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -5150,7 +5070,12 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 12 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 18 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Carrera 10</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5159,10 +5084,10 @@
         </is>
       </c>
       <c r="AC36" t="n">
-        <v>3.9055</v>
+        <v>4.3959229</v>
       </c>
       <c r="AD36" t="n">
-        <v>-76.29489</v>
+        <v>-76.0708454</v>
       </c>
     </row>
     <row r="37">
@@ -5188,64 +5113,74 @@
         <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>EL PLACER - SEDE PRINCIPAL</t>
+          <t>NUESTRA SEÑORA DE CHIQUINQUIRA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EL PLACER</t>
+          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DE CHIQUINQUIRA</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>276111000102</t>
+          <t>176622000076</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>ROLDANILLO</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>CORREG EL PLACER</t>
+          <t>CL 4 5 38</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Andalucia</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.46</v>
+        <v>48.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.2</v>
+        <v>14.74</v>
       </c>
       <c r="R37" t="n">
-        <v>9.699999999999999</v>
+        <v>114.3</v>
       </c>
       <c r="S37" t="n">
-        <v>2.9</v>
+        <v>93.2</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uso restringido</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -5269,12 +5204,12 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 30 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Calle 6</t>
+          <t>Carrera 5</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5283,10 +5218,10 @@
         </is>
       </c>
       <c r="AC37" t="n">
-        <v>3.898611</v>
+        <v>4.412260842287796</v>
       </c>
       <c r="AD37" t="n">
-        <v>-76.30056</v>
+        <v>-76.15737540436542</v>
       </c>
     </row>
     <row r="38">
@@ -5305,38 +5240,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ACADEMICO - SEDE PRINCIPAL</t>
+          <t>MANUEL DOLORES MONDRAGON</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ACADEMICO</t>
+          <t>INSTITUCION EDUCATIVA MANUEL DOLORES MONDRAGON</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>176111001104</t>
+          <t>176100000254</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BOLIVAR</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -5346,30 +5281,40 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>KR 9 A 2 55 SUR</t>
+          <t>KR 2 2 66</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Andalucia</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.44</v>
+        <v>14.74</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.17</v>
+        <v>50.86</v>
       </c>
       <c r="R38" t="n">
-        <v>6.9</v>
+        <v>114.3</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>93.2</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uso restringido</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -5393,12 +5338,12 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 25 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 43 m de esa vía.</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Carrera 9</t>
+          <t>BOLIVAR CRUCE CON VIA DE INVIAS 2302 EN TRAMO 23020 INICIO A 52m DE INICIO DE VIA 10023VL02B</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5407,10 +5352,10 @@
         </is>
       </c>
       <c r="AC38" t="n">
-        <v>3.892781656</v>
+        <v>4.340805</v>
       </c>
       <c r="AD38" t="n">
-        <v>-76.29845</v>
+        <v>-76.17979800000001</v>
       </c>
     </row>
     <row r="39">
@@ -5436,31 +5381,31 @@
         <v>11</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>NARCISO CABAL SALCEDO - SEDE PRINCIPAL</t>
+          <t>SEDE PRINCIPAL LICEO MODERNO</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA NARCISO CABAL SALCEDO</t>
+          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>176111000469</t>
+          <t>176834000106</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -5470,44 +5415,44 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>CL 2 8 47</t>
+          <t>IND CALLE 27 NO. 6AW 240</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.17</v>
+        <v>7.41</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.28</v>
+        <v>42.09</v>
       </c>
       <c r="R39" t="n">
-        <v>6.9</v>
+        <v>100.2</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5517,7 +5462,12 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 15 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 12 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Calle 27</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5526,10 +5476,10 @@
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>3.894397016</v>
+        <v>4.088515899</v>
       </c>
       <c r="AD39" t="n">
-        <v>-76.29777</v>
+        <v>-76.22009</v>
       </c>
     </row>
     <row r="40">
@@ -5548,71 +5498,81 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ESC JORGE ELIECER GAITAN</t>
+          <t>JOSE MARIA CORDOBA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TULIO ENRIQUE TASCON</t>
+          <t>INSTITUCION EDUCATIVA HERNANDO LLORENTE ARROYO</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>176111001139</t>
+          <t>276616000212</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>RIOFRIO</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>CR 10 NO 18-81</t>
+          <t>CORREG SALONICA</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.97</v>
+        <v>42.09</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.43</v>
+        <v>50.65</v>
       </c>
       <c r="R40" t="n">
-        <v>16.9</v>
+        <v>100.2</v>
       </c>
       <c r="S40" t="n">
-        <v>4.5</v>
+        <v>57</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Peligro de colapso</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>en revisión de la mesa</t>
+        </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -5636,12 +5596,12 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 29 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Carrera 10</t>
+          <t>SALONICA CRUCE CON VIA 23VL13-1 EN K44+300</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5650,10 +5610,10 @@
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>3.90894</v>
+        <v>4.1258314</v>
       </c>
       <c r="AD40" t="n">
-        <v>-76.29465</v>
+        <v>-76.3722336</v>
       </c>
     </row>
     <row r="41">
@@ -5679,31 +5639,31 @@
         <v>12</v>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>INSTITUTO TECNICO AGRICOLA-SEDE PRINCIPAL</t>
+          <t>INTEGRADA DE TRUJILLO</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA AGRICOLA DE GUADALAJARA DE BUGA</t>
+          <t>INSTITUCION EDUCATIVA INTEGRADA DE TRUJILLO</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>176111000507</t>
+          <t>176828000021</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -5713,30 +5673,40 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>CL 23 KR 9 A</t>
+          <t>KR 18 15 40</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.43</v>
+        <v>46.98</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.52</v>
+        <v>0.67</v>
       </c>
       <c r="R41" t="n">
-        <v>16.9</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="S41" t="n">
-        <v>4.5</v>
+        <v>48.5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>No habitable</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -5760,7 +5730,12 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 32 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 33 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Carrera 18</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5769,10 +5744,10 @@
         </is>
       </c>
       <c r="AC41" t="n">
-        <v>3.914166667</v>
+        <v>4.208406</v>
       </c>
       <c r="AD41" t="n">
-        <v>-76.2925</v>
+        <v>-76.31959500000001</v>
       </c>
     </row>
     <row r="42">
@@ -5787,42 +5762,42 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CRISTOBAL COLÓN</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MANUEL ANTONIO SANCLEMENTE</t>
+          <t>INSTITUCION EDUCATIVA INTEGRADA DE TRUJILLO</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>276111001087</t>
+          <t>176828000064</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -5832,30 +5807,30 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>VDA GUADUALEJO</t>
+          <t>KR 18 15 27</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.38</v>
+        <v>0.67</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.54</v>
+        <v>44.3</v>
       </c>
       <c r="R42" t="n">
-        <v>9.1</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="S42" t="n">
-        <v>2.8</v>
+        <v>48.5</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -5879,12 +5854,12 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Calle 4A</t>
+          <t>Carrera 18</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -5893,10 +5868,10 @@
         </is>
       </c>
       <c r="AC42" t="n">
-        <v>3.893611111</v>
+        <v>4.210077</v>
       </c>
       <c r="AD42" t="n">
-        <v>-76.29111</v>
+        <v>-76.319047</v>
       </c>
     </row>
     <row r="43">
@@ -5922,64 +5897,74 @@
         <v>13</v>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>MANUEL ANTONIO SANCLEMENTE - SEDE PRINCIPAL</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MANUEL ANTONIO SANCLEMENTE</t>
+          <t>INSTITUCION EDUCATIVA SAN ISIDRO</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>176111000515</t>
+          <t>276828000174</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>CL 4 A 1 E 26</t>
+          <t>CORREGIMIENTO EL TABOR PUENTE BLANCO</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.54</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.14</v>
+        <v>69.08</v>
       </c>
       <c r="R43" t="n">
-        <v>9.1</v>
+        <v>146.3</v>
       </c>
       <c r="S43" t="n">
-        <v>2.8</v>
+        <v>74.2</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Habitable</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -6003,12 +5988,12 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 30 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Calle 4</t>
+          <t>TRUJILLO - LA SONORA CRUCE VIA 23VL13-1 K64+160</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -6017,10 +6002,10 @@
         </is>
       </c>
       <c r="AC43" t="n">
-        <v>3.89307</v>
+        <v>4.210564</v>
       </c>
       <c r="AD43" t="n">
-        <v>-76.29131</v>
+        <v>-76.38158300000001</v>
       </c>
     </row>
     <row r="44">
@@ -6050,42 +6035,42 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>ANGEL CUADROS - SEDE PRINCIPAL</t>
+          <t>SEDE INSTITUTO CAMPESTRE SANTA CECILIA</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ANGEL CUADROS</t>
+          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>276111000153</t>
+          <t>176834000599</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>CORREG ZANJON-HONDO</t>
+          <t>IND CALLE 27 NO 6AW 240</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -6094,25 +6079,25 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>14.84</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.16</v>
+        <v>32.44</v>
       </c>
       <c r="R44" t="n">
-        <v>42.4</v>
+        <v>82.5</v>
       </c>
       <c r="S44" t="n">
-        <v>28.8</v>
+        <v>59.6</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -6127,7 +6112,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 78 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 50 m de esa vía.</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -6136,10 +6121,10 @@
         </is>
       </c>
       <c r="AC44" t="n">
-        <v>3.845303584</v>
+        <v>4.090555556</v>
       </c>
       <c r="AD44" t="n">
-        <v>-76.30364</v>
+        <v>-76.22221999999999</v>
       </c>
     </row>
     <row r="45">
@@ -6169,27 +6154,27 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ANTONIO GUENDICA</t>
+          <t>ALFREDO GARRIDO TOVAR</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ANGEL CUADROS</t>
+          <t>INSTITUCION EDUCATIVA ALFREDO GARRIDO TOVAR</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>276111000811</t>
+          <t>276616000654</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>RIOFRIO</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -6199,12 +6184,12 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>QUEBRADASECA</t>
+          <t>CORREG PORTUGAL DE PIEDRAS</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Tulua</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -6213,45 +6198,55 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>4.16</v>
+        <v>32.44</v>
       </c>
       <c r="Q45" t="n">
-        <v>23.43</v>
+        <v>40.13</v>
       </c>
       <c r="R45" t="n">
-        <v>42.4</v>
+        <v>82.5</v>
       </c>
       <c r="S45" t="n">
-        <v>28.8</v>
+        <v>59.6</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>No habitable</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «trunk»). La sede queda a 37 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Troncal de Occidente</t>
+          <t>PORTUGAL DE PIEDRAS - CRUCE VIA 23VL13</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6260,10 +6255,10 @@
         </is>
       </c>
       <c r="AC45" t="n">
-        <v>3.850833</v>
+        <v>4.0553</v>
       </c>
       <c r="AD45" t="n">
-        <v>-76.29722</v>
+        <v>-76.35465000000001</v>
       </c>
     </row>
     <row r="46">
@@ -6680,7 +6675,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>LUIS CARLOS PEÑA</t>
+          <t>FABIO SALAZAR GOMEZ</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6690,7 +6685,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>276147000583</t>
+          <t>276147001083</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6705,7 +6700,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>CORREG CAUCA</t>
+          <t>VDA GUANABANO</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6719,16 +6714,16 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>11.2</v>
+        <v>20.37</v>
       </c>
       <c r="Q49" t="n">
-        <v>12.67</v>
+        <v>20.39</v>
       </c>
       <c r="R49" t="n">
-        <v>23.9</v>
+        <v>40.8</v>
       </c>
       <c r="S49" t="n">
-        <v>9.9</v>
+        <v>15.4</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -6742,7 +6737,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -6752,12 +6747,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 3 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>Carrera 2</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 7 m de esa vía.</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -6766,10 +6756,10 @@
         </is>
       </c>
       <c r="AC49" t="n">
-        <v>4.764444444</v>
+        <v>4.764122</v>
       </c>
       <c r="AD49" t="n">
-        <v>-75.95083</v>
+        <v>-75.966184</v>
       </c>
     </row>
     <row r="50">
@@ -6804,7 +6794,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FABIO SALAZAR GOMEZ</t>
+          <t>LUIS CARLOS PEÑA</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6814,7 +6804,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>276147001083</t>
+          <t>276147000583</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6829,7 +6819,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>VDA GUANABANO</t>
+          <t>CORREG CAUCA</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -6843,16 +6833,16 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>20.37</v>
+        <v>41.64</v>
       </c>
       <c r="Q50" t="n">
-        <v>20.39</v>
+        <v>47.87</v>
       </c>
       <c r="R50" t="n">
-        <v>40.8</v>
+        <v>89.5</v>
       </c>
       <c r="S50" t="n">
-        <v>15.4</v>
+        <v>33.6</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -6866,17 +6856,17 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 7 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -6885,10 +6875,10 @@
         </is>
       </c>
       <c r="AC50" t="n">
-        <v>4.764122</v>
+        <v>4.720727</v>
       </c>
       <c r="AD50" t="n">
-        <v>-75.966184</v>
+        <v>-75.996379</v>
       </c>
     </row>
     <row r="51">
@@ -6965,10 +6955,10 @@
         <v>44.94</v>
       </c>
       <c r="Q51" t="n">
-        <v>9.27</v>
+        <v>9.06</v>
       </c>
       <c r="R51" t="n">
-        <v>97.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="S51" t="n">
         <v>39.8</v>
@@ -7081,13 +7071,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>9.27</v>
+        <v>9.06</v>
       </c>
       <c r="Q52" t="n">
-        <v>43.73</v>
+        <v>43.82</v>
       </c>
       <c r="R52" t="n">
-        <v>97.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="S52" t="n">
         <v>39.8</v>
@@ -7104,7 +7094,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -7114,7 +7104,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 179 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 11 m de esa vía.</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7123,10 +7113,10 @@
         </is>
       </c>
       <c r="AC52" t="n">
-        <v>4.660883219</v>
+        <v>4.658657</v>
       </c>
       <c r="AD52" t="n">
-        <v>-75.88415999999999</v>
+        <v>-75.88515599999999</v>
       </c>
     </row>
     <row r="53">
@@ -8897,13 +8887,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>23.24</v>
+        <v>23.45</v>
       </c>
       <c r="Q66" t="n">
-        <v>8.890000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="R66" t="n">
-        <v>100.3</v>
+        <v>100.4</v>
       </c>
       <c r="S66" t="n">
         <v>53.5</v>
@@ -8930,7 +8920,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 2 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 38 m de esa vía.</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
@@ -8939,10 +8929,10 @@
         </is>
       </c>
       <c r="AC66" t="n">
-        <v>4.708390336</v>
+        <v>4.7075452</v>
       </c>
       <c r="AD66" t="n">
-        <v>-75.87908</v>
+        <v>-75.8790746</v>
       </c>
     </row>
     <row r="67">
@@ -9016,13 +9006,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>8.890000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="Q67" t="n">
         <v>68.20999999999999</v>
       </c>
       <c r="R67" t="n">
-        <v>100.3</v>
+        <v>100.4</v>
       </c>
       <c r="S67" t="n">
         <v>53.5</v>
@@ -12183,10 +12173,10 @@
         <v>27</v>
       </c>
       <c r="D11" t="n">
-        <v>18.7</v>
+        <v>21.4</v>
       </c>
       <c r="E11" t="n">
-        <v>739</v>
+        <v>816</v>
       </c>
       <c r="F11" t="n">
         <v>14</v>
@@ -12208,10 +12198,10 @@
         <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>27.1</v>
       </c>
       <c r="E12" t="n">
-        <v>750</v>
+        <v>774</v>
       </c>
       <c r="F12" t="n">
         <v>13</v>

--- a/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
+++ b/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>POLICARPA SALAVARRIETA</t>
+          <t>ALFONSO ZAWADZKY</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>176890000020</t>
+          <t>176890000305</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>KR 6 6 67</t>
+          <t>KR 5 5 79</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.37</v>
+        <v>1.08</v>
       </c>
       <c r="R15" t="n">
         <v>3.1</v>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Peligro de colapso</t>
+          <t>No habitable</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Carrera 6</t>
+          <t>Calle 6</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="AC15" t="n">
-        <v>3.85991597259148</v>
+        <v>3.86056963997</v>
       </c>
       <c r="AD15" t="n">
-        <v>-76.38388046730552</v>
+        <v>-76.38430955440001</v>
       </c>
     </row>
     <row r="16">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ALFONSO ZAWADZKY</t>
+          <t>POLICARPA SALAVARRIETA</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>176890000305</t>
+          <t>176890000020</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>KR 5 5 79</t>
+          <t>KR 6 6 67</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.37</v>
+        <v>1.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.99</v>
+        <v>1.25</v>
       </c>
       <c r="R16" t="n">
         <v>3.1</v>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>No habitable</t>
+          <t>Peligro de colapso</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2515,32 +2515,32 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 15 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 19 m de esa vía.</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Calle 6</t>
+          <t>Carrera 6</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>3.86056963997</v>
+        <v>3.859774</v>
       </c>
       <c r="AD16" t="n">
-        <v>-76.38430955440001</v>
+        <v>-76.383831</v>
       </c>
     </row>
     <row r="17">
@@ -4020,16 +4020,16 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4.38</v>
+        <v>11.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.54</v>
+        <v>7.13</v>
       </c>
       <c r="R28" t="n">
-        <v>9.1</v>
+        <v>23.3</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4053,12 +4053,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Calle 4A</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 24 m de esa vía.</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4067,10 +4062,10 @@
         </is>
       </c>
       <c r="AC28" t="n">
-        <v>3.893611111</v>
+        <v>3.888313</v>
       </c>
       <c r="AD28" t="n">
-        <v>-76.29111</v>
+        <v>-76.267938</v>
       </c>
     </row>
     <row r="29">
@@ -4144,16 +4139,16 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.54</v>
+        <v>7.13</v>
       </c>
       <c r="Q29" t="n">
         <v>4.14</v>
       </c>
       <c r="R29" t="n">
-        <v>9.1</v>
+        <v>23.3</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -6079,16 +6074,16 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>9.890000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="Q44" t="n">
-        <v>32.44</v>
+        <v>31.51</v>
       </c>
       <c r="R44" t="n">
-        <v>82.5</v>
+        <v>80</v>
       </c>
       <c r="S44" t="n">
-        <v>59.6</v>
+        <v>59.1</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -6102,17 +6097,22 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 50 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 29 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Calle 25</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="AC44" t="n">
-        <v>4.090555556</v>
+        <v>4.0892334</v>
       </c>
       <c r="AD44" t="n">
-        <v>-76.22221999999999</v>
+        <v>-76.2211688</v>
       </c>
     </row>
     <row r="45">
@@ -6198,16 +6198,16 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>32.44</v>
+        <v>31.51</v>
       </c>
       <c r="Q45" t="n">
         <v>40.13</v>
       </c>
       <c r="R45" t="n">
-        <v>82.5</v>
+        <v>80</v>
       </c>
       <c r="S45" t="n">
-        <v>59.6</v>
+        <v>59.1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -12173,10 +12173,10 @@
         <v>27</v>
       </c>
       <c r="D11" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="E11" t="n">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="F11" t="n">
         <v>14</v>

--- a/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
+++ b/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
@@ -9602,32 +9602,32 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>JOSE EUSEBIO CARO</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA INMACULADA CONCEPCION</t>
+          <t>INSTITUCION EDUCATIVA ABSALON TORRES CAMACHO</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>276130000288</t>
+          <t>176275000125</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>CANDELARIA</t>
+          <t>FLORIDA</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>CR 12 NO 10-81</t>
+          <t>CR 21 NO 9-89</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -9641,26 +9641,16 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>11.66</v>
+        <v>27.65</v>
       </c>
       <c r="Q72" t="n">
-        <v>8.539999999999999</v>
+        <v>28.95</v>
       </c>
       <c r="R72" t="n">
-        <v>20.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="S72" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>44</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -9684,12 +9674,12 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 23 m de esa vía.</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>CALLEJON FLORO MERCADO CRUCE VIA 13025VL04-2E</t>
+          <t>Calle 10</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
@@ -9698,10 +9688,10 @@
         </is>
       </c>
       <c r="AC72" t="n">
-        <v>3.39537597879</v>
+        <v>3.32644406118</v>
       </c>
       <c r="AD72" t="n">
-        <v>-76.3859481842</v>
+        <v>-76.23742270629999</v>
       </c>
     </row>
     <row r="73">
@@ -9720,14 +9710,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -9736,32 +9726,32 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>JOSE EUSEBIO CARO</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ABSALON TORRES CAMACHO</t>
+          <t>INSTITUCION EDUCATIVA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>176275000125</t>
+          <t>276130000288</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>FLORIDA</t>
+          <t>CANDELARIA</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>CR 21 NO 9-89</t>
+          <t>CR 12 NO 10-81</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -9771,20 +9761,30 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>27.65</v>
+        <v>28.95</v>
       </c>
       <c r="Q73" t="n">
-        <v>50.58</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="R73" t="n">
-        <v>119.1</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="S73" t="n">
-        <v>65.8</v>
+        <v>44</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>No habitable</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -9808,12 +9808,12 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 23 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Calle 10</t>
+          <t>CALLEJON FLORO MERCADO CRUCE VIA 13025VL04-2E</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
@@ -9822,10 +9822,10 @@
         </is>
       </c>
       <c r="AC73" t="n">
-        <v>3.32644406118</v>
+        <v>3.39537597879</v>
       </c>
       <c r="AD73" t="n">
-        <v>-76.23742270629999</v>
+        <v>-76.3859481842</v>
       </c>
     </row>
     <row r="74">
@@ -9851,7 +9851,7 @@
         <v>4</v>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9899,16 +9899,16 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>50.58</v>
+        <v>60.37</v>
       </c>
       <c r="Q74" t="n">
-        <v>40.86</v>
+        <v>40.02</v>
       </c>
       <c r="R74" t="n">
-        <v>119.1</v>
+        <v>117.8</v>
       </c>
       <c r="S74" t="n">
-        <v>65.8</v>
+        <v>61.6</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -9932,19 +9932,19 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 129 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 35 m de esa vía.</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC74" t="n">
-        <v>3.499130225</v>
+        <v>3.496808</v>
       </c>
       <c r="AD74" t="n">
-        <v>-76.18842022</v>
+        <v>-76.189471</v>
       </c>
     </row>
     <row r="75">
@@ -9963,14 +9963,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -9979,17 +9979,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>NIÑA MARIA</t>
+          <t>ROSARIO DE FATIMA</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DEL PALMAR</t>
+          <t>INSTITUCION EDUCATIVA TABLONES</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>176520002261</t>
+          <t>276520000742</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -9999,76 +9999,76 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>KR 26 37 01</t>
+          <t>CORREG LA BOLSA</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
+          <t>Candelaria</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>Palmira</t>
-        </is>
-      </c>
       <c r="P75" t="n">
-        <v>1.99</v>
+        <v>40.02</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.75</v>
+        <v>17.42</v>
       </c>
       <c r="R75" t="n">
-        <v>6.4</v>
+        <v>117.8</v>
       </c>
       <c r="S75" t="n">
-        <v>1.9</v>
+        <v>61.6</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 21 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Carrera 26</t>
+          <t>La Bolsa</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC75" t="n">
-        <v>3.53399314013</v>
+        <v>3.555961</v>
       </c>
       <c r="AD75" t="n">
-        <v>-76.2962377697</v>
+        <v>-76.23436599999999</v>
       </c>
     </row>
     <row r="76">
@@ -10094,7 +10094,7 @@
         <v>5</v>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>LICEO FEMENINO</t>
+          <t>NIÑA MARIA</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>176520000489</t>
+          <t>176520002261</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>CR 28 NO 37 81</t>
+          <t>KR 26 37 01</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -10142,16 +10142,16 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.66</v>
+        <v>2.01</v>
       </c>
       <c r="R76" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="S76" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 43 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 21 m de esa vía.</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Carrera 28</t>
+          <t>Carrera 26</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
@@ -10189,10 +10189,10 @@
         </is>
       </c>
       <c r="AC76" t="n">
-        <v>3.53438389943</v>
+        <v>3.53399314013</v>
       </c>
       <c r="AD76" t="n">
-        <v>-76.2982293309</v>
+        <v>-76.2962377697</v>
       </c>
     </row>
     <row r="77">
@@ -10760,13 +10760,13 @@
         <v>10.39</v>
       </c>
       <c r="Q81" t="n">
-        <v>47.5</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="R81" t="n">
-        <v>100.6</v>
+        <v>21.8</v>
       </c>
       <c r="S81" t="n">
-        <v>55.7</v>
+        <v>7.6</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -10842,17 +10842,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>MARCO FIDEL SUAREZ</t>
+          <t>LICEO FEMENINO</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TABLONES</t>
+          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DEL PALMAR</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>276520001684</t>
+          <t>176520000489</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>VDA LA ESPERANZA</t>
+          <t>CR 28 NO 37 81</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -10881,20 +10881,30 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>47.5</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="Q82" t="n">
-        <v>42.74</v>
+        <v>2.66</v>
       </c>
       <c r="R82" t="n">
-        <v>100.6</v>
+        <v>21.8</v>
       </c>
       <c r="S82" t="n">
-        <v>55.7</v>
+        <v>7.6</v>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
@@ -10904,19 +10914,24 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 9 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 43 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Carrera 28</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC82" t="n">
-        <v>3.610511</v>
+        <v>3.53438389943</v>
       </c>
       <c r="AD82" t="n">
-        <v>-76.155193</v>
+        <v>-76.2982293309</v>
       </c>
     </row>
     <row r="83">
@@ -10993,13 +11008,13 @@
         <v>33.72</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.14</v>
+        <v>22.95</v>
       </c>
       <c r="R83" t="n">
-        <v>53.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="S83" t="n">
-        <v>28.7</v>
+        <v>56.1</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -11075,7 +11090,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>ROSARIO DE FATIMA</t>
+          <t>MARCO FIDEL SUAREZ</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -11085,7 +11100,7 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>276520000742</t>
+          <t>276520001684</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -11100,7 +11115,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>CORREG LA BOLSA</t>
+          <t>VDA LA ESPERANZA</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -11114,45 +11129,30 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.14</v>
+        <v>22.95</v>
       </c>
       <c r="Q84" t="n">
-        <v>17.42</v>
+        <v>42.74</v>
       </c>
       <c r="R84" t="n">
-        <v>53.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="S84" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Colapso parcial</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Critico</t>
-        </is>
+        <v>56.1</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 18 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>La Bolsa</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 9 m de esa vía.</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
@@ -11161,10 +11161,10 @@
         </is>
       </c>
       <c r="AC84" t="n">
-        <v>3.555961</v>
+        <v>3.610511</v>
       </c>
       <c r="AD84" t="n">
-        <v>-76.23436599999999</v>
+        <v>-76.155193</v>
       </c>
     </row>
     <row r="85">
@@ -12223,10 +12223,10 @@
         <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="E13" t="n">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>

--- a/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
+++ b/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan'!$A$1:$AD$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan'!$A$1:$AI$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD91"/>
+  <dimension ref="A1:AI91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,55 +556,80 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Concepto (tablero del Valle)</t>
+          <t>Especialidad de la visita</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>Concepto técnico (tablero del Valle)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>Dictamen</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Estado (MEN)</t>
-        </is>
-      </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>Restringido en la ficha</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Reporte rector al MEN</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>Nivel de afectación (MEN)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Reporte rector a la Secretaría del Valle</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Reporte FFIE 2026</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Marca en el mapa</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Tipo de vía</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Por qué</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Vía de acceso</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Coordenada en revisión</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Latitud</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Longitud</t>
         </is>
@@ -692,40 +717,40 @@
       <c r="S2" t="n">
         <v>35.4</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC2" t="n">
+      <c r="AH2" t="n">
         <v>3.573823</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AI2" t="n">
         <v>-76.48081000000001</v>
       </c>
     </row>
@@ -811,45 +836,45 @@
       <c r="S3" t="n">
         <v>35.4</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>Calle 10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC3" t="n">
+      <c r="AH3" t="n">
         <v>3.51115</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AI3" t="n">
         <v>-76.51866</v>
       </c>
     </row>
@@ -935,40 +960,45 @@
       <c r="S4" t="n">
         <v>31.2</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>rojo</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 3 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC4" t="n">
+      <c r="AH4" t="n">
         <v>3.5643709</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AI4" t="n">
         <v>-76.4995401</v>
       </c>
     </row>
@@ -1054,45 +1084,45 @@
       <c r="S5" t="n">
         <v>31.2</v>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 4 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>Calle 7B</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC5" t="n">
+      <c r="AH5" t="n">
         <v>3.5690111</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AI5" t="n">
         <v>-76.4979953</v>
       </c>
     </row>
@@ -1180,53 +1210,63 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>EL CARMEN - VIA SIMON BOLIVAR CRUCE VIA 3201</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC6" t="n">
+      <c r="AH6" t="n">
         <v>3.54959</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AI6" t="n">
         <v>-76.632525</v>
       </c>
     </row>
@@ -1314,53 +1354,63 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL - GEOLOGO</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Colapso parcial</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 16 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>LA JULIA CRUCE VIA 3201</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC7" t="n">
+      <c r="AH7" t="n">
         <v>3.574795</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AI7" t="n">
         <v>-76.64960499999999</v>
       </c>
     </row>
@@ -1448,53 +1498,63 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>EL CARMEN - VIA SIMON BOLIVAR CRUCE VIA 3201</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC8" t="n">
+      <c r="AH8" t="n">
         <v>3.5527246</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AI8" t="n">
         <v>-76.6515909</v>
       </c>
     </row>
@@ -1582,48 +1642,63 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL - GEOLOGO</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Colapso parcial</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>amarillo</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 9 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC9" t="n">
+      <c r="AH9" t="n">
         <v>3.6041469</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AI9" t="n">
         <v>-76.6490644</v>
       </c>
     </row>
@@ -1711,48 +1786,58 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC10" t="n">
+      <c r="AH10" t="n">
         <v>3.595044</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AI10" t="n">
         <v>-76.665947</v>
       </c>
     </row>
@@ -1840,48 +1925,58 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Sin diagnóstico — espera verificación</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC11" t="n">
+      <c r="AH11" t="n">
         <v>3.606151</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AI11" t="n">
         <v>-76.70789000000001</v>
       </c>
     </row>
@@ -1969,53 +2064,63 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Sin diagnóstico — espera verificación</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>Carrera 2</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC12" t="n">
+      <c r="AH12" t="n">
         <v>3.6489149</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AI12" t="n">
         <v>-76.56672399999999</v>
       </c>
     </row>
@@ -2103,53 +2208,63 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Riesgo inminente de colapso</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 49 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AF13" t="inlineStr">
         <is>
           <t>Diagonal 1</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC13" t="n">
+      <c r="AH13" t="n">
         <v>3.6478665</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AI13" t="n">
         <v>-76.56629270000001</v>
       </c>
     </row>
@@ -2237,53 +2352,63 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 7 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AF14" t="inlineStr">
         <is>
           <t>SANTA MARIA - EL LIMONAR CRUCE VIA 23319VL02 K5+555</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC14" t="n">
+      <c r="AH14" t="n">
         <v>3.63352</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AI14" t="n">
         <v>-76.715591</v>
       </c>
     </row>
@@ -2371,53 +2496,68 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Riesgo inminente de colapso</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>amarillo</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AF15" t="inlineStr">
         <is>
           <t>Calle 6</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC15" t="n">
+      <c r="AH15" t="n">
         <v>3.86056963997</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AI15" t="n">
         <v>-76.38430955440001</v>
       </c>
     </row>
@@ -2505,53 +2645,68 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>no estructural: No habitable · estructural: No habitable</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 19 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>Carrera 6</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC16" t="n">
+      <c r="AH16" t="n">
         <v>3.859774</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AI16" t="n">
         <v>-76.383831</v>
       </c>
     </row>
@@ -2639,53 +2794,63 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL - GEOLOGO</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Colapso parcial</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
         <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 23 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>MEDIACANOA - MIRAVALLE - CAMPO ALEGRE - CRUCE VIA 2302</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC17" t="n">
+      <c r="AH17" t="n">
         <v>3.962278</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AI17" t="n">
         <v>-76.40526699999999</v>
       </c>
     </row>
@@ -2773,53 +2938,63 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 24 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>MEDIACANOA - PRIMAVERA</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC18" t="n">
+      <c r="AH18" t="n">
         <v>3.900556391368746</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AI18" t="n">
         <v>-76.37662112784321</v>
       </c>
     </row>
@@ -2907,53 +3082,73 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>estado general: No habitable · no estructural: No habitable</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Colapso parcial</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>rojo, verde</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 31 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AF19" t="inlineStr">
         <is>
           <t>Carrera 9</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC19" t="n">
+      <c r="AH19" t="n">
         <v>3.82299113556</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AI19" t="n">
         <v>-76.52146344489999</v>
       </c>
     </row>
@@ -3041,53 +3236,63 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL - GEOLOGO</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Colapso parcial</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AF20" t="inlineStr">
         <is>
           <t>LA GUAIRA - KM113- LOMITAS</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC20" t="n">
+      <c r="AH20" t="n">
         <v>3.6919524</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AI20" t="n">
         <v>-76.63414659999999</v>
       </c>
     </row>
@@ -3175,53 +3380,68 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>Habitable</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Concepto Habitable aprobado: confirmar con la secretaría si se repite la evaluación</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 32 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AF21" t="inlineStr">
         <is>
           <t>EL TAMBOR - LA RIVERA - OCACHE</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AG21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC21" t="n">
+      <c r="AH21" t="n">
         <v>3.741864</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AI21" t="n">
         <v>-76.49940700000001</v>
       </c>
     </row>
@@ -3307,40 +3527,40 @@
       <c r="S22" t="n">
         <v>23.2</v>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC22" t="n">
+      <c r="AH22" t="n">
         <v>3.8504316</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AI22" t="n">
         <v>-76.29718</v>
       </c>
     </row>
@@ -3426,40 +3646,40 @@
       <c r="S23" t="n">
         <v>23.2</v>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC23" t="n">
+      <c r="AH23" t="n">
         <v>3.870531</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AI23" t="n">
         <v>-76.29683900000001</v>
       </c>
     </row>
@@ -3545,45 +3765,45 @@
       <c r="S24" t="n">
         <v>2</v>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 25 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AF24" t="inlineStr">
         <is>
           <t>Carrera 9</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC24" t="n">
+      <c r="AH24" t="n">
         <v>3.892781656</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AI24" t="n">
         <v>-76.29845</v>
       </c>
     </row>
@@ -3669,40 +3889,40 @@
       <c r="S25" t="n">
         <v>2</v>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC25" t="n">
+      <c r="AH25" t="n">
         <v>3.894397016</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AI25" t="n">
         <v>-76.29777</v>
       </c>
     </row>
@@ -3788,40 +4008,40 @@
       <c r="S26" t="n">
         <v>3.3</v>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC26" t="n">
+      <c r="AH26" t="n">
         <v>3.9055</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AI26" t="n">
         <v>-76.29489</v>
       </c>
     </row>
@@ -3907,45 +4127,45 @@
       <c r="S27" t="n">
         <v>3.3</v>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 29 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AF27" t="inlineStr">
         <is>
           <t>Carrera 10</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC27" t="n">
+      <c r="AH27" t="n">
         <v>3.90894</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AI27" t="n">
         <v>-76.29465</v>
       </c>
     </row>
@@ -4031,40 +4251,40 @@
       <c r="S28" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 24 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC28" t="n">
+      <c r="AH28" t="n">
         <v>3.888313</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AI28" t="n">
         <v>-76.267938</v>
       </c>
     </row>
@@ -4150,45 +4370,45 @@
       <c r="S29" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 30 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AF29" t="inlineStr">
         <is>
           <t>Calle 4</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC29" t="n">
+      <c r="AH29" t="n">
         <v>3.89307</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AI29" t="n">
         <v>-76.29131</v>
       </c>
     </row>
@@ -4274,45 +4494,45 @@
       <c r="S30" t="n">
         <v>20.4</v>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «trunk»). La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AF30" t="inlineStr">
         <is>
           <t>Troncal de Occidente</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AG30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC30" t="n">
+      <c r="AH30" t="n">
         <v>3.9553497</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AI30" t="n">
         <v>-76.2707521</v>
       </c>
     </row>
@@ -4398,45 +4618,45 @@
       <c r="S31" t="n">
         <v>20.4</v>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AF31" t="inlineStr">
         <is>
           <t>Carrera 27</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC31" t="n">
+      <c r="AH31" t="n">
         <v>3.911822</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AI31" t="n">
         <v>-76.30735</v>
       </c>
     </row>
@@ -4522,40 +4742,45 @@
       <c r="S32" t="n">
         <v>77.5</v>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>amarillo</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 90 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC32" t="n">
+      <c r="AH32" t="n">
         <v>3.88102932</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AI32" t="n">
         <v>-76.09909786</v>
       </c>
     </row>
@@ -4641,45 +4866,50 @@
       <c r="S33" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>rojo, verde</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AF33" t="inlineStr">
         <is>
           <t>Calle 25</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC33" t="n">
+      <c r="AH33" t="n">
         <v>3.911563</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AI33" t="n">
         <v>-76.291687</v>
       </c>
     </row>
@@ -4767,53 +4997,68 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>estructural: No habitable</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Colapso parcial</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AF34" t="inlineStr">
         <is>
           <t>Calle 6</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC34" t="n">
+      <c r="AH34" t="n">
         <v>4.165067</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AI34" t="n">
         <v>-76.16943499999999</v>
       </c>
     </row>
@@ -4901,53 +5146,63 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Sin diagnóstico — espera verificación</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AF35" t="inlineStr">
         <is>
           <t>Calle 5</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC35" t="n">
+      <c r="AH35" t="n">
         <v>4.329633623</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AI35" t="n">
         <v>-75.82531724</v>
       </c>
     </row>
@@ -5035,53 +5290,63 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Riesgo inminente de colapso</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AF36" t="inlineStr">
         <is>
           <t>Carrera 10</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC36" t="n">
+      <c r="AH36" t="n">
         <v>4.3959229</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AI36" t="n">
         <v>-76.0708454</v>
       </c>
     </row>
@@ -5169,53 +5434,68 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>verde</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AF37" t="inlineStr">
         <is>
           <t>Carrera 5</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC37" t="n">
+      <c r="AH37" t="n">
         <v>4.412260842287796</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AI37" t="n">
         <v>-76.15737540436542</v>
       </c>
     </row>
@@ -5303,53 +5583,68 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>estructural: Uso restringido</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 43 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AF38" t="inlineStr">
         <is>
           <t>BOLIVAR CRUCE CON VIA DE INVIAS 2302 EN TRAMO 23020 INICIO A 52m DE INICIO DE VIA 10023VL02B</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC38" t="n">
+      <c r="AH38" t="n">
         <v>4.340805</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AI38" t="n">
         <v>-76.17979800000001</v>
       </c>
     </row>
@@ -5435,45 +5730,50 @@
       <c r="S39" t="n">
         <v>57</v>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>rojo</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AF39" t="inlineStr">
         <is>
           <t>Calle 27</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AG39" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC39" t="n">
+      <c r="AH39" t="n">
         <v>4.088515899</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AI39" t="n">
         <v>-76.22009</v>
       </c>
     </row>
@@ -5561,53 +5861,63 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>en revisión de la mesa</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Riesgo inminente de colapso</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AF40" t="inlineStr">
         <is>
           <t>SALONICA CRUCE CON VIA 23VL13-1 EN K44+300</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC40" t="n">
+      <c r="AH40" t="n">
         <v>4.1258314</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AI40" t="n">
         <v>-76.3722336</v>
       </c>
     </row>
@@ -5695,53 +6005,68 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL - GEOLOGO</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Colapso parcial</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>amarillo</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AF41" t="inlineStr">
         <is>
           <t>Carrera 18</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AG41" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC41" t="n">
+      <c r="AH41" t="n">
         <v>4.208406</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AI41" t="n">
         <v>-76.31959500000001</v>
       </c>
     </row>
@@ -5827,45 +6152,55 @@
       <c r="S42" t="n">
         <v>48.5</v>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>PATOLOGIA ESTRUCTURAL - GEOLOGO</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>rojo</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="AD42" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AE42" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AF42" t="inlineStr">
         <is>
           <t>Carrera 18</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AG42" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC42" t="n">
+      <c r="AH42" t="n">
         <v>4.210077</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AI42" t="n">
         <v>-76.319047</v>
       </c>
     </row>
@@ -5953,53 +6288,73 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL - GEOLOGO</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
           <t>Habitable</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>estado general: Uso restringido · no estructural: Uso restringido · habitabilidad: Uso restringido</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Concepto Habitable aprobado: confirmar con la secretaría si se repite la evaluación</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="AD43" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AE43" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AF43" t="inlineStr">
         <is>
           <t>TRUJILLO - LA SONORA CRUCE VIA 23VL13-1 K64+160</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AG43" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC43" t="n">
+      <c r="AH43" t="n">
         <v>4.210564</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AI43" t="n">
         <v>-76.38158300000001</v>
       </c>
     </row>
@@ -6085,45 +6440,45 @@
       <c r="S44" t="n">
         <v>59.1</v>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AE44" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 29 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AF44" t="inlineStr">
         <is>
           <t>Calle 25</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AG44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC44" t="n">
+      <c r="AH44" t="n">
         <v>4.0892334</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AI44" t="n">
         <v>-76.2211688</v>
       </c>
     </row>
@@ -6211,53 +6566,63 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Colapso parcial</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AE45" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AF45" t="inlineStr">
         <is>
           <t>PORTUGAL DE PIEDRAS - CRUCE VIA 23VL13</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AG45" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC45" t="n">
+      <c r="AH45" t="n">
         <v>4.0553</v>
       </c>
-      <c r="AD45" t="n">
+      <c r="AI45" t="n">
         <v>-76.35465000000001</v>
       </c>
     </row>
@@ -6345,48 +6710,68 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
           <t>Habitable</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>geotécnica: Uso restringido</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Sin diagnóstico — espera verificación</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Concepto Habitable aprobado: confirmar con la secretaría si se repite la evaluación</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AE46" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AG46" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC46" t="n">
+      <c r="AH46" t="n">
         <v>3.716456</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AI46" t="n">
         <v>-76.47793299999999</v>
       </c>
     </row>
@@ -6474,53 +6859,68 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>estado general: Uso restringido · no estructural: Uso restringido · entorno: Uso restringido · estructural: Uso restringido</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AE47" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 3 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AF47" t="inlineStr">
         <is>
           <t>Carrera 4</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AG47" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC47" t="n">
+      <c r="AH47" t="n">
         <v>3.699871998710244</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AI47" t="n">
         <v>-76.44279828333418</v>
       </c>
     </row>
@@ -6606,40 +7006,40 @@
       <c r="S48" t="n">
         <v>78.8</v>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AE48" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 29 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AG48" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC48" t="n">
+      <c r="AH48" t="n">
         <v>4.635095</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AI48" t="n">
         <v>-75.871531</v>
       </c>
     </row>
@@ -6725,40 +7125,40 @@
       <c r="S49" t="n">
         <v>15.4</v>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AE49" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 7 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AG49" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC49" t="n">
+      <c r="AH49" t="n">
         <v>4.764122</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AI49" t="n">
         <v>-75.966184</v>
       </c>
     </row>
@@ -6844,40 +7244,40 @@
       <c r="S50" t="n">
         <v>33.6</v>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="AD50" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AE50" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AG50" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC50" t="n">
+      <c r="AH50" t="n">
         <v>4.720727</v>
       </c>
-      <c r="AD50" t="n">
+      <c r="AI50" t="n">
         <v>-75.996379</v>
       </c>
     </row>
@@ -6963,40 +7363,40 @@
       <c r="S51" t="n">
         <v>39.8</v>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="AD51" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AE51" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AG51" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC51" t="n">
+      <c r="AH51" t="n">
         <v>4.647653</v>
       </c>
-      <c r="AD51" t="n">
+      <c r="AI51" t="n">
         <v>-75.894413</v>
       </c>
     </row>
@@ -7082,40 +7482,40 @@
       <c r="S52" t="n">
         <v>39.8</v>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="AD52" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AE52" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 11 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AG52" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC52" t="n">
+      <c r="AH52" t="n">
         <v>4.658657</v>
       </c>
-      <c r="AD52" t="n">
+      <c r="AI52" t="n">
         <v>-75.88515599999999</v>
       </c>
     </row>
@@ -7201,40 +7601,40 @@
       <c r="S53" t="n">
         <v>41.7</v>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AE53" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «primary»). La sede queda a 30 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AG53" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC53" t="n">
+      <c r="AH53" t="n">
         <v>4.711094</v>
       </c>
-      <c r="AD53" t="n">
+      <c r="AI53" t="n">
         <v>-75.858474</v>
       </c>
     </row>
@@ -7320,40 +7720,40 @@
       <c r="S54" t="n">
         <v>41.7</v>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="AC54" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="AD54" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AE54" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 45 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AG54" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC54" t="n">
+      <c r="AH54" t="n">
         <v>4.648227</v>
       </c>
-      <c r="AD54" t="n">
+      <c r="AI54" t="n">
         <v>-75.85445900000001</v>
       </c>
     </row>
@@ -7441,53 +7841,63 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Riesgo inminente de colapso</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="AD55" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AE55" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 13 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AF55" t="inlineStr">
         <is>
           <t>EL VERGEL CRUCE CON VIA 04123VL13-5C EN K6+384</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
+      <c r="AG55" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC55" t="n">
+      <c r="AH55" t="n">
         <v>4.86111676163</v>
       </c>
-      <c r="AD55" t="n">
+      <c r="AI55" t="n">
         <v>-75.99733304110001</v>
       </c>
     </row>
@@ -7575,53 +7985,63 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL - GEOLOGO</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>Colapso total</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Colapso total</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="AD56" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AE56" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 34 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AF56" t="inlineStr">
         <is>
           <t>LA PLAYA CRUCE CON VIA 04123VL13-5G3 EN K3</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
+      <c r="AG56" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC56" t="n">
+      <c r="AH56" t="n">
         <v>4.819842722212309</v>
       </c>
-      <c r="AD56" t="n">
+      <c r="AI56" t="n">
         <v>-76.08934449628445</v>
       </c>
     </row>
@@ -7709,53 +8129,63 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL - GEOLOGO</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="AD57" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AE57" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 3 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AF57" t="inlineStr">
         <is>
           <t>EL REAL PLACER CRUCE CON VIA 0414802VL-G EN K22+316</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
+      <c r="AG57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC57" t="n">
+      <c r="AH57" t="n">
         <v>4.7883859</v>
       </c>
-      <c r="AD57" t="n">
+      <c r="AI57" t="n">
         <v>-76.0724936</v>
       </c>
     </row>
@@ -7843,53 +8273,63 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>Colapso parcial</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="AD58" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AE58" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AF58" t="inlineStr">
         <is>
           <t>LAS BRISAS - EL BRILLANTE</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AG58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC58" t="n">
+      <c r="AH58" t="n">
         <v>4.72634</v>
       </c>
-      <c r="AD58" t="n">
+      <c r="AI58" t="n">
         <v>-76.11562499999999</v>
       </c>
     </row>
@@ -7977,53 +8417,63 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL - GEOLOGO</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>Colapso parcial</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="AD59" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AE59" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AF59" t="inlineStr">
         <is>
           <t>SAN FRANCISCO CRUCE 82323VL02-N K0+000</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
+      <c r="AG59" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC59" t="n">
+      <c r="AH59" t="n">
         <v>4.68415925</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AI59" t="n">
         <v>-76.0351458</v>
       </c>
     </row>
@@ -8111,53 +8561,63 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Colapso parcial</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="AD60" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AE60" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 41 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AF60" t="inlineStr">
         <is>
           <t>Calle 18</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
+      <c r="AG60" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC60" t="n">
+      <c r="AH60" t="n">
         <v>4.60769678</v>
       </c>
-      <c r="AD60" t="n">
+      <c r="AI60" t="n">
         <v>-76.07215911999999</v>
       </c>
     </row>
@@ -8243,40 +8703,50 @@
       <c r="S61" t="n">
         <v>36.4</v>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>PATOLOGIA ESTRUCTURAL - GEOLOGO</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>rojo</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="AD61" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AE61" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 14 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
+      <c r="AG61" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC61" t="n">
+      <c r="AH61" t="n">
         <v>4.64998614</v>
       </c>
-      <c r="AD61" t="n">
+      <c r="AI61" t="n">
         <v>-76.13698533</v>
       </c>
     </row>
@@ -8364,53 +8834,63 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="AD62" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AE62" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 11 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AF62" t="inlineStr">
         <is>
           <t>Calle 13</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
+      <c r="AG62" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC62" t="n">
+      <c r="AH62" t="n">
         <v>4.5307229</v>
       </c>
-      <c r="AD62" t="n">
+      <c r="AI62" t="n">
         <v>-76.1031742</v>
       </c>
     </row>
@@ -8498,53 +8978,63 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="AD63" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AE63" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 14 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AF63" t="inlineStr">
         <is>
           <t>Calle 13</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
+      <c r="AG63" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC63" t="n">
+      <c r="AH63" t="n">
         <v>4.5306222</v>
       </c>
-      <c r="AD63" t="n">
+      <c r="AI63" t="n">
         <v>-76.10365280000001</v>
       </c>
     </row>
@@ -8632,53 +9122,63 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>Colapso total</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Sin diagnóstico — espera verificación</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="AD64" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AE64" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 11 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AF64" t="inlineStr">
         <is>
           <t>Calle 16</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
+      <c r="AG64" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC64" t="n">
+      <c r="AH64" t="n">
         <v>4.53325</v>
       </c>
-      <c r="AD64" t="n">
+      <c r="AI64" t="n">
         <v>-76.1032</v>
       </c>
     </row>
@@ -8766,53 +9266,63 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Riesgo inminente de colapso</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="AD65" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AE65" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AF65" t="inlineStr">
         <is>
           <t>Carrera 8</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
+      <c r="AG65" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC65" t="n">
+      <c r="AH65" t="n">
         <v>4.522653896403604</v>
       </c>
-      <c r="AD65" t="n">
+      <c r="AI65" t="n">
         <v>-76.0369985666723</v>
       </c>
     </row>
@@ -8898,40 +9408,40 @@
       <c r="S66" t="n">
         <v>53.5</v>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="AC66" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="AD66" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AE66" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 38 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
+      <c r="AG66" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC66" t="n">
+      <c r="AH66" t="n">
         <v>4.7075452</v>
       </c>
-      <c r="AD66" t="n">
+      <c r="AI66" t="n">
         <v>-75.8790746</v>
       </c>
     </row>
@@ -9017,40 +9527,40 @@
       <c r="S67" t="n">
         <v>53.5</v>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="AC67" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="AD67" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AE67" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
+      <c r="AG67" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC67" t="n">
+      <c r="AH67" t="n">
         <v>4.681657</v>
       </c>
-      <c r="AD67" t="n">
+      <c r="AI67" t="n">
         <v>-75.889206</v>
       </c>
     </row>
@@ -9136,45 +9646,45 @@
       <c r="S68" t="n">
         <v>61.9</v>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="AC68" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="AD68" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AE68" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 50 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AF68" t="inlineStr">
         <is>
           <t>Vía la Acequia</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
+      <c r="AG68" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC68" t="n">
+      <c r="AH68" t="n">
         <v>3.634558</v>
       </c>
-      <c r="AD68" t="n">
+      <c r="AI68" t="n">
         <v>-76.387384</v>
       </c>
     </row>
@@ -9260,45 +9770,45 @@
       <c r="S69" t="n">
         <v>61.9</v>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="AC69" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="AD69" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AE69" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 39 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AF69" t="inlineStr">
         <is>
           <t>Carrera 9</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
+      <c r="AG69" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC69" t="n">
+      <c r="AH69" t="n">
         <v>3.611331</v>
       </c>
-      <c r="AD69" t="n">
+      <c r="AI69" t="n">
         <v>-76.38498199999999</v>
       </c>
     </row>
@@ -9386,53 +9896,63 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="V70" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="AD70" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AE70" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AF70" t="inlineStr">
         <is>
           <t>Calle 7</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
+      <c r="AG70" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC70" t="n">
+      <c r="AH70" t="n">
         <v>3.407489</v>
       </c>
-      <c r="AD70" t="n">
+      <c r="AI70" t="n">
         <v>-76.34917799999999</v>
       </c>
     </row>
@@ -9520,53 +10040,63 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="V71" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="AD71" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AE71" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AF71" t="inlineStr">
         <is>
           <t>Calle 7</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
+      <c r="AG71" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC71" t="n">
+      <c r="AH71" t="n">
         <v>3.40761667</v>
       </c>
-      <c r="AD71" t="n">
+      <c r="AI71" t="n">
         <v>-76.34858894</v>
       </c>
     </row>
@@ -9652,45 +10182,50 @@
       <c r="S72" t="n">
         <v>44</v>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="AC72" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="AD72" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AE72" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 23 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AF72" t="inlineStr">
         <is>
           <t>Calle 10</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
+      <c r="AG72" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC72" t="n">
+      <c r="AH72" t="n">
         <v>3.32644406118</v>
       </c>
-      <c r="AD72" t="n">
+      <c r="AI72" t="n">
         <v>-76.23742270629999</v>
       </c>
     </row>
@@ -9778,53 +10313,63 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="V73" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Afectación menor</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="AD73" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AE73" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
+      <c r="AF73" t="inlineStr">
         <is>
           <t>CALLEJON FLORO MERCADO CRUCE VIA 13025VL04-2E</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
+      <c r="AG73" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC73" t="n">
+      <c r="AH73" t="n">
         <v>3.39537597879</v>
       </c>
-      <c r="AD73" t="n">
+      <c r="AI73" t="n">
         <v>-76.3859481842</v>
       </c>
     </row>
@@ -9910,40 +10455,40 @@
       <c r="S74" t="n">
         <v>61.6</v>
       </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X74" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="AD74" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AE74" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 35 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
+      <c r="AG74" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC74" t="n">
+      <c r="AH74" t="n">
         <v>3.496808</v>
       </c>
-      <c r="AD74" t="n">
+      <c r="AI74" t="n">
         <v>-76.189471</v>
       </c>
     </row>
@@ -10029,45 +10574,45 @@
       <c r="S75" t="n">
         <v>61.6</v>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="AC75" t="inlineStr">
         <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="AD75" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AE75" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr">
+      <c r="AF75" t="inlineStr">
         <is>
           <t>La Bolsa</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
+      <c r="AG75" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC75" t="n">
+      <c r="AH75" t="n">
         <v>3.555961</v>
       </c>
-      <c r="AD75" t="n">
+      <c r="AI75" t="n">
         <v>-76.23436599999999</v>
       </c>
     </row>
@@ -10153,45 +10698,45 @@
       <c r="S76" t="n">
         <v>1.2</v>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="AC76" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="AD76" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AE76" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 21 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AF76" t="inlineStr">
         <is>
           <t>Carrera 26</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
+      <c r="AG76" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC76" t="n">
+      <c r="AH76" t="n">
         <v>3.53399314013</v>
       </c>
-      <c r="AD76" t="n">
+      <c r="AI76" t="n">
         <v>-76.2962377697</v>
       </c>
     </row>
@@ -10277,45 +10822,45 @@
       <c r="S77" t="n">
         <v>5.8</v>
       </c>
-      <c r="V77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="AC77" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="AD77" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AE77" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AF77" t="inlineStr">
         <is>
           <t>Calle 21</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
+      <c r="AG77" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC77" t="n">
+      <c r="AH77" t="n">
         <v>3.519487</v>
       </c>
-      <c r="AD77" t="n">
+      <c r="AI77" t="n">
         <v>-76.29709</v>
       </c>
     </row>
@@ -10401,40 +10946,40 @@
       <c r="S78" t="n">
         <v>5.8</v>
       </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X78" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="AD78" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AE78" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 17 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
+      <c r="AG78" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC78" t="n">
+      <c r="AH78" t="n">
         <v>3.528177503</v>
       </c>
-      <c r="AD78" t="n">
+      <c r="AI78" t="n">
         <v>-76.28814192999999</v>
       </c>
     </row>
@@ -10520,45 +11065,45 @@
       <c r="S79" t="n">
         <v>5.5</v>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="AC79" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="AD79" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AE79" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 48 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA79" t="inlineStr">
+      <c r="AF79" t="inlineStr">
         <is>
           <t>Carrera 41</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
+      <c r="AG79" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC79" t="n">
+      <c r="AH79" t="n">
         <v>3.528369858</v>
       </c>
-      <c r="AD79" t="n">
+      <c r="AI79" t="n">
         <v>-76.30969955</v>
       </c>
     </row>
@@ -10644,45 +11189,45 @@
       <c r="S80" t="n">
         <v>5.5</v>
       </c>
-      <c r="V80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
+      <c r="Y80" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="AC80" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="AD80" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AE80" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 35 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA80" t="inlineStr">
+      <c r="AF80" t="inlineStr">
         <is>
           <t>Carrera 33A</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
+      <c r="AG80" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC80" t="n">
+      <c r="AH80" t="n">
         <v>3.521358245</v>
       </c>
-      <c r="AD80" t="n">
+      <c r="AI80" t="n">
         <v>-76.30535072000001</v>
       </c>
     </row>
@@ -10768,45 +11313,45 @@
       <c r="S81" t="n">
         <v>7.6</v>
       </c>
-      <c r="V81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="AC81" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="AD81" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AE81" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AF81" t="inlineStr">
         <is>
           <t>Carrera 32</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
+      <c r="AG81" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC81" t="n">
+      <c r="AH81" t="n">
         <v>3.556083</v>
       </c>
-      <c r="AD81" t="n">
+      <c r="AI81" t="n">
         <v>-76.30073299999999</v>
       </c>
     </row>
@@ -10892,45 +11437,45 @@
       <c r="S82" t="n">
         <v>7.6</v>
       </c>
-      <c r="V82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="AC82" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="AD82" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
+      <c r="AE82" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 43 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr">
+      <c r="AF82" t="inlineStr">
         <is>
           <t>Carrera 28</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
+      <c r="AG82" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC82" t="n">
+      <c r="AH82" t="n">
         <v>3.53438389943</v>
       </c>
-      <c r="AD82" t="n">
+      <c r="AI82" t="n">
         <v>-76.2982293309</v>
       </c>
     </row>
@@ -11016,45 +11561,45 @@
       <c r="S83" t="n">
         <v>56.1</v>
       </c>
-      <c r="V83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="AC83" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="AD83" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AE83" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 37 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr">
+      <c r="AF83" t="inlineStr">
         <is>
           <t>Vía a Tienda Nueva</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
+      <c r="AG83" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC83" t="n">
+      <c r="AH83" t="n">
         <v>3.564564</v>
       </c>
-      <c r="AD83" t="n">
+      <c r="AI83" t="n">
         <v>-76.231579</v>
       </c>
     </row>
@@ -11142,28 +11687,38 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
+          <t>No está en la capa del MEN</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="AD84" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AE84" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 9 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AC84" t="n">
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="AH84" t="n">
         <v>3.610511</v>
       </c>
-      <c r="AD84" t="n">
+      <c r="AI84" t="n">
         <v>-76.155193</v>
       </c>
     </row>
@@ -11251,33 +11806,43 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
+          <t>No está en la capa del MEN</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="AD85" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
+      <c r="AE85" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 16 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA85" t="inlineStr">
+      <c r="AF85" t="inlineStr">
         <is>
           <t>Via Tenjo - Mariala Alta</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
+      <c r="AG85" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC85" t="n">
+      <c r="AH85" t="n">
         <v>3.510825276</v>
       </c>
-      <c r="AD85" t="n">
+      <c r="AI85" t="n">
         <v>-76.14317477</v>
       </c>
     </row>
@@ -11363,40 +11928,40 @@
       <c r="S86" t="n">
         <v>61</v>
       </c>
-      <c r="V86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W86" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="AC86" t="inlineStr">
         <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="AD86" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AE86" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 21 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
+      <c r="AG86" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC86" t="n">
+      <c r="AH86" t="n">
         <v>3.602559</v>
       </c>
-      <c r="AD86" t="n">
+      <c r="AI86" t="n">
         <v>-76.20097800000001</v>
       </c>
     </row>
@@ -11482,40 +12047,40 @@
       <c r="S87" t="n">
         <v>61</v>
       </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X87" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="AD87" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="AE87" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 1330 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
+      <c r="AG87" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC87" t="n">
+      <c r="AH87" t="n">
         <v>3.582859967</v>
       </c>
-      <c r="AD87" t="n">
+      <c r="AI87" t="n">
         <v>-76.15750609</v>
       </c>
     </row>
@@ -11601,40 +12166,40 @@
       <c r="S88" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="V88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W88" t="inlineStr">
+      <c r="Y88" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="AC88" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="AD88" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="AE88" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 272 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AC88" t="n">
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="AH88" t="n">
         <v>3.545813</v>
       </c>
-      <c r="AD88" t="n">
+      <c r="AI88" t="n">
         <v>-76.113687</v>
       </c>
     </row>
@@ -11720,40 +12285,40 @@
       <c r="S89" t="n">
         <v>83.90000000000001</v>
       </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X89" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="AD89" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="AE89" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 352 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
+      <c r="AG89" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC89" t="n">
+      <c r="AH89" t="n">
         <v>3.641394707</v>
       </c>
-      <c r="AD89" t="n">
+      <c r="AI89" t="n">
         <v>-76.05537963</v>
       </c>
     </row>
@@ -11839,40 +12404,40 @@
       <c r="S90" t="n">
         <v>52.2</v>
       </c>
-      <c r="V90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="AC90" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="AD90" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="AE90" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
+      <c r="AG90" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC90" t="n">
+      <c r="AH90" t="n">
         <v>3.58445</v>
       </c>
-      <c r="AD90" t="n">
+      <c r="AI90" t="n">
         <v>-76.425567</v>
       </c>
     </row>
@@ -11958,45 +12523,45 @@
       <c r="S91" t="n">
         <v>52.2</v>
       </c>
-      <c r="V91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W91" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="AC91" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="AD91" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="AE91" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
+      <c r="AG91" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC91" t="n">
+      <c r="AH91" t="n">
         <v>3.571063</v>
       </c>
-      <c r="AD91" t="n">
+      <c r="AI91" t="n">
         <v>-76.397188</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD91"/>
+  <autoFilter ref="A1:AI91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12007,7 +12572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12034,7 +12599,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -12098,88 +12663,75 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Cuadrilla</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Días</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Sedes</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Horas de carretera</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Km</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Noches fuera</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Noches de hotel</t>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cada columna dice de dónde viene el dato. «No reportó al MEN» no quiere decir que la sede no tenga daño: quiere decir que no hay reporte. Todas las sedes del plan se visitan, tengan o no reporte o concepto técnico.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>15</v>
-      </c>
-      <c r="C10" t="n">
-        <v>19</v>
-      </c>
-      <c r="D10" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>992</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" t="n">
-        <v>16</v>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Cuadrilla</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Días</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Sedes</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Horas de carretera</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Km</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Noches fuera</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Noches de hotel</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>21.6</v>
+        <v>33.8</v>
       </c>
       <c r="E11" t="n">
-        <v>822</v>
+        <v>992</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>16</v>
@@ -12188,50 +12740,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" t="n">
+        <v>27</v>
+      </c>
+      <c r="D12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>822</v>
+      </c>
+      <c r="F12" t="n">
         <v>14</v>
       </c>
-      <c r="C12" t="n">
-        <v>20</v>
-      </c>
-      <c r="D12" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>774</v>
-      </c>
-      <c r="F12" t="n">
-        <v>13</v>
-      </c>
       <c r="G12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>18.9</v>
+        <v>27.1</v>
       </c>
       <c r="E13" t="n">
-        <v>572</v>
+        <v>774</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
       </c>
       <c r="G13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>14</v>
+      </c>
+      <c r="C14" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>572</v>
+      </c>
+      <c r="F14" t="n">
+        <v>13</v>
+      </c>
+      <c r="G14" t="n">
         <v>15</v>
       </c>
     </row>

--- a/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
+++ b/public/datos/plan_cuadrillas_todas_4_cuadrillas.xlsx
@@ -9631,7 +9631,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -9641,10 +9641,10 @@
         <v>7.07</v>
       </c>
       <c r="R68" t="n">
-        <v>83.3</v>
+        <v>75.8</v>
       </c>
       <c r="S68" t="n">
-        <v>61.9</v>
+        <v>49.8</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -9755,20 +9755,20 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="P69" t="n">
         <v>7.07</v>
       </c>
       <c r="Q69" t="n">
-        <v>37.84</v>
+        <v>30.35</v>
       </c>
       <c r="R69" t="n">
-        <v>83.3</v>
+        <v>75.8</v>
       </c>
       <c r="S69" t="n">
-        <v>61.9</v>
+        <v>49.8</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -9839,27 +9839,27 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>ALFONSO LOPEZ PUMAREJO</t>
+          <t>NIÑA MARIA</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DE LA CANDELARIA</t>
+          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DEL PALMAR</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>176130000330</t>
+          <t>176520002261</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>CANDELARIA</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -9869,45 +9869,30 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>CL 7 9 11</t>
+          <t>KR 26 37 01</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0.23</v>
+        <v>1.99</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="R70" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="S70" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>PATOLOGIA ESTRUCTURAL</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>1.9</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -9919,14 +9904,9 @@
           <t>Moderado</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Afectación parcial</t>
-        </is>
-      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
@@ -9936,24 +9916,24 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 2 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 21 m de esa vía.</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>Calle 7</t>
+          <t>Carrera 26</t>
         </is>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AH70" t="n">
-        <v>3.407489</v>
+        <v>3.53399314013</v>
       </c>
       <c r="AI70" t="n">
-        <v>-76.34917799999999</v>
+        <v>-76.2962377697</v>
       </c>
     </row>
     <row r="71">
@@ -9983,27 +9963,27 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SAGRADA FAMILIA</t>
+          <t>LICEO FEMENINO</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DE LA CANDELARIA</t>
+          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DEL PALMAR</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>176130000356</t>
+          <t>176520000489</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>CANDELARIA</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -10013,45 +9993,30 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>CL 7 8 42</t>
+          <t>CR 28 NO 37 81</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.68</v>
+        <v>2.66</v>
       </c>
       <c r="R71" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="S71" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>PATOLOGIA ESTRUCTURAL</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>1.9</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -10063,14 +10028,9 @@
           <t>Moderado</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>Afectación parcial</t>
-        </is>
-      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
@@ -10080,24 +10040,24 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 43 m de esa vía.</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>Calle 7</t>
+          <t>Carrera 28</t>
         </is>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>3.40761667</v>
+        <v>3.53438389943</v>
       </c>
       <c r="AI71" t="n">
-        <v>-76.34858894</v>
+        <v>-76.2982293309</v>
       </c>
     </row>
     <row r="72">
@@ -10127,27 +10087,27 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>ROSA VIRGINIA</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ABSALON TORRES CAMACHO</t>
+          <t>INSTITUCION EDUCATIVA SAN VICENTE</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>176275000125</t>
+          <t>176520002295</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>FLORIDA</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -10157,35 +10117,30 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>CR 21 NO 9-89</t>
+          <t>CR 32 NO 46 00</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>27.65</v>
+        <v>5.2</v>
       </c>
       <c r="Q72" t="n">
-        <v>28.95</v>
+        <v>7.79</v>
       </c>
       <c r="R72" t="n">
-        <v>65.09999999999999</v>
+        <v>18.9</v>
       </c>
       <c r="S72" t="n">
-        <v>44</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>PATOLOGIA ESTRUCTURAL</t>
-        </is>
+        <v>6.3</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -10209,12 +10164,12 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 23 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 5 m de esa vía.</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>Calle 10</t>
+          <t>Calle 46</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
@@ -10223,10 +10178,10 @@
         </is>
       </c>
       <c r="AH72" t="n">
-        <v>3.32644406118</v>
+        <v>3.541522</v>
       </c>
       <c r="AI72" t="n">
-        <v>-76.23742270629999</v>
+        <v>-76.300059</v>
       </c>
     </row>
     <row r="73">
@@ -10256,75 +10211,60 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>JOSE EUSEBIO CARO</t>
+          <t>ENELIA RIVERA</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA INMACULADA CONCEPCION</t>
+          <t>INSTITUCION EDUCATIVA SANTA BARBARA</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>276130000288</t>
+          <t>176520001957</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>CANDELARIA</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>CR 12 NO 10-81</t>
+          <t>CLL 30 CR 40</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>28.95</v>
+        <v>7.79</v>
       </c>
       <c r="Q73" t="n">
-        <v>8.539999999999999</v>
+        <v>5.87</v>
       </c>
       <c r="R73" t="n">
-        <v>65.09999999999999</v>
+        <v>18.9</v>
       </c>
       <c r="S73" t="n">
-        <v>44</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>PATOLOGIA ESTRUCTURAL</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>6.3</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -10336,11 +10276,6 @@
           <t>Bajo</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>Afectación menor</t>
-        </is>
-      </c>
       <c r="AC73" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
@@ -10353,24 +10288,24 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 48 m de esa vía.</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>CALLEJON FLORO MERCADO CRUCE VIA 13025VL04-2E</t>
+          <t>Carrera 41</t>
         </is>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>3.39537597879</v>
+        <v>3.528369858</v>
       </c>
       <c r="AI73" t="n">
-        <v>-76.3859481842</v>
+        <v>-76.30969955</v>
       </c>
     </row>
     <row r="74">
@@ -10405,17 +10340,17 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>SANTO TOMAS DE AQUINO</t>
+          <t>CENTRO ALFONSO LOPEZ</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA FRANCISCO MIRANDA</t>
+          <t>INSTITUCION EDUCATIVA DOMINGO IRURITA</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>276520000548</t>
+          <t>176520003623</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -10425,17 +10360,17 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>VDA MESON</t>
+          <t>KR 25 21 52</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -10444,25 +10379,25 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>60.37</v>
+        <v>4.81</v>
       </c>
       <c r="Q74" t="n">
-        <v>40.02</v>
+        <v>3.85</v>
       </c>
       <c r="R74" t="n">
-        <v>117.8</v>
+        <v>14.4</v>
       </c>
       <c r="S74" t="n">
-        <v>61.6</v>
+        <v>4.5</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>No reportó al MEN</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>Sin concepto técnico ni reporte del rector</t>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -10477,7 +10412,12 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 35 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 36 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>Calle 21</t>
         </is>
       </c>
       <c r="AG74" t="inlineStr">
@@ -10486,10 +10426,10 @@
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>3.496808</v>
+        <v>3.519487</v>
       </c>
       <c r="AI74" t="n">
-        <v>-76.189471</v>
+        <v>-76.29709</v>
       </c>
     </row>
     <row r="75">
@@ -10524,17 +10464,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>ROSARIO DE FATIMA</t>
+          <t>DOMINGO IRURITA</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TABLONES</t>
+          <t>INSTITUCION EDUCATIVA DOMINGO IRURITA</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>276520000742</t>
+          <t>176520002163</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -10544,17 +10484,17 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>CORREG LA BOLSA</t>
+          <t>CL 23 33 A 37</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Candelaria</t>
+          <t>Palmira</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -10563,57 +10503,57 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>40.02</v>
+        <v>3.85</v>
       </c>
       <c r="Q75" t="n">
-        <v>17.42</v>
+        <v>5.78</v>
       </c>
       <c r="R75" t="n">
-        <v>117.8</v>
+        <v>14.4</v>
       </c>
       <c r="S75" t="n">
-        <v>61.6</v>
+        <v>4.5</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 18 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 35 m de esa vía.</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>La Bolsa</t>
+          <t>Carrera 33A</t>
         </is>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>3.555961</v>
+        <v>3.521358245</v>
       </c>
       <c r="AI75" t="n">
-        <v>-76.23436599999999</v>
+        <v>-76.30535072000001</v>
       </c>
     </row>
     <row r="76">
@@ -10648,17 +10588,17 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>NIÑA MARIA</t>
+          <t>JOSE MANUEL GROOT</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DEL PALMAR</t>
+          <t>INSTITUCION EDUCATIVA HAROLD EDER</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>176520002261</t>
+          <t>276520002192</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -10673,7 +10613,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>KR 26 37 01</t>
+          <t>CL 65 31 C 95</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -10687,25 +10627,25 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.99</v>
+        <v>10.39</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.01</v>
+        <v>3.11</v>
       </c>
       <c r="R76" t="n">
-        <v>4</v>
+        <v>25.3</v>
       </c>
       <c r="S76" t="n">
-        <v>1.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -10720,24 +10660,24 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 21 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>Carrera 26</t>
+          <t>Carrera 32</t>
         </is>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>3.53399314013</v>
+        <v>3.556083</v>
       </c>
       <c r="AI76" t="n">
-        <v>-76.2962377697</v>
+        <v>-76.30073299999999</v>
       </c>
     </row>
     <row r="77">
@@ -10756,14 +10696,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -10772,17 +10712,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>CENTRO ALFONSO LOPEZ</t>
+          <t>ROSA ZARATE DE PEÑA</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA DOMINGO IRURITA</t>
+          <t>INSTITUCION EDUCATIVA ANTONIO LIZARAZO</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>176520003623</t>
+          <t>276520001579</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -10797,7 +10737,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>KR 25 21 52</t>
+          <t>CL 63 30 06</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -10811,30 +10751,30 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>4.81</v>
+        <v>3.11</v>
       </c>
       <c r="Q77" t="n">
-        <v>7.64</v>
+        <v>11.82</v>
       </c>
       <c r="R77" t="n">
-        <v>19.5</v>
+        <v>25.3</v>
       </c>
       <c r="S77" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>Moderado</t>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
@@ -10844,12 +10784,12 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 36 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>Calle 21</t>
+          <t>Calle 64</t>
         </is>
       </c>
       <c r="AG77" t="inlineStr">
@@ -10858,10 +10798,10 @@
         </is>
       </c>
       <c r="AH77" t="n">
-        <v>3.519487</v>
+        <v>3.553627286451045</v>
       </c>
       <c r="AI77" t="n">
-        <v>-76.29709</v>
+        <v>-76.30865764715436</v>
       </c>
     </row>
     <row r="78">
@@ -10887,7 +10827,7 @@
         <v>6</v>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -10896,17 +10836,17 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ALFONSO LOPEZ PUMAREJO</t>
+          <t>CRISTOBAL COLON</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ALFONSO LOPEZ PUMAREJO</t>
+          <t>INSTITUCION EDUCATIVA TABLONES</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>176520002091</t>
+          <t>276520001552</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -10916,12 +10856,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>KR 16 32 02</t>
+          <t>VDA LA CASCADA</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -10935,30 +10875,30 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>7.64</v>
+        <v>33.72</v>
       </c>
       <c r="Q78" t="n">
-        <v>7.03</v>
+        <v>2.14</v>
       </c>
       <c r="R78" t="n">
-        <v>19.5</v>
+        <v>53.3</v>
       </c>
       <c r="S78" t="n">
-        <v>5.8</v>
+        <v>28.7</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>No reportó al MEN</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>Sin concepto técnico ni reporte del rector</t>
+          <t>Riesgo inminente de colapso</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>Critico</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
@@ -10968,7 +10908,12 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 17 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 37 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>Vía a Tienda Nueva</t>
         </is>
       </c>
       <c r="AG78" t="inlineStr">
@@ -10977,10 +10922,10 @@
         </is>
       </c>
       <c r="AH78" t="n">
-        <v>3.528177503</v>
+        <v>3.564564</v>
       </c>
       <c r="AI78" t="n">
-        <v>-76.28814192999999</v>
+        <v>-76.231579</v>
       </c>
     </row>
     <row r="79">
@@ -10995,19 +10940,19 @@
         </is>
       </c>
       <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6</v>
+      </c>
+      <c r="F79" t="n">
         <v>2</v>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>lunes</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>7</v>
-      </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>Palmira</t>
@@ -11015,17 +10960,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ENELIA RIVERA</t>
+          <t>ROSARIO DE FATIMA</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SANTA BARBARA</t>
+          <t>INSTITUCION EDUCATIVA TABLONES</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>176520001957</t>
+          <t>276520000742</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -11035,12 +10980,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>CLL 30 CR 40</t>
+          <t>CORREG LA BOLSA</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -11054,57 +10999,57 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>6</v>
+        <v>2.14</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.8</v>
+        <v>17.42</v>
       </c>
       <c r="R79" t="n">
-        <v>16.6</v>
+        <v>53.3</v>
       </c>
       <c r="S79" t="n">
-        <v>5.5</v>
+        <v>28.7</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>Bajo</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 48 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>Carrera 41</t>
+          <t>La Bolsa</t>
         </is>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AH79" t="n">
-        <v>3.528369858</v>
+        <v>3.555961</v>
       </c>
       <c r="AI79" t="n">
-        <v>-76.30969955</v>
+        <v>-76.23436599999999</v>
       </c>
     </row>
     <row r="80">
@@ -11130,7 +11075,7 @@
         <v>7</v>
       </c>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -11139,17 +11084,17 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>DOMINGO IRURITA</t>
+          <t>ROSARIO MENESSES</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA DOMINGO IRURITA</t>
+          <t>INSTITUCION EDUCATIVA SAGRADA FAMILIA POTRERILLO</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>176520002163</t>
+          <t>276520001676</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -11159,12 +11104,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>CL 23 33 A 37</t>
+          <t>VDA LOS CUCHOS</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -11178,57 +11123,52 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>4.8</v>
+        <v>49.13</v>
       </c>
       <c r="Q80" t="n">
-        <v>5.78</v>
+        <v>33.35</v>
       </c>
       <c r="R80" t="n">
-        <v>16.6</v>
+        <v>110.6</v>
       </c>
       <c r="S80" t="n">
-        <v>5.5</v>
+        <v>52.9</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>Moderado</t>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 35 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF80" t="inlineStr">
-        <is>
-          <t>Carrera 33A</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 37 m de esa vía.</t>
         </is>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AH80" t="n">
-        <v>3.521358245</v>
+        <v>3.550561</v>
       </c>
       <c r="AI80" t="n">
-        <v>-76.30535072000001</v>
+        <v>-76.167422</v>
       </c>
     </row>
     <row r="81">
@@ -11247,14 +11187,14 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -11263,17 +11203,17 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>JOSE MANUEL GROOT</t>
+          <t>TABLONES</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA HAROLD EDER</t>
+          <t>INSTITUCION EDUCATIVA TABLONES</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>276520002192</t>
+          <t>276520000564</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -11283,12 +11223,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>CL 65 31 C 95</t>
+          <t>CORREG TABLONES</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -11302,45 +11242,40 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>10.39</v>
+        <v>33.35</v>
       </c>
       <c r="Q81" t="n">
-        <v>8.789999999999999</v>
+        <v>28.1</v>
       </c>
       <c r="R81" t="n">
-        <v>21.8</v>
+        <v>110.6</v>
       </c>
       <c r="S81" t="n">
-        <v>7.6</v>
+        <v>52.9</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF81" t="inlineStr">
-        <is>
-          <t>Carrera 32</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 21 m de esa vía.</t>
         </is>
       </c>
       <c r="AG81" t="inlineStr">
@@ -11349,10 +11284,10 @@
         </is>
       </c>
       <c r="AH81" t="n">
-        <v>3.556083</v>
+        <v>3.602559</v>
       </c>
       <c r="AI81" t="n">
-        <v>-76.30073299999999</v>
+        <v>-76.20097800000001</v>
       </c>
     </row>
     <row r="82">
@@ -11378,7 +11313,7 @@
         <v>8</v>
       </c>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -11387,17 +11322,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>LICEO FEMENINO</t>
+          <t>LA NEVERA</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DEL PALMAR</t>
+          <t>INSTITUCION EDUCATIVA SAGRADA FAMILIA POTRERILLO</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>176520000489</t>
+          <t>276520003032</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -11407,12 +11342,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>CR 28 NO 37 81</t>
+          <t>VDA LA NEVERA</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -11426,16 +11361,16 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>8.789999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.66</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="R82" t="n">
-        <v>21.8</v>
+        <v>182.3</v>
       </c>
       <c r="S82" t="n">
-        <v>7.6</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -11449,34 +11384,29 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 43 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF82" t="inlineStr">
-        <is>
-          <t>Carrera 28</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 901 m de esa vía.</t>
         </is>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AH82" t="n">
-        <v>3.53438389943</v>
+        <v>3.5386</v>
       </c>
       <c r="AI82" t="n">
-        <v>-76.2982293309</v>
+        <v>-76.1206</v>
       </c>
     </row>
     <row r="83">
@@ -11511,7 +11441,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>CRISTOBAL COLON</t>
+          <t>RITA SABOGAL</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -11521,7 +11451,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>276520001552</t>
+          <t>276520001633</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -11536,7 +11466,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>VDA LA CASCADA</t>
+          <t>VDA TIATINO</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -11550,57 +11480,52 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>33.72</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="Q83" t="n">
-        <v>22.95</v>
+        <v>74.64</v>
       </c>
       <c r="R83" t="n">
-        <v>99.40000000000001</v>
+        <v>168.9</v>
       </c>
       <c r="S83" t="n">
-        <v>56.1</v>
+        <v>80.3</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>Critico</t>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 37 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF83" t="inlineStr">
-        <is>
-          <t>Vía a Tienda Nueva</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 13 m de esa vía.</t>
         </is>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AH83" t="n">
-        <v>3.564564</v>
+        <v>3.646588</v>
       </c>
       <c r="AI83" t="n">
-        <v>-76.231579</v>
+        <v>-76.06974599999999</v>
       </c>
     </row>
     <row r="84">
@@ -11619,14 +11544,14 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -11635,17 +11560,17 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>MARCO FIDEL SUAREZ</t>
+          <t>ALFONSO LOPEZ PUMAREJO</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TABLONES</t>
+          <t>INSTITUCION EDUCATIVA ALFONSO LOPEZ PUMAREJO</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>276520001684</t>
+          <t>176520002091</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -11655,12 +11580,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>VDA LA ESPERANZA</t>
+          <t>KR 16 32 02</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -11670,24 +11595,24 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>22.95</v>
+        <v>7.29</v>
       </c>
       <c r="Q84" t="n">
-        <v>42.74</v>
+        <v>33.77</v>
       </c>
       <c r="R84" t="n">
-        <v>99.40000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="S84" t="n">
-        <v>56.1</v>
+        <v>48.8</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>No está en la capa del MEN</t>
+          <t>No reportó al MEN</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
@@ -11697,7 +11622,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr">
@@ -11707,7 +11632,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 9 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 17 m de esa vía.</t>
         </is>
       </c>
       <c r="AG84" t="inlineStr">
@@ -11716,10 +11641,10 @@
         </is>
       </c>
       <c r="AH84" t="n">
-        <v>3.610511</v>
+        <v>3.528177503</v>
       </c>
       <c r="AI84" t="n">
-        <v>-76.155193</v>
+        <v>-76.28814192999999</v>
       </c>
     </row>
     <row r="85">
@@ -11745,7 +11670,7 @@
         <v>10</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -11754,17 +11679,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>MARIA DOMINGUEZ</t>
+          <t>SANTO TOMAS DE AQUINO</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAGRADA FAMILIA POTRERILLO</t>
+          <t>INSTITUCION EDUCATIVA FRANCISCO MIRANDA</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>276520001625</t>
+          <t>276520000548</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -11779,7 +11704,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>VDA LA MARIA</t>
+          <t>VDA MESON</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -11789,24 +11714,24 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>58.29</v>
+        <v>33.77</v>
       </c>
       <c r="Q85" t="n">
-        <v>68.20999999999999</v>
+        <v>52.56</v>
       </c>
       <c r="R85" t="n">
-        <v>126.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="S85" t="n">
-        <v>49.7</v>
+        <v>48.8</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>No está en la capa del MEN</t>
+          <t>No reportó al MEN</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
@@ -11816,34 +11741,29 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 16 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF85" t="inlineStr">
-        <is>
-          <t>Via Tenjo - Mariala Alta</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AH85" t="n">
-        <v>3.510825276</v>
+        <v>3.497136</v>
       </c>
       <c r="AI85" t="n">
-        <v>-76.14317477</v>
+        <v>-76.190214</v>
       </c>
     </row>
     <row r="86">
@@ -11873,60 +11793,75 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>TABLONES</t>
+          <t>ALFONSO LOPEZ PUMAREJO</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TABLONES</t>
+          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DE LA CANDELARIA</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>276520000564</t>
+          <t>176130000330</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>CANDELARIA</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>CORREG TABLONES</t>
+          <t>CL 7 9 11</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>38.78</v>
+        <v>0.23</v>
       </c>
       <c r="Q86" t="n">
-        <v>25.67</v>
+        <v>1.88</v>
       </c>
       <c r="R86" t="n">
-        <v>117.8</v>
+        <v>2.1</v>
       </c>
       <c r="S86" t="n">
-        <v>61</v>
+        <v>0.6</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>No habitable</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -11938,19 +11873,29 @@
           <t>Moderado</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 21 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 2 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>Calle 7</t>
         </is>
       </c>
       <c r="AG86" t="inlineStr">
@@ -11959,10 +11904,10 @@
         </is>
       </c>
       <c r="AH86" t="n">
-        <v>3.602559</v>
+        <v>3.407489</v>
       </c>
       <c r="AI86" t="n">
-        <v>-76.20097800000001</v>
+        <v>-76.34917799999999</v>
       </c>
     </row>
     <row r="87">
@@ -11981,107 +11926,132 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ROSARIO MENESSES</t>
+          <t>SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAGRADA FAMILIA POTRERILLO</t>
+          <t>INSTITUCION EDUCATIVA NUESTRA SEÑORA DE LA CANDELARIA</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>276520001676</t>
+          <t>176130000356</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>CANDELARIA</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>VDA LOS CUCHOS</t>
+          <t>CL 7 8 42</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>25.67</v>
+        <v>0.44</v>
       </c>
       <c r="Q87" t="n">
-        <v>53.34</v>
+        <v>1.68</v>
       </c>
       <c r="R87" t="n">
-        <v>117.8</v>
+        <v>2.1</v>
       </c>
       <c r="S87" t="n">
-        <v>61</v>
+        <v>0.6</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>No habitable</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>No reportó al MEN</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>Sin concepto técnico ni reporte del rector</t>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 1330 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>Calle 7</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AH87" t="n">
-        <v>3.582859967</v>
+        <v>3.40761667</v>
       </c>
       <c r="AI87" t="n">
-        <v>-76.15750609</v>
+        <v>-76.34858894</v>
       </c>
     </row>
     <row r="88">
@@ -12096,111 +12066,121 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>LA NEVERA</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAGRADA FAMILIA POTRERILLO</t>
+          <t>INSTITUCION EDUCATIVA ABSALON TORRES CAMACHO</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>276520003032</t>
+          <t>176275000125</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>FLORIDA</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>VDA LA NEVERA</t>
+          <t>CR 21 NO 9-89</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>99.38</v>
+        <v>27.65</v>
       </c>
       <c r="Q88" t="n">
-        <v>104.79</v>
+        <v>28.95</v>
       </c>
       <c r="R88" t="n">
-        <v>204.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="S88" t="n">
-        <v>81.09999999999999</v>
+        <v>44</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 272 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 23 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>Calle 10</t>
         </is>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AH88" t="n">
-        <v>3.545813</v>
+        <v>3.32644406118</v>
       </c>
       <c r="AI88" t="n">
-        <v>-76.113687</v>
+        <v>-76.23742270629999</v>
       </c>
     </row>
     <row r="89">
@@ -12226,31 +12206,31 @@
         <v>13</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>RITA SABOGAL</t>
+          <t>JOSE EUSEBIO CARO</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA TABLONES</t>
+          <t>INSTITUCION EDUCATIVA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>276520001633</t>
+          <t>276130000288</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>CANDELARIA</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -12260,66 +12240,91 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>VDA TIATINO</t>
+          <t>CR 12 NO 10-81</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>98.42</v>
+        <v>28.95</v>
       </c>
       <c r="Q89" t="n">
-        <v>79.44</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="R89" t="n">
-        <v>177.9</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="S89" t="n">
-        <v>83.90000000000001</v>
+        <v>44</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>PATOLOGIA ESTRUCTURAL</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>No habitable</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>No reportó al MEN</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>Sin concepto técnico ni reporte del rector</t>
+          <t>Afectación menor</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 352 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>CALLEJON FLORO MERCADO CRUCE VIA 13025VL04-2E</t>
         </is>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AH89" t="n">
-        <v>3.641394707</v>
+        <v>3.39537597879</v>
       </c>
       <c r="AI89" t="n">
-        <v>-76.05537963</v>
+        <v>-76.3859481842</v>
       </c>
     </row>
     <row r="90">
@@ -12384,7 +12389,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -12393,16 +12398,16 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>29.19</v>
+        <v>36.99</v>
       </c>
       <c r="Q90" t="n">
         <v>11.21</v>
       </c>
       <c r="R90" t="n">
-        <v>77.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="S90" t="n">
-        <v>52.2</v>
+        <v>60.7</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -12503,7 +12508,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Candelaria</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -12518,10 +12523,10 @@
         <v>37.19</v>
       </c>
       <c r="R91" t="n">
-        <v>77.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="S91" t="n">
-        <v>52.2</v>
+        <v>60.7</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -12599,7 +12604,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -12800,10 +12805,10 @@
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>18.9</v>
+        <v>15.1</v>
       </c>
       <c r="E14" t="n">
-        <v>572</v>
+        <v>461</v>
       </c>
       <c r="F14" t="n">
         <v>13</v>
